--- a/5. Other/Danh sách số SIM BH-SX/SIM_Test BH-SX.xlsx
+++ b/5. Other/Danh sách số SIM BH-SX/SIM_Test BH-SX.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\5. Other\Danh sách số SIM BH-SX\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNETGPS\VNET\5. Other\Danh sách số SIM BH-SX\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC80D5A7-F605-41F6-A101-8F16B9E33C19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C54B437D-A107-40BF-BCC6-03B211A572FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{68255EAF-D8EA-4C2C-BCF7-C24A5FBA6E37}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{68255EAF-D8EA-4C2C-BCF7-C24A5FBA6E37}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="61">
   <si>
     <t>Seri</t>
   </si>
@@ -203,9 +203,6 @@
   </si>
   <si>
     <t>01699555418</t>
-  </si>
-  <si>
-    <t>cho a thông mượn</t>
   </si>
   <si>
     <t>Tùng đang sử dụng</t>
@@ -1066,9 +1063,7 @@
       </c>
       <c r="D21" s="20"/>
       <c r="E21" s="20"/>
-      <c r="F21" s="6" t="s">
-        <v>59</v>
-      </c>
+      <c r="F21" s="6"/>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="2">
@@ -1301,7 +1296,7 @@
         <v>55</v>
       </c>
       <c r="F37" s="12" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
@@ -1319,7 +1314,7 @@
         <v>55</v>
       </c>
       <c r="F38" s="12" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
@@ -1336,9 +1331,7 @@
       <c r="E39" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="F39" s="12" t="s">
-        <v>59</v>
-      </c>
+      <c r="F39" s="12"/>
     </row>
   </sheetData>
   <mergeCells count="7">

--- a/5. Other/Danh sách số SIM BH-SX/SIM_Test BH-SX.xlsx
+++ b/5. Other/Danh sách số SIM BH-SX/SIM_Test BH-SX.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNETGPS\VNET\5. Other\Danh sách số SIM BH-SX\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\5. Other\Danh sách số SIM BH-SX\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C54B437D-A107-40BF-BCC6-03B211A572FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A7B75C8-112D-4F0F-8383-1663A5A29BA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{68255EAF-D8EA-4C2C-BCF7-C24A5FBA6E37}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{68255EAF-D8EA-4C2C-BCF7-C24A5FBA6E37}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="69">
   <si>
     <t>Seri</t>
   </si>
@@ -205,10 +205,34 @@
     <t>01699555418</t>
   </si>
   <si>
-    <t>Tùng đang sử dụng</t>
-  </si>
-  <si>
-    <t>Hậu đang sử dụng</t>
+    <t>01212634836</t>
+  </si>
+  <si>
+    <t>01210118612</t>
+  </si>
+  <si>
+    <t>01210565136</t>
+  </si>
+  <si>
+    <t>8401260150905596</t>
+  </si>
+  <si>
+    <t>8401260150905594</t>
+  </si>
+  <si>
+    <t>8401260150910847</t>
+  </si>
+  <si>
+    <t>Mobifone</t>
+  </si>
+  <si>
+    <t>Hậu đang sử dụng, Viettel</t>
+  </si>
+  <si>
+    <t>Viettel</t>
+  </si>
+  <si>
+    <t>Tùng đang sử dụng, Viettel(Thịnh Aithings đang giữ)</t>
   </si>
 </sst>
 </file>
@@ -352,7 +376,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -361,9 +385,6 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="49" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="49" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -728,7 +749,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{69ED331E-3E24-49D9-A8FD-C7C548CF9C48}">
-  <dimension ref="A1:F39"/>
+  <dimension ref="A1:F42"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5.140625" style="3" customWidth="1"/>
@@ -740,60 +761,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="B1" s="10" t="s">
+      <c r="B1" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="10" t="s">
+      <c r="C1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="10" t="s">
+      <c r="D1" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="10" t="s">
+      <c r="E1" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="F1" s="10" t="s">
+      <c r="F1" s="9" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="7">
+      <c r="A2" s="6">
         <v>1</v>
       </c>
-      <c r="B2" s="11">
+      <c r="B2" s="10">
         <v>1174221624</v>
       </c>
-      <c r="C2" s="11" t="s">
+      <c r="C2" s="10" t="s">
         <v>3</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="E2" s="17" t="s">
+      <c r="E2" s="16" t="s">
         <v>40</v>
       </c>
-      <c r="F2" s="6" t="s">
+      <c r="F2" s="5" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="7">
+      <c r="A3" s="6">
         <v>2</v>
       </c>
-      <c r="B3" s="11">
+      <c r="B3" s="10">
         <v>1174221625</v>
       </c>
-      <c r="C3" s="11" t="s">
+      <c r="C3" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="D3" s="18" t="s">
+      <c r="D3" s="17" t="s">
         <v>42</v>
       </c>
-      <c r="E3" s="17"/>
-      <c r="F3" s="6" t="s">
+      <c r="E3" s="16"/>
+      <c r="F3" s="5" t="s">
         <v>46</v>
       </c>
     </row>
@@ -807,9 +828,9 @@
       <c r="C4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D4" s="18"/>
-      <c r="E4" s="17"/>
-      <c r="F4" s="6"/>
+      <c r="D4" s="17"/>
+      <c r="E4" s="16"/>
+      <c r="F4" s="5"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
@@ -821,25 +842,25 @@
       <c r="C5" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D5" s="21" t="s">
+      <c r="D5" s="20" t="s">
         <v>43</v>
       </c>
-      <c r="E5" s="17"/>
-      <c r="F5" s="6"/>
+      <c r="E5" s="16"/>
+      <c r="F5" s="5"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
         <v>5</v>
       </c>
-      <c r="B6" s="9">
+      <c r="B6" s="8">
         <v>1174966078</v>
       </c>
-      <c r="C6" s="9" t="s">
+      <c r="C6" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="D6" s="21"/>
-      <c r="E6" s="17"/>
-      <c r="F6" s="6"/>
+      <c r="D6" s="20"/>
+      <c r="E6" s="16"/>
+      <c r="F6" s="5"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
@@ -851,27 +872,27 @@
       <c r="C7" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D7" s="18" t="s">
+      <c r="D7" s="17" t="s">
         <v>41</v>
       </c>
-      <c r="E7" s="19" t="s">
+      <c r="E7" s="18" t="s">
         <v>44</v>
       </c>
-      <c r="F7" s="6"/>
+      <c r="F7" s="5"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="7">
+      <c r="A8" s="6">
         <v>7</v>
       </c>
-      <c r="B8" s="8">
+      <c r="B8" s="7">
         <v>1173963041</v>
       </c>
-      <c r="C8" s="8" t="s">
+      <c r="C8" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="D8" s="18"/>
-      <c r="E8" s="20"/>
-      <c r="F8" s="6" t="s">
+      <c r="D8" s="17"/>
+      <c r="E8" s="19"/>
+      <c r="F8" s="5" t="s">
         <v>47</v>
       </c>
     </row>
@@ -885,9 +906,9 @@
       <c r="C9" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D9" s="18"/>
-      <c r="E9" s="20"/>
-      <c r="F9" s="6" t="s">
+      <c r="D9" s="17"/>
+      <c r="E9" s="19"/>
+      <c r="F9" s="5" t="s">
         <v>50</v>
       </c>
     </row>
@@ -901,447 +922,497 @@
       <c r="C10" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D10" s="18"/>
-      <c r="E10" s="20"/>
-      <c r="F10" s="6"/>
+      <c r="D10" s="17"/>
+      <c r="E10" s="19"/>
+      <c r="F10" s="5"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="2">
         <v>10</v>
       </c>
-      <c r="B11" s="1">
-        <v>1173963044</v>
+      <c r="B11" s="1" t="s">
+        <v>64</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="D11" s="18" t="s">
-        <v>42</v>
-      </c>
-      <c r="E11" s="20"/>
-      <c r="F11" s="6"/>
+        <v>59</v>
+      </c>
+      <c r="D11" s="17"/>
+      <c r="E11" s="19"/>
+      <c r="F11" s="5" t="s">
+        <v>65</v>
+      </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="7">
+      <c r="A12" s="2">
         <v>11</v>
       </c>
-      <c r="B12" s="8">
-        <v>1173963045</v>
-      </c>
-      <c r="C12" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D12" s="18"/>
-      <c r="E12" s="20"/>
-      <c r="F12" s="6" t="s">
-        <v>46</v>
+      <c r="B12" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="D12" s="17"/>
+      <c r="E12" s="19"/>
+      <c r="F12" s="5" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="2">
         <v>12</v>
       </c>
-      <c r="B13" s="1">
-        <v>1173963046</v>
+      <c r="B13" s="1" t="s">
+        <v>62</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D13" s="18"/>
-      <c r="E13" s="20"/>
-      <c r="F13" s="6"/>
+        <v>61</v>
+      </c>
+      <c r="D13" s="17"/>
+      <c r="E13" s="19"/>
+      <c r="F13" s="5" t="s">
+        <v>65</v>
+      </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="2">
         <v>13</v>
       </c>
       <c r="B14" s="1">
-        <v>1173963047</v>
+        <v>1173963044</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D14" s="18"/>
-      <c r="E14" s="20"/>
-      <c r="F14" s="6"/>
+        <v>12</v>
+      </c>
+      <c r="D14" s="17" t="s">
+        <v>42</v>
+      </c>
+      <c r="E14" s="19"/>
+      <c r="F14" s="5"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="2">
         <v>14</v>
       </c>
-      <c r="B15" s="1">
-        <v>1173963048</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="D15" s="19" t="s">
-        <v>43</v>
-      </c>
-      <c r="E15" s="20"/>
-      <c r="F15" s="6"/>
+      <c r="B15" s="7">
+        <v>1173963045</v>
+      </c>
+      <c r="C15" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="D15" s="17"/>
+      <c r="E15" s="19"/>
+      <c r="F15" s="5" t="s">
+        <v>46</v>
+      </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="2">
         <v>15</v>
       </c>
       <c r="B16" s="1">
-        <v>1173963049</v>
+        <v>1173963046</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="D16" s="20"/>
-      <c r="E16" s="20"/>
-      <c r="F16" s="6"/>
+        <v>14</v>
+      </c>
+      <c r="D16" s="17"/>
+      <c r="E16" s="19"/>
+      <c r="F16" s="5"/>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="2">
         <v>16</v>
       </c>
       <c r="B17" s="1">
-        <v>1173963050</v>
+        <v>1173963047</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D17" s="20"/>
-      <c r="E17" s="20"/>
-      <c r="F17" s="6"/>
+        <v>15</v>
+      </c>
+      <c r="D17" s="17"/>
+      <c r="E17" s="19"/>
+      <c r="F17" s="5"/>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="2">
         <v>17</v>
       </c>
       <c r="B18" s="1">
-        <v>1173963051</v>
+        <v>1173963048</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D18" s="20"/>
-      <c r="E18" s="20"/>
-      <c r="F18" s="6"/>
+        <v>16</v>
+      </c>
+      <c r="D18" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="E18" s="19"/>
+      <c r="F18" s="5"/>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="2">
         <v>18</v>
       </c>
-      <c r="B19" s="9">
-        <v>1173963052</v>
-      </c>
-      <c r="C19" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="D19" s="20"/>
-      <c r="E19" s="20"/>
-      <c r="F19" s="6"/>
+      <c r="B19" s="1">
+        <v>1173963049</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D19" s="19"/>
+      <c r="E19" s="19"/>
+      <c r="F19" s="5"/>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="2">
         <v>19</v>
       </c>
-      <c r="B20" s="9">
-        <v>1173963053</v>
-      </c>
-      <c r="C20" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="D20" s="20"/>
-      <c r="E20" s="20"/>
-      <c r="F20" s="6"/>
+      <c r="B20" s="1">
+        <v>1173963050</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D20" s="19"/>
+      <c r="E20" s="19"/>
+      <c r="F20" s="5"/>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="2">
         <v>20</v>
       </c>
-      <c r="B21" s="9">
-        <v>1173963054</v>
-      </c>
-      <c r="C21" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="D21" s="20"/>
-      <c r="E21" s="20"/>
-      <c r="F21" s="6"/>
+      <c r="B21" s="1">
+        <v>1173963051</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D21" s="19"/>
+      <c r="E21" s="19"/>
+      <c r="F21" s="5"/>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="2">
         <v>21</v>
       </c>
-      <c r="B22" s="9">
-        <v>1173963055</v>
-      </c>
-      <c r="C22" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="D22" s="20"/>
-      <c r="E22" s="20"/>
-      <c r="F22" s="6"/>
+      <c r="B22" s="8">
+        <v>1173963052</v>
+      </c>
+      <c r="C22" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="D22" s="19"/>
+      <c r="E22" s="19"/>
+      <c r="F22" s="5"/>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" s="4">
+      <c r="A23" s="2">
         <v>22</v>
       </c>
-      <c r="B23" s="5">
-        <v>1173963056</v>
-      </c>
-      <c r="C23" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="D23" s="20"/>
-      <c r="E23" s="20"/>
-      <c r="F23" s="6" t="s">
-        <v>46</v>
-      </c>
+      <c r="B23" s="8">
+        <v>1173963053</v>
+      </c>
+      <c r="C23" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="D23" s="19"/>
+      <c r="E23" s="19"/>
+      <c r="F23" s="5"/>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="2">
         <v>23</v>
       </c>
-      <c r="B24" s="9">
-        <v>1173963057</v>
-      </c>
-      <c r="C24" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="D24" s="20"/>
-      <c r="E24" s="20"/>
-      <c r="F24" s="6"/>
+      <c r="B24" s="8">
+        <v>1173963054</v>
+      </c>
+      <c r="C24" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="D24" s="19"/>
+      <c r="E24" s="19"/>
+      <c r="F24" s="5"/>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="2">
         <v>24</v>
       </c>
-      <c r="B25" s="9">
-        <v>1173963058</v>
-      </c>
-      <c r="C25" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="D25" s="20"/>
-      <c r="E25" s="20"/>
-      <c r="F25" s="6"/>
+      <c r="B25" s="8">
+        <v>1173963055</v>
+      </c>
+      <c r="C25" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="D25" s="19"/>
+      <c r="E25" s="19"/>
+      <c r="F25" s="5"/>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="2">
         <v>25</v>
       </c>
-      <c r="B26" s="9">
-        <v>1173963059</v>
-      </c>
-      <c r="C26" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="D26" s="20"/>
-      <c r="E26" s="20"/>
-      <c r="F26" s="6"/>
+      <c r="B26" s="4">
+        <v>1173963056</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D26" s="19"/>
+      <c r="E26" s="19"/>
+      <c r="F26" s="5" t="s">
+        <v>46</v>
+      </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="2">
         <v>26</v>
       </c>
-      <c r="B27" s="9">
-        <v>1173963060</v>
-      </c>
-      <c r="C27" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="D27" s="20"/>
-      <c r="E27" s="20"/>
-      <c r="F27" s="6"/>
+      <c r="B27" s="8">
+        <v>1173963057</v>
+      </c>
+      <c r="C27" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="D27" s="19"/>
+      <c r="E27" s="19"/>
+      <c r="F27" s="5"/>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A28" s="7">
+      <c r="A28" s="2">
         <v>27</v>
       </c>
       <c r="B28" s="8">
-        <v>1173963061</v>
+        <v>1173963058</v>
       </c>
       <c r="C28" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="D28" s="20"/>
-      <c r="E28" s="20"/>
-      <c r="F28" s="6" t="s">
-        <v>49</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="D28" s="19"/>
+      <c r="E28" s="19"/>
+      <c r="F28" s="5"/>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="2">
         <v>28</v>
       </c>
-      <c r="B29" s="9">
-        <v>1173963062</v>
-      </c>
-      <c r="C29" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="D29" s="20"/>
-      <c r="E29" s="20"/>
-      <c r="F29" s="6"/>
+      <c r="B29" s="8">
+        <v>1173963059</v>
+      </c>
+      <c r="C29" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="D29" s="19"/>
+      <c r="E29" s="19"/>
+      <c r="F29" s="5"/>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="2">
         <v>29</v>
       </c>
-      <c r="B30" s="9">
-        <v>1173963063</v>
-      </c>
-      <c r="C30" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="D30" s="20"/>
-      <c r="E30" s="20"/>
-      <c r="F30" s="6"/>
+      <c r="B30" s="8">
+        <v>1173963060</v>
+      </c>
+      <c r="C30" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="D30" s="19"/>
+      <c r="E30" s="19"/>
+      <c r="F30" s="5"/>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="2">
         <v>30</v>
       </c>
-      <c r="B31" s="9">
-        <v>1173963064</v>
-      </c>
-      <c r="C31" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="D31" s="20"/>
-      <c r="E31" s="20"/>
-      <c r="F31" s="6"/>
+      <c r="B31" s="7">
+        <v>1173963061</v>
+      </c>
+      <c r="C31" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="D31" s="19"/>
+      <c r="E31" s="19"/>
+      <c r="F31" s="5" t="s">
+        <v>49</v>
+      </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A32" s="4">
+      <c r="A32" s="2">
         <v>31</v>
       </c>
-      <c r="B32" s="5">
-        <v>1173963065</v>
-      </c>
-      <c r="C32" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="D32" s="20"/>
-      <c r="E32" s="20"/>
-      <c r="F32" s="6" t="s">
-        <v>48</v>
-      </c>
+      <c r="B32" s="8">
+        <v>1173963062</v>
+      </c>
+      <c r="C32" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="D32" s="19"/>
+      <c r="E32" s="19"/>
+      <c r="F32" s="5"/>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="2">
         <v>32</v>
       </c>
-      <c r="B33" s="9">
-        <v>1173963066</v>
-      </c>
-      <c r="C33" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="D33" s="20"/>
-      <c r="E33" s="20"/>
-      <c r="F33" s="6"/>
+      <c r="B33" s="8">
+        <v>1173963063</v>
+      </c>
+      <c r="C33" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="D33" s="19"/>
+      <c r="E33" s="19"/>
+      <c r="F33" s="5"/>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="2">
         <v>33</v>
       </c>
-      <c r="B34" s="9">
-        <v>1173963067</v>
-      </c>
-      <c r="C34" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="D34" s="20"/>
-      <c r="E34" s="20"/>
-      <c r="F34" s="6"/>
+      <c r="B34" s="8">
+        <v>1173963064</v>
+      </c>
+      <c r="C34" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="D34" s="19"/>
+      <c r="E34" s="19"/>
+      <c r="F34" s="5"/>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="2">
         <v>34</v>
       </c>
-      <c r="B35" s="9">
-        <v>1170534788</v>
-      </c>
-      <c r="C35" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="D35" s="20"/>
-      <c r="E35" s="20"/>
-      <c r="F35" s="6"/>
+      <c r="B35" s="4">
+        <v>1173963065</v>
+      </c>
+      <c r="C35" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="D35" s="19"/>
+      <c r="E35" s="19"/>
+      <c r="F35" s="5" t="s">
+        <v>48</v>
+      </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="2">
         <v>35</v>
       </c>
-      <c r="B36" s="9">
-        <v>1170534789</v>
-      </c>
-      <c r="C36" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="D36" s="20"/>
-      <c r="E36" s="20"/>
-      <c r="F36" s="6"/>
+      <c r="B36" s="8">
+        <v>1173963066</v>
+      </c>
+      <c r="C36" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="D36" s="19"/>
+      <c r="E36" s="19"/>
+      <c r="F36" s="5"/>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="2">
         <v>36</v>
       </c>
-      <c r="B37" s="13" t="s">
-        <v>52</v>
-      </c>
-      <c r="C37" s="14" t="s">
-        <v>56</v>
-      </c>
-      <c r="D37" s="20"/>
-      <c r="E37" s="16" t="s">
-        <v>55</v>
-      </c>
-      <c r="F37" s="12" t="s">
-        <v>59</v>
-      </c>
+      <c r="B37" s="8">
+        <v>1173963067</v>
+      </c>
+      <c r="C37" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="D37" s="19"/>
+      <c r="E37" s="19"/>
+      <c r="F37" s="5"/>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="2">
         <v>37</v>
       </c>
-      <c r="B38" s="15" t="s">
-        <v>53</v>
-      </c>
-      <c r="C38" s="14" t="s">
-        <v>57</v>
-      </c>
-      <c r="D38" s="20"/>
-      <c r="E38" s="16" t="s">
-        <v>55</v>
-      </c>
-      <c r="F38" s="12" t="s">
-        <v>60</v>
-      </c>
+      <c r="B38" s="8">
+        <v>1170534788</v>
+      </c>
+      <c r="C38" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="D38" s="19"/>
+      <c r="E38" s="19"/>
+      <c r="F38" s="5"/>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="2">
         <v>38</v>
       </c>
-      <c r="B39" s="15" t="s">
+      <c r="B39" s="8">
+        <v>1170534789</v>
+      </c>
+      <c r="C39" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="D39" s="19"/>
+      <c r="E39" s="19"/>
+      <c r="F39" s="5"/>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A40" s="2">
+        <v>39</v>
+      </c>
+      <c r="B40" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="C40" s="13" t="s">
+        <v>56</v>
+      </c>
+      <c r="D40" s="19"/>
+      <c r="E40" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="F40" s="11" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A41" s="2">
+        <v>40</v>
+      </c>
+      <c r="B41" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="C41" s="13" t="s">
+        <v>57</v>
+      </c>
+      <c r="D41" s="19"/>
+      <c r="E41" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="F41" s="11" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A42" s="2">
+        <v>41</v>
+      </c>
+      <c r="B42" s="14" t="s">
         <v>54</v>
       </c>
-      <c r="C39" s="14" t="s">
+      <c r="C42" s="13" t="s">
         <v>58</v>
       </c>
-      <c r="D39" s="22"/>
-      <c r="E39" s="16" t="s">
+      <c r="D42" s="21"/>
+      <c r="E42" s="15" t="s">
         <v>55</v>
       </c>
-      <c r="F39" s="12"/>
+      <c r="F42" s="11" t="s">
+        <v>67</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="7">
     <mergeCell ref="E2:E6"/>
     <mergeCell ref="D3:D4"/>
-    <mergeCell ref="E7:E36"/>
-    <mergeCell ref="D7:D10"/>
-    <mergeCell ref="D11:D14"/>
+    <mergeCell ref="E7:E39"/>
+    <mergeCell ref="D7:D13"/>
+    <mergeCell ref="D14:D17"/>
     <mergeCell ref="D5:D6"/>
-    <mergeCell ref="D15:D39"/>
+    <mergeCell ref="D18:D42"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="256" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>

--- a/5. Other/Danh sách số SIM BH-SX/SIM_Test BH-SX.xlsx
+++ b/5. Other/Danh sách số SIM BH-SX/SIM_Test BH-SX.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\5. Other\Danh sách số SIM BH-SX\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNETGPS\VNET\5. Other\Danh sách số SIM BH-SX\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A7B75C8-112D-4F0F-8383-1663A5A29BA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A21EBACD-0233-4439-BE2C-627CC2C29121}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{68255EAF-D8EA-4C2C-BCF7-C24A5FBA6E37}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{68255EAF-D8EA-4C2C-BCF7-C24A5FBA6E37}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="69">
   <si>
     <t>Seri</t>
   </si>
@@ -280,7 +280,7 @@
       <family val="1"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -308,6 +308,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -376,7 +382,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -416,6 +422,12 @@
     </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -793,7 +805,7 @@
       <c r="D2" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="E2" s="16" t="s">
+      <c r="E2" s="18" t="s">
         <v>40</v>
       </c>
       <c r="F2" s="5" t="s">
@@ -810,10 +822,10 @@
       <c r="C3" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="D3" s="17" t="s">
+      <c r="D3" s="19" t="s">
         <v>42</v>
       </c>
-      <c r="E3" s="16"/>
+      <c r="E3" s="18"/>
       <c r="F3" s="5" t="s">
         <v>46</v>
       </c>
@@ -828,39 +840,41 @@
       <c r="C4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D4" s="17"/>
-      <c r="E4" s="16"/>
+      <c r="D4" s="19"/>
+      <c r="E4" s="18"/>
       <c r="F4" s="5"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
         <v>4</v>
       </c>
-      <c r="B5" s="1">
+      <c r="B5" s="16">
         <v>1174966077</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D5" s="20" t="s">
+      <c r="D5" s="22" t="s">
         <v>43</v>
       </c>
-      <c r="E5" s="16"/>
+      <c r="E5" s="18"/>
       <c r="F5" s="5"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
         <v>5</v>
       </c>
-      <c r="B6" s="8">
+      <c r="B6" s="7">
         <v>1174966078</v>
       </c>
-      <c r="C6" s="8" t="s">
+      <c r="C6" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="D6" s="20"/>
-      <c r="E6" s="16"/>
-      <c r="F6" s="5"/>
+      <c r="D6" s="22"/>
+      <c r="E6" s="18"/>
+      <c r="F6" s="5" t="s">
+        <v>49</v>
+      </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
@@ -872,10 +886,10 @@
       <c r="C7" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D7" s="17" t="s">
+      <c r="D7" s="19" t="s">
         <v>41</v>
       </c>
-      <c r="E7" s="18" t="s">
+      <c r="E7" s="20" t="s">
         <v>44</v>
       </c>
       <c r="F7" s="5"/>
@@ -890,8 +904,8 @@
       <c r="C8" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="D8" s="17"/>
-      <c r="E8" s="19"/>
+      <c r="D8" s="19"/>
+      <c r="E8" s="21"/>
       <c r="F8" s="5" t="s">
         <v>47</v>
       </c>
@@ -906,8 +920,8 @@
       <c r="C9" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D9" s="17"/>
-      <c r="E9" s="19"/>
+      <c r="D9" s="19"/>
+      <c r="E9" s="21"/>
       <c r="F9" s="5" t="s">
         <v>50</v>
       </c>
@@ -922,8 +936,8 @@
       <c r="C10" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D10" s="17"/>
-      <c r="E10" s="19"/>
+      <c r="D10" s="19"/>
+      <c r="E10" s="21"/>
       <c r="F10" s="5"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -936,8 +950,8 @@
       <c r="C11" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="D11" s="17"/>
-      <c r="E11" s="19"/>
+      <c r="D11" s="19"/>
+      <c r="E11" s="21"/>
       <c r="F11" s="5" t="s">
         <v>65</v>
       </c>
@@ -952,8 +966,8 @@
       <c r="C12" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="D12" s="17"/>
-      <c r="E12" s="19"/>
+      <c r="D12" s="19"/>
+      <c r="E12" s="21"/>
       <c r="F12" s="5" t="s">
         <v>65</v>
       </c>
@@ -968,8 +982,8 @@
       <c r="C13" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="D13" s="17"/>
-      <c r="E13" s="19"/>
+      <c r="D13" s="19"/>
+      <c r="E13" s="21"/>
       <c r="F13" s="5" t="s">
         <v>65</v>
       </c>
@@ -984,10 +998,10 @@
       <c r="C14" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D14" s="17" t="s">
+      <c r="D14" s="19" t="s">
         <v>42</v>
       </c>
-      <c r="E14" s="19"/>
+      <c r="E14" s="21"/>
       <c r="F14" s="5"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
@@ -1000,8 +1014,8 @@
       <c r="C15" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="D15" s="17"/>
-      <c r="E15" s="19"/>
+      <c r="D15" s="19"/>
+      <c r="E15" s="21"/>
       <c r="F15" s="5" t="s">
         <v>46</v>
       </c>
@@ -1016,8 +1030,8 @@
       <c r="C16" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="D16" s="17"/>
-      <c r="E16" s="19"/>
+      <c r="D16" s="19"/>
+      <c r="E16" s="21"/>
       <c r="F16" s="5"/>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
@@ -1030,122 +1044,124 @@
       <c r="C17" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D17" s="17"/>
-      <c r="E17" s="19"/>
+      <c r="D17" s="19"/>
+      <c r="E17" s="21"/>
       <c r="F17" s="5"/>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="2">
         <v>17</v>
       </c>
-      <c r="B18" s="1">
+      <c r="B18" s="16">
         <v>1173963048</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D18" s="18" t="s">
+      <c r="D18" s="20" t="s">
         <v>43</v>
       </c>
-      <c r="E18" s="19"/>
+      <c r="E18" s="21"/>
       <c r="F18" s="5"/>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="2">
         <v>18</v>
       </c>
-      <c r="B19" s="1">
+      <c r="B19" s="16">
         <v>1173963049</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D19" s="19"/>
-      <c r="E19" s="19"/>
+      <c r="D19" s="21"/>
+      <c r="E19" s="21"/>
       <c r="F19" s="5"/>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="2">
         <v>19</v>
       </c>
-      <c r="B20" s="1">
+      <c r="B20" s="16">
         <v>1173963050</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D20" s="19"/>
-      <c r="E20" s="19"/>
+      <c r="D20" s="21"/>
+      <c r="E20" s="21"/>
       <c r="F20" s="5"/>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="2">
         <v>20</v>
       </c>
-      <c r="B21" s="1">
+      <c r="B21" s="16">
         <v>1173963051</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D21" s="19"/>
-      <c r="E21" s="19"/>
+      <c r="D21" s="21"/>
+      <c r="E21" s="21"/>
       <c r="F21" s="5"/>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="2">
         <v>21</v>
       </c>
-      <c r="B22" s="8">
+      <c r="B22" s="16">
         <v>1173963052</v>
       </c>
       <c r="C22" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="D22" s="19"/>
-      <c r="E22" s="19"/>
+      <c r="D22" s="21"/>
+      <c r="E22" s="21"/>
       <c r="F22" s="5"/>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="2">
         <v>22</v>
       </c>
-      <c r="B23" s="8">
+      <c r="B23" s="4">
         <v>1173963053</v>
       </c>
-      <c r="C23" s="8" t="s">
+      <c r="C23" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="D23" s="19"/>
-      <c r="E23" s="19"/>
-      <c r="F23" s="5"/>
+      <c r="D23" s="21"/>
+      <c r="E23" s="21"/>
+      <c r="F23" s="5" t="s">
+        <v>49</v>
+      </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="2">
         <v>23</v>
       </c>
-      <c r="B24" s="8">
+      <c r="B24" s="16">
         <v>1173963054</v>
       </c>
       <c r="C24" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="D24" s="19"/>
-      <c r="E24" s="19"/>
+      <c r="D24" s="21"/>
+      <c r="E24" s="21"/>
       <c r="F24" s="5"/>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="2">
         <v>24</v>
       </c>
-      <c r="B25" s="8">
+      <c r="B25" s="16">
         <v>1173963055</v>
       </c>
       <c r="C25" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="D25" s="19"/>
-      <c r="E25" s="19"/>
+      <c r="D25" s="21"/>
+      <c r="E25" s="21"/>
       <c r="F25" s="5"/>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
@@ -1158,8 +1174,8 @@
       <c r="C26" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="D26" s="19"/>
-      <c r="E26" s="19"/>
+      <c r="D26" s="21"/>
+      <c r="E26" s="21"/>
       <c r="F26" s="5" t="s">
         <v>46</v>
       </c>
@@ -1168,56 +1184,56 @@
       <c r="A27" s="2">
         <v>26</v>
       </c>
-      <c r="B27" s="8">
+      <c r="B27" s="16">
         <v>1173963057</v>
       </c>
       <c r="C27" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="D27" s="19"/>
-      <c r="E27" s="19"/>
+      <c r="D27" s="21"/>
+      <c r="E27" s="21"/>
       <c r="F27" s="5"/>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="2">
         <v>27</v>
       </c>
-      <c r="B28" s="8">
+      <c r="B28" s="16">
         <v>1173963058</v>
       </c>
       <c r="C28" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="D28" s="19"/>
-      <c r="E28" s="19"/>
+      <c r="D28" s="21"/>
+      <c r="E28" s="21"/>
       <c r="F28" s="5"/>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="2">
         <v>28</v>
       </c>
-      <c r="B29" s="8">
+      <c r="B29" s="16">
         <v>1173963059</v>
       </c>
       <c r="C29" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="D29" s="19"/>
-      <c r="E29" s="19"/>
+      <c r="D29" s="21"/>
+      <c r="E29" s="21"/>
       <c r="F29" s="5"/>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="2">
         <v>29</v>
       </c>
-      <c r="B30" s="8">
+      <c r="B30" s="16">
         <v>1173963060</v>
       </c>
       <c r="C30" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="D30" s="19"/>
-      <c r="E30" s="19"/>
+      <c r="D30" s="21"/>
+      <c r="E30" s="21"/>
       <c r="F30" s="5"/>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
@@ -1230,8 +1246,8 @@
       <c r="C31" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="D31" s="19"/>
-      <c r="E31" s="19"/>
+      <c r="D31" s="21"/>
+      <c r="E31" s="21"/>
       <c r="F31" s="5" t="s">
         <v>49</v>
       </c>
@@ -1240,42 +1256,42 @@
       <c r="A32" s="2">
         <v>31</v>
       </c>
-      <c r="B32" s="8">
+      <c r="B32" s="16">
         <v>1173963062</v>
       </c>
       <c r="C32" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="D32" s="19"/>
-      <c r="E32" s="19"/>
+      <c r="D32" s="21"/>
+      <c r="E32" s="21"/>
       <c r="F32" s="5"/>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="2">
         <v>32</v>
       </c>
-      <c r="B33" s="8">
+      <c r="B33" s="16">
         <v>1173963063</v>
       </c>
       <c r="C33" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="D33" s="19"/>
-      <c r="E33" s="19"/>
+      <c r="D33" s="21"/>
+      <c r="E33" s="21"/>
       <c r="F33" s="5"/>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="2">
         <v>33</v>
       </c>
-      <c r="B34" s="8">
+      <c r="B34" s="16">
         <v>1173963064</v>
       </c>
       <c r="C34" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="D34" s="19"/>
-      <c r="E34" s="19"/>
+      <c r="D34" s="21"/>
+      <c r="E34" s="21"/>
       <c r="F34" s="5"/>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
@@ -1288,8 +1304,8 @@
       <c r="C35" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="D35" s="19"/>
-      <c r="E35" s="19"/>
+      <c r="D35" s="21"/>
+      <c r="E35" s="21"/>
       <c r="F35" s="5" t="s">
         <v>48</v>
       </c>
@@ -1298,56 +1314,56 @@
       <c r="A36" s="2">
         <v>35</v>
       </c>
-      <c r="B36" s="8">
+      <c r="B36" s="16">
         <v>1173963066</v>
       </c>
       <c r="C36" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="D36" s="19"/>
-      <c r="E36" s="19"/>
+      <c r="D36" s="21"/>
+      <c r="E36" s="21"/>
       <c r="F36" s="5"/>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="2">
         <v>36</v>
       </c>
-      <c r="B37" s="8">
+      <c r="B37" s="16">
         <v>1173963067</v>
       </c>
       <c r="C37" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="D37" s="19"/>
-      <c r="E37" s="19"/>
+      <c r="D37" s="21"/>
+      <c r="E37" s="21"/>
       <c r="F37" s="5"/>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="2">
         <v>37</v>
       </c>
-      <c r="B38" s="8">
+      <c r="B38" s="16">
         <v>1170534788</v>
       </c>
       <c r="C38" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="D38" s="19"/>
-      <c r="E38" s="19"/>
+      <c r="D38" s="21"/>
+      <c r="E38" s="21"/>
       <c r="F38" s="5"/>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="2">
         <v>38</v>
       </c>
-      <c r="B39" s="8">
+      <c r="B39" s="16">
         <v>1170534789</v>
       </c>
       <c r="C39" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="D39" s="19"/>
-      <c r="E39" s="19"/>
+      <c r="D39" s="21"/>
+      <c r="E39" s="21"/>
       <c r="F39" s="5"/>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
@@ -1360,7 +1376,7 @@
       <c r="C40" s="13" t="s">
         <v>56</v>
       </c>
-      <c r="D40" s="19"/>
+      <c r="D40" s="21"/>
       <c r="E40" s="15" t="s">
         <v>55</v>
       </c>
@@ -1378,7 +1394,7 @@
       <c r="C41" s="13" t="s">
         <v>57</v>
       </c>
-      <c r="D41" s="19"/>
+      <c r="D41" s="21"/>
       <c r="E41" s="15" t="s">
         <v>55</v>
       </c>
@@ -1390,13 +1406,13 @@
       <c r="A42" s="2">
         <v>41</v>
       </c>
-      <c r="B42" s="14" t="s">
+      <c r="B42" s="17" t="s">
         <v>54</v>
       </c>
       <c r="C42" s="13" t="s">
         <v>58</v>
       </c>
-      <c r="D42" s="21"/>
+      <c r="D42" s="23"/>
       <c r="E42" s="15" t="s">
         <v>55</v>
       </c>

--- a/5. Other/Danh sách số SIM BH-SX/SIM_Test BH-SX.xlsx
+++ b/5. Other/Danh sách số SIM BH-SX/SIM_Test BH-SX.xlsx
@@ -5,15 +5,16 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNETGPS\VNET\5. Other\Danh sách số SIM BH-SX\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\5. Other\Danh sách số SIM BH-SX\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A21EBACD-0233-4439-BE2C-627CC2C29121}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C1CE3E0-3328-4F8C-B8AE-8692A920CEA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{68255EAF-D8EA-4C2C-BCF7-C24A5FBA6E37}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="1" xr2:uid="{68255EAF-D8EA-4C2C-BCF7-C24A5FBA6E37}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="SIM_TEST" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -25,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="227" uniqueCount="74">
   <si>
     <t>Seri</t>
   </si>
@@ -181,9 +182,6 @@
     <t>Phôi nhựa lỗi lắp sang phôi mobi: 8401210650168374</t>
   </si>
   <si>
-    <t>SIM lỗi phôi</t>
-  </si>
-  <si>
     <t>8984048000969492510</t>
   </si>
   <si>
@@ -233,6 +231,24 @@
   </si>
   <si>
     <t>Tùng đang sử dụng, Viettel(Thịnh Aithings đang giữ)</t>
+  </si>
+  <si>
+    <t>Nhà mạng</t>
+  </si>
+  <si>
+    <t>Chùng loại SIM</t>
+  </si>
+  <si>
+    <t>Vinaphone</t>
+  </si>
+  <si>
+    <t>SIM test CAM</t>
+  </si>
+  <si>
+    <t>SIM test định vị</t>
+  </si>
+  <si>
+    <t>Thịnh Aithings đang giữ</t>
   </si>
 </sst>
 </file>
@@ -280,7 +296,7 @@
       <family val="1"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -314,6 +330,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -382,7 +404,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -429,6 +451,30 @@
     <xf numFmtId="49" fontId="2" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -446,6 +492,18 @@
     </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -805,12 +863,10 @@
       <c r="D2" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="E2" s="18" t="s">
+      <c r="E2" s="26" t="s">
         <v>40</v>
       </c>
-      <c r="F2" s="5" t="s">
-        <v>51</v>
-      </c>
+      <c r="F2" s="5"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="6">
@@ -822,10 +878,10 @@
       <c r="C3" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="D3" s="19" t="s">
+      <c r="D3" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="E3" s="18"/>
+      <c r="E3" s="26"/>
       <c r="F3" s="5" t="s">
         <v>46</v>
       </c>
@@ -840,8 +896,8 @@
       <c r="C4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D4" s="19"/>
-      <c r="E4" s="18"/>
+      <c r="D4" s="27"/>
+      <c r="E4" s="26"/>
       <c r="F4" s="5"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -854,10 +910,10 @@
       <c r="C5" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D5" s="22" t="s">
+      <c r="D5" s="30" t="s">
         <v>43</v>
       </c>
-      <c r="E5" s="18"/>
+      <c r="E5" s="26"/>
       <c r="F5" s="5"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -870,8 +926,8 @@
       <c r="C6" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="D6" s="22"/>
-      <c r="E6" s="18"/>
+      <c r="D6" s="30"/>
+      <c r="E6" s="26"/>
       <c r="F6" s="5" t="s">
         <v>49</v>
       </c>
@@ -886,10 +942,10 @@
       <c r="C7" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D7" s="19" t="s">
+      <c r="D7" s="27" t="s">
         <v>41</v>
       </c>
-      <c r="E7" s="20" t="s">
+      <c r="E7" s="28" t="s">
         <v>44</v>
       </c>
       <c r="F7" s="5"/>
@@ -904,8 +960,8 @@
       <c r="C8" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="D8" s="19"/>
-      <c r="E8" s="21"/>
+      <c r="D8" s="27"/>
+      <c r="E8" s="29"/>
       <c r="F8" s="5" t="s">
         <v>47</v>
       </c>
@@ -920,8 +976,8 @@
       <c r="C9" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D9" s="19"/>
-      <c r="E9" s="21"/>
+      <c r="D9" s="27"/>
+      <c r="E9" s="29"/>
       <c r="F9" s="5" t="s">
         <v>50</v>
       </c>
@@ -936,8 +992,8 @@
       <c r="C10" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D10" s="19"/>
-      <c r="E10" s="21"/>
+      <c r="D10" s="27"/>
+      <c r="E10" s="29"/>
       <c r="F10" s="5"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -945,15 +1001,15 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="D11" s="27"/>
+      <c r="E11" s="29"/>
+      <c r="F11" s="5" t="s">
         <v>64</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="D11" s="19"/>
-      <c r="E11" s="21"/>
-      <c r="F11" s="5" t="s">
-        <v>65</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
@@ -961,15 +1017,15 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="D12" s="19"/>
-      <c r="E12" s="21"/>
+        <v>59</v>
+      </c>
+      <c r="D12" s="27"/>
+      <c r="E12" s="29"/>
       <c r="F12" s="5" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
@@ -977,15 +1033,15 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="D13" s="19"/>
-      <c r="E13" s="21"/>
+        <v>60</v>
+      </c>
+      <c r="D13" s="27"/>
+      <c r="E13" s="29"/>
       <c r="F13" s="5" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
@@ -998,10 +1054,10 @@
       <c r="C14" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D14" s="19" t="s">
+      <c r="D14" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="E14" s="21"/>
+      <c r="E14" s="29"/>
       <c r="F14" s="5"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
@@ -1014,8 +1070,8 @@
       <c r="C15" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="D15" s="19"/>
-      <c r="E15" s="21"/>
+      <c r="D15" s="27"/>
+      <c r="E15" s="29"/>
       <c r="F15" s="5" t="s">
         <v>46</v>
       </c>
@@ -1030,8 +1086,8 @@
       <c r="C16" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="D16" s="19"/>
-      <c r="E16" s="21"/>
+      <c r="D16" s="27"/>
+      <c r="E16" s="29"/>
       <c r="F16" s="5"/>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
@@ -1044,8 +1100,8 @@
       <c r="C17" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D17" s="19"/>
-      <c r="E17" s="21"/>
+      <c r="D17" s="27"/>
+      <c r="E17" s="29"/>
       <c r="F17" s="5"/>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
@@ -1058,10 +1114,10 @@
       <c r="C18" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D18" s="20" t="s">
+      <c r="D18" s="28" t="s">
         <v>43</v>
       </c>
-      <c r="E18" s="21"/>
+      <c r="E18" s="29"/>
       <c r="F18" s="5"/>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
@@ -1074,8 +1130,8 @@
       <c r="C19" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D19" s="21"/>
-      <c r="E19" s="21"/>
+      <c r="D19" s="29"/>
+      <c r="E19" s="29"/>
       <c r="F19" s="5"/>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
@@ -1088,8 +1144,8 @@
       <c r="C20" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D20" s="21"/>
-      <c r="E20" s="21"/>
+      <c r="D20" s="29"/>
+      <c r="E20" s="29"/>
       <c r="F20" s="5"/>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
@@ -1102,8 +1158,8 @@
       <c r="C21" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D21" s="21"/>
-      <c r="E21" s="21"/>
+      <c r="D21" s="29"/>
+      <c r="E21" s="29"/>
       <c r="F21" s="5"/>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
@@ -1116,8 +1172,8 @@
       <c r="C22" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="D22" s="21"/>
-      <c r="E22" s="21"/>
+      <c r="D22" s="29"/>
+      <c r="E22" s="29"/>
       <c r="F22" s="5"/>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
@@ -1130,8 +1186,8 @@
       <c r="C23" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="D23" s="21"/>
-      <c r="E23" s="21"/>
+      <c r="D23" s="29"/>
+      <c r="E23" s="29"/>
       <c r="F23" s="5" t="s">
         <v>49</v>
       </c>
@@ -1146,8 +1202,8 @@
       <c r="C24" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="D24" s="21"/>
-      <c r="E24" s="21"/>
+      <c r="D24" s="29"/>
+      <c r="E24" s="29"/>
       <c r="F24" s="5"/>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
@@ -1160,8 +1216,8 @@
       <c r="C25" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="D25" s="21"/>
-      <c r="E25" s="21"/>
+      <c r="D25" s="29"/>
+      <c r="E25" s="29"/>
       <c r="F25" s="5"/>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
@@ -1174,8 +1230,8 @@
       <c r="C26" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="D26" s="21"/>
-      <c r="E26" s="21"/>
+      <c r="D26" s="29"/>
+      <c r="E26" s="29"/>
       <c r="F26" s="5" t="s">
         <v>46</v>
       </c>
@@ -1190,8 +1246,8 @@
       <c r="C27" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="D27" s="21"/>
-      <c r="E27" s="21"/>
+      <c r="D27" s="29"/>
+      <c r="E27" s="29"/>
       <c r="F27" s="5"/>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
@@ -1204,8 +1260,8 @@
       <c r="C28" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="D28" s="21"/>
-      <c r="E28" s="21"/>
+      <c r="D28" s="29"/>
+      <c r="E28" s="29"/>
       <c r="F28" s="5"/>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
@@ -1218,8 +1274,8 @@
       <c r="C29" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="D29" s="21"/>
-      <c r="E29" s="21"/>
+      <c r="D29" s="29"/>
+      <c r="E29" s="29"/>
       <c r="F29" s="5"/>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
@@ -1232,8 +1288,8 @@
       <c r="C30" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="D30" s="21"/>
-      <c r="E30" s="21"/>
+      <c r="D30" s="29"/>
+      <c r="E30" s="29"/>
       <c r="F30" s="5"/>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
@@ -1246,8 +1302,8 @@
       <c r="C31" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="D31" s="21"/>
-      <c r="E31" s="21"/>
+      <c r="D31" s="29"/>
+      <c r="E31" s="29"/>
       <c r="F31" s="5" t="s">
         <v>49</v>
       </c>
@@ -1262,8 +1318,8 @@
       <c r="C32" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="D32" s="21"/>
-      <c r="E32" s="21"/>
+      <c r="D32" s="29"/>
+      <c r="E32" s="29"/>
       <c r="F32" s="5"/>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
@@ -1276,8 +1332,8 @@
       <c r="C33" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="D33" s="21"/>
-      <c r="E33" s="21"/>
+      <c r="D33" s="29"/>
+      <c r="E33" s="29"/>
       <c r="F33" s="5"/>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
@@ -1290,8 +1346,8 @@
       <c r="C34" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="D34" s="21"/>
-      <c r="E34" s="21"/>
+      <c r="D34" s="29"/>
+      <c r="E34" s="29"/>
       <c r="F34" s="5"/>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
@@ -1304,8 +1360,8 @@
       <c r="C35" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="D35" s="21"/>
-      <c r="E35" s="21"/>
+      <c r="D35" s="29"/>
+      <c r="E35" s="29"/>
       <c r="F35" s="5" t="s">
         <v>48</v>
       </c>
@@ -1320,8 +1376,8 @@
       <c r="C36" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="D36" s="21"/>
-      <c r="E36" s="21"/>
+      <c r="D36" s="29"/>
+      <c r="E36" s="29"/>
       <c r="F36" s="5"/>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
@@ -1334,8 +1390,8 @@
       <c r="C37" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="D37" s="21"/>
-      <c r="E37" s="21"/>
+      <c r="D37" s="29"/>
+      <c r="E37" s="29"/>
       <c r="F37" s="5"/>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
@@ -1348,8 +1404,8 @@
       <c r="C38" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="D38" s="21"/>
-      <c r="E38" s="21"/>
+      <c r="D38" s="29"/>
+      <c r="E38" s="29"/>
       <c r="F38" s="5"/>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
@@ -1362,8 +1418,8 @@
       <c r="C39" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="D39" s="21"/>
-      <c r="E39" s="21"/>
+      <c r="D39" s="29"/>
+      <c r="E39" s="29"/>
       <c r="F39" s="5"/>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
@@ -1371,17 +1427,17 @@
         <v>39</v>
       </c>
       <c r="B40" s="12" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C40" s="13" t="s">
-        <v>56</v>
-      </c>
-      <c r="D40" s="21"/>
+        <v>55</v>
+      </c>
+      <c r="D40" s="29"/>
       <c r="E40" s="15" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F40" s="11" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
@@ -1389,17 +1445,17 @@
         <v>40</v>
       </c>
       <c r="B41" s="14" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C41" s="13" t="s">
-        <v>57</v>
-      </c>
-      <c r="D41" s="21"/>
+        <v>56</v>
+      </c>
+      <c r="D41" s="29"/>
       <c r="E41" s="15" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F41" s="11" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
@@ -1407,17 +1463,17 @@
         <v>41</v>
       </c>
       <c r="B42" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="C42" s="13" t="s">
+        <v>57</v>
+      </c>
+      <c r="D42" s="31"/>
+      <c r="E42" s="15" t="s">
         <v>54</v>
       </c>
-      <c r="C42" s="13" t="s">
-        <v>58</v>
-      </c>
-      <c r="D42" s="23"/>
-      <c r="E42" s="15" t="s">
-        <v>55</v>
-      </c>
       <c r="F42" s="11" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
   </sheetData>
@@ -1433,4 +1489,854 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="256" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4F2BD792-CCE4-406F-96E2-4768C3AF568E}">
+  <dimension ref="A1:G42"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="6.28515625" style="18" customWidth="1"/>
+    <col min="2" max="2" width="12.42578125" style="18" customWidth="1"/>
+    <col min="3" max="3" width="20.7109375" style="18" customWidth="1"/>
+    <col min="4" max="4" width="16.140625" style="18" customWidth="1"/>
+    <col min="5" max="5" width="13.85546875" style="18" customWidth="1"/>
+    <col min="6" max="6" width="18.7109375" style="18" customWidth="1"/>
+    <col min="7" max="7" width="27.42578125" style="18" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1" s="24" t="s">
+        <v>38</v>
+      </c>
+      <c r="B1" s="24" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="24" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" s="24" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="24" t="s">
+        <v>68</v>
+      </c>
+      <c r="F1" s="24" t="s">
+        <v>69</v>
+      </c>
+      <c r="G1" s="24" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" s="19">
+        <v>1</v>
+      </c>
+      <c r="B2" s="32" t="s">
+        <v>41</v>
+      </c>
+      <c r="C2" s="23">
+        <v>1174221624</v>
+      </c>
+      <c r="D2" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="E2" s="19" t="s">
+        <v>70</v>
+      </c>
+      <c r="F2" s="19" t="s">
+        <v>71</v>
+      </c>
+      <c r="G2" s="19"/>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" s="19">
+        <v>2</v>
+      </c>
+      <c r="B3" s="32"/>
+      <c r="C3" s="1">
+        <v>1173963040</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E3" s="19" t="s">
+        <v>70</v>
+      </c>
+      <c r="F3" s="19" t="s">
+        <v>72</v>
+      </c>
+      <c r="G3" s="19"/>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" s="19">
+        <v>3</v>
+      </c>
+      <c r="B4" s="32"/>
+      <c r="C4" s="7">
+        <v>1173963041</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E4" s="20" t="s">
+        <v>70</v>
+      </c>
+      <c r="F4" s="20" t="s">
+        <v>72</v>
+      </c>
+      <c r="G4" s="20" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" s="19">
+        <v>4</v>
+      </c>
+      <c r="B5" s="32"/>
+      <c r="C5" s="1">
+        <v>1173963042</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E5" s="19" t="s">
+        <v>70</v>
+      </c>
+      <c r="F5" s="19" t="s">
+        <v>72</v>
+      </c>
+      <c r="G5" s="19"/>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" s="19">
+        <v>5</v>
+      </c>
+      <c r="B6" s="32"/>
+      <c r="C6" s="1">
+        <v>1173963043</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E6" s="19" t="s">
+        <v>70</v>
+      </c>
+      <c r="F6" s="19" t="s">
+        <v>72</v>
+      </c>
+      <c r="G6" s="19"/>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" s="19">
+        <v>6</v>
+      </c>
+      <c r="B7" s="32"/>
+      <c r="C7" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E7" s="19" t="s">
+        <v>64</v>
+      </c>
+      <c r="F7" s="19" t="s">
+        <v>72</v>
+      </c>
+      <c r="G7" s="19"/>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" s="19">
+        <v>7</v>
+      </c>
+      <c r="B8" s="32"/>
+      <c r="C8" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="E8" s="19" t="s">
+        <v>64</v>
+      </c>
+      <c r="F8" s="19" t="s">
+        <v>72</v>
+      </c>
+      <c r="G8" s="19"/>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" s="19">
+        <v>8</v>
+      </c>
+      <c r="B9" s="32"/>
+      <c r="C9" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="E9" s="19" t="s">
+        <v>64</v>
+      </c>
+      <c r="F9" s="19" t="s">
+        <v>72</v>
+      </c>
+      <c r="G9" s="19"/>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" s="19">
+        <v>9</v>
+      </c>
+      <c r="B10" s="32"/>
+      <c r="C10" s="21" t="s">
+        <v>51</v>
+      </c>
+      <c r="D10" s="25" t="s">
+        <v>55</v>
+      </c>
+      <c r="E10" s="22" t="s">
+        <v>66</v>
+      </c>
+      <c r="F10" s="22" t="s">
+        <v>71</v>
+      </c>
+      <c r="G10" s="22" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" s="19">
+        <v>10</v>
+      </c>
+      <c r="B11" s="32" t="s">
+        <v>42</v>
+      </c>
+      <c r="C11" s="10">
+        <v>1174221625</v>
+      </c>
+      <c r="D11" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="E11" s="20" t="s">
+        <v>70</v>
+      </c>
+      <c r="F11" s="20" t="s">
+        <v>71</v>
+      </c>
+      <c r="G11" s="20" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12" s="19">
+        <v>11</v>
+      </c>
+      <c r="B12" s="32"/>
+      <c r="C12" s="1">
+        <v>1174221626</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="E12" s="19" t="s">
+        <v>70</v>
+      </c>
+      <c r="F12" s="19" t="s">
+        <v>71</v>
+      </c>
+      <c r="G12" s="19"/>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A13" s="19">
+        <v>12</v>
+      </c>
+      <c r="B13" s="32"/>
+      <c r="C13" s="1">
+        <v>1173963044</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E13" s="19" t="s">
+        <v>70</v>
+      </c>
+      <c r="F13" s="19" t="s">
+        <v>72</v>
+      </c>
+      <c r="G13" s="19"/>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A14" s="19">
+        <v>13</v>
+      </c>
+      <c r="B14" s="32"/>
+      <c r="C14" s="7">
+        <v>1173963045</v>
+      </c>
+      <c r="D14" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="E14" s="20" t="s">
+        <v>70</v>
+      </c>
+      <c r="F14" s="20" t="s">
+        <v>72</v>
+      </c>
+      <c r="G14" s="20" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A15" s="19">
+        <v>14</v>
+      </c>
+      <c r="B15" s="32"/>
+      <c r="C15" s="1">
+        <v>1173963046</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E15" s="19" t="s">
+        <v>70</v>
+      </c>
+      <c r="F15" s="19" t="s">
+        <v>72</v>
+      </c>
+      <c r="G15" s="19"/>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A16" s="19">
+        <v>15</v>
+      </c>
+      <c r="B16" s="32"/>
+      <c r="C16" s="1">
+        <v>1173963047</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E16" s="19" t="s">
+        <v>70</v>
+      </c>
+      <c r="F16" s="19" t="s">
+        <v>72</v>
+      </c>
+      <c r="G16" s="19"/>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A17" s="19">
+        <v>16</v>
+      </c>
+      <c r="B17" s="32"/>
+      <c r="C17" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="E17" s="19" t="s">
+        <v>66</v>
+      </c>
+      <c r="F17" s="19" t="s">
+        <v>71</v>
+      </c>
+      <c r="G17" s="19"/>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A18" s="19">
+        <v>17</v>
+      </c>
+      <c r="B18" s="33" t="s">
+        <v>43</v>
+      </c>
+      <c r="C18" s="8">
+        <v>1174966077</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E18" s="19" t="s">
+        <v>70</v>
+      </c>
+      <c r="F18" s="19" t="s">
+        <v>71</v>
+      </c>
+      <c r="G18" s="19"/>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A19" s="19">
+        <v>18</v>
+      </c>
+      <c r="B19" s="34"/>
+      <c r="C19" s="7">
+        <v>1174966078</v>
+      </c>
+      <c r="D19" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="E19" s="20" t="s">
+        <v>70</v>
+      </c>
+      <c r="F19" s="20" t="s">
+        <v>71</v>
+      </c>
+      <c r="G19" s="20" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A20" s="19">
+        <v>19</v>
+      </c>
+      <c r="B20" s="34"/>
+      <c r="C20" s="8">
+        <v>1173963048</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E20" s="19" t="s">
+        <v>70</v>
+      </c>
+      <c r="F20" s="19" t="s">
+        <v>72</v>
+      </c>
+      <c r="G20" s="19"/>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A21" s="19">
+        <v>20</v>
+      </c>
+      <c r="B21" s="34"/>
+      <c r="C21" s="8">
+        <v>1173963049</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E21" s="19" t="s">
+        <v>70</v>
+      </c>
+      <c r="F21" s="19" t="s">
+        <v>72</v>
+      </c>
+      <c r="G21" s="19"/>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A22" s="19">
+        <v>21</v>
+      </c>
+      <c r="B22" s="34"/>
+      <c r="C22" s="8">
+        <v>1173963050</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E22" s="19" t="s">
+        <v>70</v>
+      </c>
+      <c r="F22" s="19" t="s">
+        <v>72</v>
+      </c>
+      <c r="G22" s="19"/>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A23" s="19">
+        <v>22</v>
+      </c>
+      <c r="B23" s="34"/>
+      <c r="C23" s="8">
+        <v>1173963051</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E23" s="19" t="s">
+        <v>70</v>
+      </c>
+      <c r="F23" s="19" t="s">
+        <v>72</v>
+      </c>
+      <c r="G23" s="19"/>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A24" s="19">
+        <v>23</v>
+      </c>
+      <c r="B24" s="34"/>
+      <c r="C24" s="8">
+        <v>1173963052</v>
+      </c>
+      <c r="D24" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="E24" s="19" t="s">
+        <v>70</v>
+      </c>
+      <c r="F24" s="19" t="s">
+        <v>72</v>
+      </c>
+      <c r="G24" s="19"/>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A25" s="19">
+        <v>24</v>
+      </c>
+      <c r="B25" s="34"/>
+      <c r="C25" s="4">
+        <v>1173963053</v>
+      </c>
+      <c r="D25" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E25" s="20" t="s">
+        <v>70</v>
+      </c>
+      <c r="F25" s="20" t="s">
+        <v>72</v>
+      </c>
+      <c r="G25" s="20" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A26" s="19">
+        <v>25</v>
+      </c>
+      <c r="B26" s="34"/>
+      <c r="C26" s="8">
+        <v>1173963054</v>
+      </c>
+      <c r="D26" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="E26" s="19" t="s">
+        <v>70</v>
+      </c>
+      <c r="F26" s="19" t="s">
+        <v>72</v>
+      </c>
+      <c r="G26" s="19"/>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A27" s="19">
+        <v>26</v>
+      </c>
+      <c r="B27" s="34"/>
+      <c r="C27" s="8">
+        <v>1173963055</v>
+      </c>
+      <c r="D27" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="E27" s="19" t="s">
+        <v>70</v>
+      </c>
+      <c r="F27" s="19" t="s">
+        <v>72</v>
+      </c>
+      <c r="G27" s="19"/>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A28" s="19">
+        <v>27</v>
+      </c>
+      <c r="B28" s="34"/>
+      <c r="C28" s="4">
+        <v>1173963056</v>
+      </c>
+      <c r="D28" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="E28" s="20" t="s">
+        <v>70</v>
+      </c>
+      <c r="F28" s="20" t="s">
+        <v>72</v>
+      </c>
+      <c r="G28" s="20" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A29" s="19">
+        <v>28</v>
+      </c>
+      <c r="B29" s="34"/>
+      <c r="C29" s="8">
+        <v>1173963057</v>
+      </c>
+      <c r="D29" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="E29" s="19" t="s">
+        <v>70</v>
+      </c>
+      <c r="F29" s="19" t="s">
+        <v>72</v>
+      </c>
+      <c r="G29" s="19"/>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A30" s="19">
+        <v>29</v>
+      </c>
+      <c r="B30" s="34"/>
+      <c r="C30" s="8">
+        <v>1173963058</v>
+      </c>
+      <c r="D30" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="E30" s="19" t="s">
+        <v>70</v>
+      </c>
+      <c r="F30" s="19" t="s">
+        <v>72</v>
+      </c>
+      <c r="G30" s="19"/>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A31" s="19">
+        <v>30</v>
+      </c>
+      <c r="B31" s="34"/>
+      <c r="C31" s="8">
+        <v>1173963059</v>
+      </c>
+      <c r="D31" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="E31" s="19" t="s">
+        <v>70</v>
+      </c>
+      <c r="F31" s="19" t="s">
+        <v>72</v>
+      </c>
+      <c r="G31" s="19"/>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A32" s="19">
+        <v>31</v>
+      </c>
+      <c r="B32" s="34"/>
+      <c r="C32" s="8">
+        <v>1173963060</v>
+      </c>
+      <c r="D32" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="E32" s="19" t="s">
+        <v>70</v>
+      </c>
+      <c r="F32" s="19" t="s">
+        <v>72</v>
+      </c>
+      <c r="G32" s="19"/>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A33" s="19">
+        <v>32</v>
+      </c>
+      <c r="B33" s="34"/>
+      <c r="C33" s="7">
+        <v>1173963061</v>
+      </c>
+      <c r="D33" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E33" s="20" t="s">
+        <v>70</v>
+      </c>
+      <c r="F33" s="20" t="s">
+        <v>72</v>
+      </c>
+      <c r="G33" s="20" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A34" s="19">
+        <v>33</v>
+      </c>
+      <c r="B34" s="34"/>
+      <c r="C34" s="8">
+        <v>1173963062</v>
+      </c>
+      <c r="D34" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="E34" s="19" t="s">
+        <v>70</v>
+      </c>
+      <c r="F34" s="19" t="s">
+        <v>72</v>
+      </c>
+      <c r="G34" s="19"/>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A35" s="19">
+        <v>34</v>
+      </c>
+      <c r="B35" s="34"/>
+      <c r="C35" s="8">
+        <v>1173963063</v>
+      </c>
+      <c r="D35" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="E35" s="19" t="s">
+        <v>70</v>
+      </c>
+      <c r="F35" s="19" t="s">
+        <v>72</v>
+      </c>
+      <c r="G35" s="19"/>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A36" s="19">
+        <v>35</v>
+      </c>
+      <c r="B36" s="34"/>
+      <c r="C36" s="8">
+        <v>1173963064</v>
+      </c>
+      <c r="D36" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="E36" s="19" t="s">
+        <v>70</v>
+      </c>
+      <c r="F36" s="19" t="s">
+        <v>72</v>
+      </c>
+      <c r="G36" s="19"/>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A37" s="19">
+        <v>36</v>
+      </c>
+      <c r="B37" s="34"/>
+      <c r="C37" s="4">
+        <v>1173963065</v>
+      </c>
+      <c r="D37" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="E37" s="20" t="s">
+        <v>70</v>
+      </c>
+      <c r="F37" s="20" t="s">
+        <v>72</v>
+      </c>
+      <c r="G37" s="20" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A38" s="19">
+        <v>37</v>
+      </c>
+      <c r="B38" s="34"/>
+      <c r="C38" s="8">
+        <v>1173963066</v>
+      </c>
+      <c r="D38" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="E38" s="19" t="s">
+        <v>70</v>
+      </c>
+      <c r="F38" s="19" t="s">
+        <v>72</v>
+      </c>
+      <c r="G38" s="19"/>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A39" s="19">
+        <v>38</v>
+      </c>
+      <c r="B39" s="34"/>
+      <c r="C39" s="8">
+        <v>1173963067</v>
+      </c>
+      <c r="D39" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E39" s="19" t="s">
+        <v>70</v>
+      </c>
+      <c r="F39" s="19" t="s">
+        <v>72</v>
+      </c>
+      <c r="G39" s="19"/>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A40" s="19">
+        <v>39</v>
+      </c>
+      <c r="B40" s="34"/>
+      <c r="C40" s="8">
+        <v>1170534788</v>
+      </c>
+      <c r="D40" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="E40" s="19" t="s">
+        <v>70</v>
+      </c>
+      <c r="F40" s="19" t="s">
+        <v>72</v>
+      </c>
+      <c r="G40" s="19"/>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A41" s="19">
+        <v>40</v>
+      </c>
+      <c r="B41" s="34"/>
+      <c r="C41" s="8">
+        <v>1170534789</v>
+      </c>
+      <c r="D41" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="E41" s="19" t="s">
+        <v>70</v>
+      </c>
+      <c r="F41" s="19" t="s">
+        <v>72</v>
+      </c>
+      <c r="G41" s="19"/>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A42" s="19">
+        <v>41</v>
+      </c>
+      <c r="B42" s="35"/>
+      <c r="C42" s="23" t="s">
+        <v>53</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="E42" s="19" t="s">
+        <v>66</v>
+      </c>
+      <c r="F42" s="19" t="s">
+        <v>71</v>
+      </c>
+      <c r="G42" s="19"/>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="B2:B10"/>
+    <mergeCell ref="B11:B17"/>
+    <mergeCell ref="B18:B42"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/5. Other/Danh sách số SIM BH-SX/SIM_Test BH-SX.xlsx
+++ b/5. Other/Danh sách số SIM BH-SX/SIM_Test BH-SX.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\5. Other\Danh sách số SIM BH-SX\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNETGPS\VNET\5. Other\Danh sách số SIM BH-SX\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C1CE3E0-3328-4F8C-B8AE-8692A920CEA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B57107D9-1622-4591-AB5B-8FBB03AFE0FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="1" xr2:uid="{68255EAF-D8EA-4C2C-BCF7-C24A5FBA6E37}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{68255EAF-D8EA-4C2C-BCF7-C24A5FBA6E37}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="227" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="243" uniqueCount="82">
   <si>
     <t>Seri</t>
   </si>
@@ -249,6 +249,30 @@
   </si>
   <si>
     <t>Thịnh Aithings đang giữ</t>
+  </si>
+  <si>
+    <t>8401260150905597</t>
+  </si>
+  <si>
+    <t>8401260150910846</t>
+  </si>
+  <si>
+    <t>8401260150905595</t>
+  </si>
+  <si>
+    <t>8401260150905593</t>
+  </si>
+  <si>
+    <t>01211065926</t>
+  </si>
+  <si>
+    <t>01210207642</t>
+  </si>
+  <si>
+    <t>01212631236</t>
+  </si>
+  <si>
+    <t>01211326214</t>
   </si>
 </sst>
 </file>
@@ -497,13 +521,13 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1493,7 +1517,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4F2BD792-CCE4-406F-96E2-4768C3AF568E}">
-  <dimension ref="A1:G42"/>
+  <dimension ref="A1:G46"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="6.28515625" style="18" customWidth="1"/>
@@ -2316,7 +2340,7 @@
       <c r="A42" s="19">
         <v>41</v>
       </c>
-      <c r="B42" s="35"/>
+      <c r="B42" s="34"/>
       <c r="C42" s="23" t="s">
         <v>53</v>
       </c>
@@ -2330,12 +2354,88 @@
         <v>71</v>
       </c>
       <c r="G42" s="19"/>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A43" s="19">
+        <v>42</v>
+      </c>
+      <c r="B43" s="34"/>
+      <c r="C43" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="E43" s="19" t="s">
+        <v>64</v>
+      </c>
+      <c r="F43" s="19" t="s">
+        <v>72</v>
+      </c>
+      <c r="G43" s="19"/>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A44" s="19">
+        <v>43</v>
+      </c>
+      <c r="B44" s="34"/>
+      <c r="C44" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="E44" s="19" t="s">
+        <v>64</v>
+      </c>
+      <c r="F44" s="19" t="s">
+        <v>72</v>
+      </c>
+      <c r="G44" s="19"/>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A45" s="19">
+        <v>44</v>
+      </c>
+      <c r="B45" s="34"/>
+      <c r="C45" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E45" s="19" t="s">
+        <v>64</v>
+      </c>
+      <c r="F45" s="19" t="s">
+        <v>72</v>
+      </c>
+      <c r="G45" s="19"/>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A46" s="19">
+        <v>45</v>
+      </c>
+      <c r="B46" s="35"/>
+      <c r="C46" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="E46" s="19" t="s">
+        <v>64</v>
+      </c>
+      <c r="F46" s="19" t="s">
+        <v>72</v>
+      </c>
+      <c r="G46" s="19"/>
     </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="B2:B10"/>
     <mergeCell ref="B11:B17"/>
-    <mergeCell ref="B18:B42"/>
+    <mergeCell ref="B18:B46"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/5. Other/Danh sách số SIM BH-SX/SIM_Test BH-SX.xlsx
+++ b/5. Other/Danh sách số SIM BH-SX/SIM_Test BH-SX.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\5. Other\Danh sách số SIM BH-SX\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C1CE3E0-3328-4F8C-B8AE-8692A920CEA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53A32F40-F4F7-414E-87CF-2DA6CB817C83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="1" xr2:uid="{68255EAF-D8EA-4C2C-BCF7-C24A5FBA6E37}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{68255EAF-D8EA-4C2C-BCF7-C24A5FBA6E37}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="227" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="78">
   <si>
     <t>Seri</t>
   </si>
@@ -249,6 +249,18 @@
   </si>
   <si>
     <t>Thịnh Aithings đang giữ</t>
+  </si>
+  <si>
+    <t>8401260150910848</t>
+  </si>
+  <si>
+    <t>8401260150910849</t>
+  </si>
+  <si>
+    <t>01212816836</t>
+  </si>
+  <si>
+    <t>01212807436</t>
   </si>
 </sst>
 </file>
@@ -475,6 +487,18 @@
     <xf numFmtId="49" fontId="2" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -492,18 +516,6 @@
     </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -523,9 +535,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -563,7 +575,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -669,7 +681,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -811,7 +823,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -863,7 +875,7 @@
       <c r="D2" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="E2" s="26" t="s">
+      <c r="E2" s="30" t="s">
         <v>40</v>
       </c>
       <c r="F2" s="5"/>
@@ -878,10 +890,10 @@
       <c r="C3" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="D3" s="27" t="s">
+      <c r="D3" s="31" t="s">
         <v>42</v>
       </c>
-      <c r="E3" s="26"/>
+      <c r="E3" s="30"/>
       <c r="F3" s="5" t="s">
         <v>46</v>
       </c>
@@ -896,8 +908,8 @@
       <c r="C4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D4" s="27"/>
-      <c r="E4" s="26"/>
+      <c r="D4" s="31"/>
+      <c r="E4" s="30"/>
       <c r="F4" s="5"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -910,10 +922,10 @@
       <c r="C5" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D5" s="30" t="s">
+      <c r="D5" s="34" t="s">
         <v>43</v>
       </c>
-      <c r="E5" s="26"/>
+      <c r="E5" s="30"/>
       <c r="F5" s="5"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -926,8 +938,8 @@
       <c r="C6" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="D6" s="30"/>
-      <c r="E6" s="26"/>
+      <c r="D6" s="34"/>
+      <c r="E6" s="30"/>
       <c r="F6" s="5" t="s">
         <v>49</v>
       </c>
@@ -942,10 +954,10 @@
       <c r="C7" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D7" s="27" t="s">
+      <c r="D7" s="31" t="s">
         <v>41</v>
       </c>
-      <c r="E7" s="28" t="s">
+      <c r="E7" s="32" t="s">
         <v>44</v>
       </c>
       <c r="F7" s="5"/>
@@ -960,8 +972,8 @@
       <c r="C8" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="D8" s="27"/>
-      <c r="E8" s="29"/>
+      <c r="D8" s="31"/>
+      <c r="E8" s="33"/>
       <c r="F8" s="5" t="s">
         <v>47</v>
       </c>
@@ -976,8 +988,8 @@
       <c r="C9" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D9" s="27"/>
-      <c r="E9" s="29"/>
+      <c r="D9" s="31"/>
+      <c r="E9" s="33"/>
       <c r="F9" s="5" t="s">
         <v>50</v>
       </c>
@@ -992,8 +1004,8 @@
       <c r="C10" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D10" s="27"/>
-      <c r="E10" s="29"/>
+      <c r="D10" s="31"/>
+      <c r="E10" s="33"/>
       <c r="F10" s="5"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -1006,8 +1018,8 @@
       <c r="C11" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="D11" s="27"/>
-      <c r="E11" s="29"/>
+      <c r="D11" s="31"/>
+      <c r="E11" s="33"/>
       <c r="F11" s="5" t="s">
         <v>64</v>
       </c>
@@ -1022,8 +1034,8 @@
       <c r="C12" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="D12" s="27"/>
-      <c r="E12" s="29"/>
+      <c r="D12" s="31"/>
+      <c r="E12" s="33"/>
       <c r="F12" s="5" t="s">
         <v>64</v>
       </c>
@@ -1038,8 +1050,8 @@
       <c r="C13" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="D13" s="27"/>
-      <c r="E13" s="29"/>
+      <c r="D13" s="31"/>
+      <c r="E13" s="33"/>
       <c r="F13" s="5" t="s">
         <v>64</v>
       </c>
@@ -1054,10 +1066,10 @@
       <c r="C14" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D14" s="27" t="s">
+      <c r="D14" s="31" t="s">
         <v>42</v>
       </c>
-      <c r="E14" s="29"/>
+      <c r="E14" s="33"/>
       <c r="F14" s="5"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
@@ -1070,8 +1082,8 @@
       <c r="C15" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="D15" s="27"/>
-      <c r="E15" s="29"/>
+      <c r="D15" s="31"/>
+      <c r="E15" s="33"/>
       <c r="F15" s="5" t="s">
         <v>46</v>
       </c>
@@ -1086,8 +1098,8 @@
       <c r="C16" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="D16" s="27"/>
-      <c r="E16" s="29"/>
+      <c r="D16" s="31"/>
+      <c r="E16" s="33"/>
       <c r="F16" s="5"/>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
@@ -1100,8 +1112,8 @@
       <c r="C17" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D17" s="27"/>
-      <c r="E17" s="29"/>
+      <c r="D17" s="31"/>
+      <c r="E17" s="33"/>
       <c r="F17" s="5"/>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
@@ -1114,10 +1126,10 @@
       <c r="C18" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D18" s="28" t="s">
+      <c r="D18" s="32" t="s">
         <v>43</v>
       </c>
-      <c r="E18" s="29"/>
+      <c r="E18" s="33"/>
       <c r="F18" s="5"/>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
@@ -1130,8 +1142,8 @@
       <c r="C19" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D19" s="29"/>
-      <c r="E19" s="29"/>
+      <c r="D19" s="33"/>
+      <c r="E19" s="33"/>
       <c r="F19" s="5"/>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
@@ -1144,8 +1156,8 @@
       <c r="C20" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D20" s="29"/>
-      <c r="E20" s="29"/>
+      <c r="D20" s="33"/>
+      <c r="E20" s="33"/>
       <c r="F20" s="5"/>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
@@ -1158,8 +1170,8 @@
       <c r="C21" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D21" s="29"/>
-      <c r="E21" s="29"/>
+      <c r="D21" s="33"/>
+      <c r="E21" s="33"/>
       <c r="F21" s="5"/>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
@@ -1172,8 +1184,8 @@
       <c r="C22" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="D22" s="29"/>
-      <c r="E22" s="29"/>
+      <c r="D22" s="33"/>
+      <c r="E22" s="33"/>
       <c r="F22" s="5"/>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
@@ -1186,8 +1198,8 @@
       <c r="C23" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="D23" s="29"/>
-      <c r="E23" s="29"/>
+      <c r="D23" s="33"/>
+      <c r="E23" s="33"/>
       <c r="F23" s="5" t="s">
         <v>49</v>
       </c>
@@ -1202,8 +1214,8 @@
       <c r="C24" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="D24" s="29"/>
-      <c r="E24" s="29"/>
+      <c r="D24" s="33"/>
+      <c r="E24" s="33"/>
       <c r="F24" s="5"/>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
@@ -1216,8 +1228,8 @@
       <c r="C25" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="D25" s="29"/>
-      <c r="E25" s="29"/>
+      <c r="D25" s="33"/>
+      <c r="E25" s="33"/>
       <c r="F25" s="5"/>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
@@ -1230,8 +1242,8 @@
       <c r="C26" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="D26" s="29"/>
-      <c r="E26" s="29"/>
+      <c r="D26" s="33"/>
+      <c r="E26" s="33"/>
       <c r="F26" s="5" t="s">
         <v>46</v>
       </c>
@@ -1246,8 +1258,8 @@
       <c r="C27" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="D27" s="29"/>
-      <c r="E27" s="29"/>
+      <c r="D27" s="33"/>
+      <c r="E27" s="33"/>
       <c r="F27" s="5"/>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
@@ -1260,8 +1272,8 @@
       <c r="C28" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="D28" s="29"/>
-      <c r="E28" s="29"/>
+      <c r="D28" s="33"/>
+      <c r="E28" s="33"/>
       <c r="F28" s="5"/>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
@@ -1274,8 +1286,8 @@
       <c r="C29" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="D29" s="29"/>
-      <c r="E29" s="29"/>
+      <c r="D29" s="33"/>
+      <c r="E29" s="33"/>
       <c r="F29" s="5"/>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
@@ -1288,8 +1300,8 @@
       <c r="C30" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="D30" s="29"/>
-      <c r="E30" s="29"/>
+      <c r="D30" s="33"/>
+      <c r="E30" s="33"/>
       <c r="F30" s="5"/>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
@@ -1302,8 +1314,8 @@
       <c r="C31" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="D31" s="29"/>
-      <c r="E31" s="29"/>
+      <c r="D31" s="33"/>
+      <c r="E31" s="33"/>
       <c r="F31" s="5" t="s">
         <v>49</v>
       </c>
@@ -1318,8 +1330,8 @@
       <c r="C32" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="D32" s="29"/>
-      <c r="E32" s="29"/>
+      <c r="D32" s="33"/>
+      <c r="E32" s="33"/>
       <c r="F32" s="5"/>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
@@ -1332,8 +1344,8 @@
       <c r="C33" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="D33" s="29"/>
-      <c r="E33" s="29"/>
+      <c r="D33" s="33"/>
+      <c r="E33" s="33"/>
       <c r="F33" s="5"/>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
@@ -1346,8 +1358,8 @@
       <c r="C34" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="D34" s="29"/>
-      <c r="E34" s="29"/>
+      <c r="D34" s="33"/>
+      <c r="E34" s="33"/>
       <c r="F34" s="5"/>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
@@ -1360,8 +1372,8 @@
       <c r="C35" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="D35" s="29"/>
-      <c r="E35" s="29"/>
+      <c r="D35" s="33"/>
+      <c r="E35" s="33"/>
       <c r="F35" s="5" t="s">
         <v>48</v>
       </c>
@@ -1376,8 +1388,8 @@
       <c r="C36" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="D36" s="29"/>
-      <c r="E36" s="29"/>
+      <c r="D36" s="33"/>
+      <c r="E36" s="33"/>
       <c r="F36" s="5"/>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
@@ -1390,8 +1402,8 @@
       <c r="C37" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="D37" s="29"/>
-      <c r="E37" s="29"/>
+      <c r="D37" s="33"/>
+      <c r="E37" s="33"/>
       <c r="F37" s="5"/>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
@@ -1404,8 +1416,8 @@
       <c r="C38" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="D38" s="29"/>
-      <c r="E38" s="29"/>
+      <c r="D38" s="33"/>
+      <c r="E38" s="33"/>
       <c r="F38" s="5"/>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
@@ -1418,8 +1430,8 @@
       <c r="C39" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="D39" s="29"/>
-      <c r="E39" s="29"/>
+      <c r="D39" s="33"/>
+      <c r="E39" s="33"/>
       <c r="F39" s="5"/>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
@@ -1432,7 +1444,7 @@
       <c r="C40" s="13" t="s">
         <v>55</v>
       </c>
-      <c r="D40" s="29"/>
+      <c r="D40" s="33"/>
       <c r="E40" s="15" t="s">
         <v>54</v>
       </c>
@@ -1450,7 +1462,7 @@
       <c r="C41" s="13" t="s">
         <v>56</v>
       </c>
-      <c r="D41" s="29"/>
+      <c r="D41" s="33"/>
       <c r="E41" s="15" t="s">
         <v>54</v>
       </c>
@@ -1468,7 +1480,7 @@
       <c r="C42" s="13" t="s">
         <v>57</v>
       </c>
-      <c r="D42" s="31"/>
+      <c r="D42" s="35"/>
       <c r="E42" s="15" t="s">
         <v>54</v>
       </c>
@@ -1493,7 +1505,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4F2BD792-CCE4-406F-96E2-4768C3AF568E}">
-  <dimension ref="A1:G42"/>
+  <dimension ref="A1:G44"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="6.28515625" style="18" customWidth="1"/>
@@ -1532,7 +1544,7 @@
       <c r="A2" s="19">
         <v>1</v>
       </c>
-      <c r="B2" s="32" t="s">
+      <c r="B2" s="26" t="s">
         <v>41</v>
       </c>
       <c r="C2" s="23">
@@ -1553,7 +1565,7 @@
       <c r="A3" s="19">
         <v>2</v>
       </c>
-      <c r="B3" s="32"/>
+      <c r="B3" s="26"/>
       <c r="C3" s="1">
         <v>1173963040</v>
       </c>
@@ -1572,7 +1584,7 @@
       <c r="A4" s="19">
         <v>3</v>
       </c>
-      <c r="B4" s="32"/>
+      <c r="B4" s="26"/>
       <c r="C4" s="7">
         <v>1173963041</v>
       </c>
@@ -1593,7 +1605,7 @@
       <c r="A5" s="19">
         <v>4</v>
       </c>
-      <c r="B5" s="32"/>
+      <c r="B5" s="26"/>
       <c r="C5" s="1">
         <v>1173963042</v>
       </c>
@@ -1612,7 +1624,7 @@
       <c r="A6" s="19">
         <v>5</v>
       </c>
-      <c r="B6" s="32"/>
+      <c r="B6" s="26"/>
       <c r="C6" s="1">
         <v>1173963043</v>
       </c>
@@ -1631,7 +1643,7 @@
       <c r="A7" s="19">
         <v>6</v>
       </c>
-      <c r="B7" s="32"/>
+      <c r="B7" s="26"/>
       <c r="C7" s="1" t="s">
         <v>63</v>
       </c>
@@ -1650,7 +1662,7 @@
       <c r="A8" s="19">
         <v>7</v>
       </c>
-      <c r="B8" s="32"/>
+      <c r="B8" s="26"/>
       <c r="C8" s="1" t="s">
         <v>62</v>
       </c>
@@ -1669,7 +1681,7 @@
       <c r="A9" s="19">
         <v>8</v>
       </c>
-      <c r="B9" s="32"/>
+      <c r="B9" s="26"/>
       <c r="C9" s="1" t="s">
         <v>61</v>
       </c>
@@ -1688,7 +1700,7 @@
       <c r="A10" s="19">
         <v>9</v>
       </c>
-      <c r="B10" s="32"/>
+      <c r="B10" s="26"/>
       <c r="C10" s="21" t="s">
         <v>51</v>
       </c>
@@ -1709,7 +1721,7 @@
       <c r="A11" s="19">
         <v>10</v>
       </c>
-      <c r="B11" s="32" t="s">
+      <c r="B11" s="26" t="s">
         <v>42</v>
       </c>
       <c r="C11" s="10">
@@ -1732,7 +1744,7 @@
       <c r="A12" s="19">
         <v>11</v>
       </c>
-      <c r="B12" s="32"/>
+      <c r="B12" s="26"/>
       <c r="C12" s="1">
         <v>1174221626</v>
       </c>
@@ -1751,7 +1763,7 @@
       <c r="A13" s="19">
         <v>12</v>
       </c>
-      <c r="B13" s="32"/>
+      <c r="B13" s="26"/>
       <c r="C13" s="1">
         <v>1173963044</v>
       </c>
@@ -1770,7 +1782,7 @@
       <c r="A14" s="19">
         <v>13</v>
       </c>
-      <c r="B14" s="32"/>
+      <c r="B14" s="26"/>
       <c r="C14" s="7">
         <v>1173963045</v>
       </c>
@@ -1791,7 +1803,7 @@
       <c r="A15" s="19">
         <v>14</v>
       </c>
-      <c r="B15" s="32"/>
+      <c r="B15" s="26"/>
       <c r="C15" s="1">
         <v>1173963046</v>
       </c>
@@ -1810,7 +1822,7 @@
       <c r="A16" s="19">
         <v>15</v>
       </c>
-      <c r="B16" s="32"/>
+      <c r="B16" s="26"/>
       <c r="C16" s="1">
         <v>1173963047</v>
       </c>
@@ -1829,18 +1841,18 @@
       <c r="A17" s="19">
         <v>16</v>
       </c>
-      <c r="B17" s="32"/>
-      <c r="C17" s="12" t="s">
-        <v>52</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>56</v>
+      <c r="B17" s="26"/>
+      <c r="C17" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>76</v>
       </c>
       <c r="E17" s="19" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="F17" s="19" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="G17" s="19"/>
     </row>
@@ -1848,20 +1860,18 @@
       <c r="A18" s="19">
         <v>17</v>
       </c>
-      <c r="B18" s="33" t="s">
-        <v>43</v>
-      </c>
-      <c r="C18" s="8">
-        <v>1174966077</v>
+      <c r="B18" s="26"/>
+      <c r="C18" s="1" t="s">
+        <v>75</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>6</v>
+        <v>77</v>
       </c>
       <c r="E18" s="19" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="F18" s="19" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="G18" s="19"/>
     </row>
@@ -1869,39 +1879,39 @@
       <c r="A19" s="19">
         <v>18</v>
       </c>
-      <c r="B19" s="34"/>
-      <c r="C19" s="7">
-        <v>1174966078</v>
-      </c>
-      <c r="D19" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="E19" s="20" t="s">
-        <v>70</v>
-      </c>
-      <c r="F19" s="20" t="s">
+      <c r="B19" s="26"/>
+      <c r="C19" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="E19" s="19" t="s">
+        <v>66</v>
+      </c>
+      <c r="F19" s="19" t="s">
         <v>71</v>
       </c>
-      <c r="G19" s="20" t="s">
-        <v>49</v>
-      </c>
+      <c r="G19" s="19"/>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="19">
         <v>19</v>
       </c>
-      <c r="B20" s="34"/>
+      <c r="B20" s="27" t="s">
+        <v>43</v>
+      </c>
       <c r="C20" s="8">
-        <v>1173963048</v>
+        <v>1174966077</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="E20" s="19" t="s">
         <v>70</v>
       </c>
       <c r="F20" s="19" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="G20" s="19"/>
     </row>
@@ -1909,31 +1919,33 @@
       <c r="A21" s="19">
         <v>20</v>
       </c>
-      <c r="B21" s="34"/>
-      <c r="C21" s="8">
-        <v>1173963049</v>
-      </c>
-      <c r="D21" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="E21" s="19" t="s">
-        <v>70</v>
-      </c>
-      <c r="F21" s="19" t="s">
-        <v>72</v>
-      </c>
-      <c r="G21" s="19"/>
+      <c r="B21" s="28"/>
+      <c r="C21" s="7">
+        <v>1174966078</v>
+      </c>
+      <c r="D21" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="E21" s="20" t="s">
+        <v>70</v>
+      </c>
+      <c r="F21" s="20" t="s">
+        <v>71</v>
+      </c>
+      <c r="G21" s="20" t="s">
+        <v>49</v>
+      </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="19">
         <v>21</v>
       </c>
-      <c r="B22" s="34"/>
+      <c r="B22" s="28"/>
       <c r="C22" s="8">
-        <v>1173963050</v>
+        <v>1173963048</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E22" s="19" t="s">
         <v>70</v>
@@ -1947,12 +1959,12 @@
       <c r="A23" s="19">
         <v>22</v>
       </c>
-      <c r="B23" s="34"/>
+      <c r="B23" s="28"/>
       <c r="C23" s="8">
-        <v>1173963051</v>
+        <v>1173963049</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E23" s="19" t="s">
         <v>70</v>
@@ -1966,12 +1978,12 @@
       <c r="A24" s="19">
         <v>23</v>
       </c>
-      <c r="B24" s="34"/>
+      <c r="B24" s="28"/>
       <c r="C24" s="8">
-        <v>1173963052</v>
-      </c>
-      <c r="D24" s="8" t="s">
-        <v>20</v>
+        <v>1173963050</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>18</v>
       </c>
       <c r="E24" s="19" t="s">
         <v>70</v>
@@ -1985,33 +1997,31 @@
       <c r="A25" s="19">
         <v>24</v>
       </c>
-      <c r="B25" s="34"/>
-      <c r="C25" s="4">
-        <v>1173963053</v>
-      </c>
-      <c r="D25" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="E25" s="20" t="s">
-        <v>70</v>
-      </c>
-      <c r="F25" s="20" t="s">
-        <v>72</v>
-      </c>
-      <c r="G25" s="20" t="s">
-        <v>49</v>
-      </c>
+      <c r="B25" s="28"/>
+      <c r="C25" s="8">
+        <v>1173963051</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E25" s="19" t="s">
+        <v>70</v>
+      </c>
+      <c r="F25" s="19" t="s">
+        <v>72</v>
+      </c>
+      <c r="G25" s="19"/>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" s="19">
         <v>25</v>
       </c>
-      <c r="B26" s="34"/>
+      <c r="B26" s="28"/>
       <c r="C26" s="8">
-        <v>1173963054</v>
+        <v>1173963052</v>
       </c>
       <c r="D26" s="8" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E26" s="19" t="s">
         <v>70</v>
@@ -2025,52 +2035,52 @@
       <c r="A27" s="19">
         <v>26</v>
       </c>
-      <c r="B27" s="34"/>
-      <c r="C27" s="8">
-        <v>1173963055</v>
-      </c>
-      <c r="D27" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="E27" s="19" t="s">
-        <v>70</v>
-      </c>
-      <c r="F27" s="19" t="s">
-        <v>72</v>
-      </c>
-      <c r="G27" s="19"/>
+      <c r="B27" s="28"/>
+      <c r="C27" s="4">
+        <v>1173963053</v>
+      </c>
+      <c r="D27" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E27" s="20" t="s">
+        <v>70</v>
+      </c>
+      <c r="F27" s="20" t="s">
+        <v>72</v>
+      </c>
+      <c r="G27" s="20" t="s">
+        <v>49</v>
+      </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" s="19">
         <v>27</v>
       </c>
-      <c r="B28" s="34"/>
-      <c r="C28" s="4">
-        <v>1173963056</v>
-      </c>
-      <c r="D28" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="E28" s="20" t="s">
-        <v>70</v>
-      </c>
-      <c r="F28" s="20" t="s">
-        <v>72</v>
-      </c>
-      <c r="G28" s="20" t="s">
-        <v>46</v>
-      </c>
+      <c r="B28" s="28"/>
+      <c r="C28" s="8">
+        <v>1173963054</v>
+      </c>
+      <c r="D28" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="E28" s="19" t="s">
+        <v>70</v>
+      </c>
+      <c r="F28" s="19" t="s">
+        <v>72</v>
+      </c>
+      <c r="G28" s="19"/>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" s="19">
         <v>28</v>
       </c>
-      <c r="B29" s="34"/>
+      <c r="B29" s="28"/>
       <c r="C29" s="8">
-        <v>1173963057</v>
+        <v>1173963055</v>
       </c>
       <c r="D29" s="8" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="E29" s="19" t="s">
         <v>70</v>
@@ -2084,31 +2094,33 @@
       <c r="A30" s="19">
         <v>29</v>
       </c>
-      <c r="B30" s="34"/>
-      <c r="C30" s="8">
-        <v>1173963058</v>
-      </c>
-      <c r="D30" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="E30" s="19" t="s">
-        <v>70</v>
-      </c>
-      <c r="F30" s="19" t="s">
-        <v>72</v>
-      </c>
-      <c r="G30" s="19"/>
+      <c r="B30" s="28"/>
+      <c r="C30" s="4">
+        <v>1173963056</v>
+      </c>
+      <c r="D30" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="E30" s="20" t="s">
+        <v>70</v>
+      </c>
+      <c r="F30" s="20" t="s">
+        <v>72</v>
+      </c>
+      <c r="G30" s="20" t="s">
+        <v>46</v>
+      </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" s="19">
         <v>30</v>
       </c>
-      <c r="B31" s="34"/>
+      <c r="B31" s="28"/>
       <c r="C31" s="8">
-        <v>1173963059</v>
+        <v>1173963057</v>
       </c>
       <c r="D31" s="8" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E31" s="19" t="s">
         <v>70</v>
@@ -2122,12 +2134,12 @@
       <c r="A32" s="19">
         <v>31</v>
       </c>
-      <c r="B32" s="34"/>
+      <c r="B32" s="28"/>
       <c r="C32" s="8">
-        <v>1173963060</v>
+        <v>1173963058</v>
       </c>
       <c r="D32" s="8" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E32" s="19" t="s">
         <v>70</v>
@@ -2141,33 +2153,31 @@
       <c r="A33" s="19">
         <v>32</v>
       </c>
-      <c r="B33" s="34"/>
-      <c r="C33" s="7">
-        <v>1173963061</v>
-      </c>
-      <c r="D33" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="E33" s="20" t="s">
-        <v>70</v>
-      </c>
-      <c r="F33" s="20" t="s">
-        <v>72</v>
-      </c>
-      <c r="G33" s="20" t="s">
-        <v>49</v>
-      </c>
+      <c r="B33" s="28"/>
+      <c r="C33" s="8">
+        <v>1173963059</v>
+      </c>
+      <c r="D33" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="E33" s="19" t="s">
+        <v>70</v>
+      </c>
+      <c r="F33" s="19" t="s">
+        <v>72</v>
+      </c>
+      <c r="G33" s="19"/>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" s="19">
         <v>33</v>
       </c>
-      <c r="B34" s="34"/>
+      <c r="B34" s="28"/>
       <c r="C34" s="8">
-        <v>1173963062</v>
+        <v>1173963060</v>
       </c>
       <c r="D34" s="8" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E34" s="19" t="s">
         <v>70</v>
@@ -2181,31 +2191,33 @@
       <c r="A35" s="19">
         <v>34</v>
       </c>
-      <c r="B35" s="34"/>
-      <c r="C35" s="8">
-        <v>1173963063</v>
-      </c>
-      <c r="D35" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="E35" s="19" t="s">
-        <v>70</v>
-      </c>
-      <c r="F35" s="19" t="s">
-        <v>72</v>
-      </c>
-      <c r="G35" s="19"/>
+      <c r="B35" s="28"/>
+      <c r="C35" s="7">
+        <v>1173963061</v>
+      </c>
+      <c r="D35" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E35" s="20" t="s">
+        <v>70</v>
+      </c>
+      <c r="F35" s="20" t="s">
+        <v>72</v>
+      </c>
+      <c r="G35" s="20" t="s">
+        <v>49</v>
+      </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" s="19">
         <v>35</v>
       </c>
-      <c r="B36" s="34"/>
+      <c r="B36" s="28"/>
       <c r="C36" s="8">
-        <v>1173963064</v>
+        <v>1173963062</v>
       </c>
       <c r="D36" s="8" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E36" s="19" t="s">
         <v>70</v>
@@ -2219,33 +2231,31 @@
       <c r="A37" s="19">
         <v>36</v>
       </c>
-      <c r="B37" s="34"/>
-      <c r="C37" s="4">
-        <v>1173963065</v>
-      </c>
-      <c r="D37" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="E37" s="20" t="s">
-        <v>70</v>
-      </c>
-      <c r="F37" s="20" t="s">
-        <v>72</v>
-      </c>
-      <c r="G37" s="20" t="s">
-        <v>49</v>
-      </c>
+      <c r="B37" s="28"/>
+      <c r="C37" s="8">
+        <v>1173963063</v>
+      </c>
+      <c r="D37" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="E37" s="19" t="s">
+        <v>70</v>
+      </c>
+      <c r="F37" s="19" t="s">
+        <v>72</v>
+      </c>
+      <c r="G37" s="19"/>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" s="19">
         <v>37</v>
       </c>
-      <c r="B38" s="34"/>
+      <c r="B38" s="28"/>
       <c r="C38" s="8">
-        <v>1173963066</v>
+        <v>1173963064</v>
       </c>
       <c r="D38" s="8" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E38" s="19" t="s">
         <v>70</v>
@@ -2259,31 +2269,33 @@
       <c r="A39" s="19">
         <v>38</v>
       </c>
-      <c r="B39" s="34"/>
-      <c r="C39" s="8">
-        <v>1173963067</v>
-      </c>
-      <c r="D39" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="E39" s="19" t="s">
-        <v>70</v>
-      </c>
-      <c r="F39" s="19" t="s">
-        <v>72</v>
-      </c>
-      <c r="G39" s="19"/>
+      <c r="B39" s="28"/>
+      <c r="C39" s="4">
+        <v>1173963065</v>
+      </c>
+      <c r="D39" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="E39" s="20" t="s">
+        <v>70</v>
+      </c>
+      <c r="F39" s="20" t="s">
+        <v>72</v>
+      </c>
+      <c r="G39" s="20" t="s">
+        <v>49</v>
+      </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" s="19">
         <v>39</v>
       </c>
-      <c r="B40" s="34"/>
+      <c r="B40" s="28"/>
       <c r="C40" s="8">
-        <v>1170534788</v>
+        <v>1173963066</v>
       </c>
       <c r="D40" s="8" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E40" s="19" t="s">
         <v>70</v>
@@ -2297,12 +2309,12 @@
       <c r="A41" s="19">
         <v>40</v>
       </c>
-      <c r="B41" s="34"/>
+      <c r="B41" s="28"/>
       <c r="C41" s="8">
-        <v>1170534789</v>
+        <v>1173963067</v>
       </c>
       <c r="D41" s="8" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E41" s="19" t="s">
         <v>70</v>
@@ -2316,26 +2328,64 @@
       <c r="A42" s="19">
         <v>41</v>
       </c>
-      <c r="B42" s="35"/>
-      <c r="C42" s="23" t="s">
+      <c r="B42" s="28"/>
+      <c r="C42" s="8">
+        <v>1170534788</v>
+      </c>
+      <c r="D42" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="E42" s="19" t="s">
+        <v>70</v>
+      </c>
+      <c r="F42" s="19" t="s">
+        <v>72</v>
+      </c>
+      <c r="G42" s="19"/>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A43" s="19">
+        <v>42</v>
+      </c>
+      <c r="B43" s="28"/>
+      <c r="C43" s="8">
+        <v>1170534789</v>
+      </c>
+      <c r="D43" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="E43" s="19" t="s">
+        <v>70</v>
+      </c>
+      <c r="F43" s="19" t="s">
+        <v>72</v>
+      </c>
+      <c r="G43" s="19"/>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A44" s="19">
+        <v>43</v>
+      </c>
+      <c r="B44" s="29"/>
+      <c r="C44" s="23" t="s">
         <v>53</v>
       </c>
-      <c r="D42" s="2" t="s">
+      <c r="D44" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="E42" s="19" t="s">
+      <c r="E44" s="19" t="s">
         <v>66</v>
       </c>
-      <c r="F42" s="19" t="s">
+      <c r="F44" s="19" t="s">
         <v>71</v>
       </c>
-      <c r="G42" s="19"/>
+      <c r="G44" s="19"/>
     </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="B2:B10"/>
-    <mergeCell ref="B11:B17"/>
-    <mergeCell ref="B18:B42"/>
+    <mergeCell ref="B11:B19"/>
+    <mergeCell ref="B20:B44"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/5. Other/Danh sách số SIM BH-SX/SIM_Test BH-SX.xlsx
+++ b/5. Other/Danh sách số SIM BH-SX/SIM_Test BH-SX.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\5. Other\Danh sách số SIM BH-SX\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNETGPS\VNET\5. Other\Danh sách số SIM BH-SX\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53A32F40-F4F7-414E-87CF-2DA6CB817C83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{466A70A8-4B07-444A-82F1-1846A9E5CA78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{68255EAF-D8EA-4C2C-BCF7-C24A5FBA6E37}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{68255EAF-D8EA-4C2C-BCF7-C24A5FBA6E37}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="78">
   <si>
     <t>Seri</t>
   </si>
@@ -416,7 +416,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -487,6 +487,24 @@
     <xf numFmtId="49" fontId="2" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -499,23 +517,14 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -535,9 +544,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -575,7 +584,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -681,7 +690,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -823,7 +832,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -875,7 +884,7 @@
       <c r="D2" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="E2" s="30" t="s">
+      <c r="E2" s="26" t="s">
         <v>40</v>
       </c>
       <c r="F2" s="5"/>
@@ -890,10 +899,10 @@
       <c r="C3" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="D3" s="31" t="s">
+      <c r="D3" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="E3" s="30"/>
+      <c r="E3" s="26"/>
       <c r="F3" s="5" t="s">
         <v>46</v>
       </c>
@@ -908,8 +917,8 @@
       <c r="C4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D4" s="31"/>
-      <c r="E4" s="30"/>
+      <c r="D4" s="27"/>
+      <c r="E4" s="26"/>
       <c r="F4" s="5"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -922,10 +931,10 @@
       <c r="C5" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D5" s="34" t="s">
+      <c r="D5" s="30" t="s">
         <v>43</v>
       </c>
-      <c r="E5" s="30"/>
+      <c r="E5" s="26"/>
       <c r="F5" s="5"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -938,8 +947,8 @@
       <c r="C6" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="D6" s="34"/>
-      <c r="E6" s="30"/>
+      <c r="D6" s="30"/>
+      <c r="E6" s="26"/>
       <c r="F6" s="5" t="s">
         <v>49</v>
       </c>
@@ -954,10 +963,10 @@
       <c r="C7" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D7" s="31" t="s">
+      <c r="D7" s="27" t="s">
         <v>41</v>
       </c>
-      <c r="E7" s="32" t="s">
+      <c r="E7" s="28" t="s">
         <v>44</v>
       </c>
       <c r="F7" s="5"/>
@@ -972,8 +981,8 @@
       <c r="C8" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="D8" s="31"/>
-      <c r="E8" s="33"/>
+      <c r="D8" s="27"/>
+      <c r="E8" s="29"/>
       <c r="F8" s="5" t="s">
         <v>47</v>
       </c>
@@ -988,8 +997,8 @@
       <c r="C9" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D9" s="31"/>
-      <c r="E9" s="33"/>
+      <c r="D9" s="27"/>
+      <c r="E9" s="29"/>
       <c r="F9" s="5" t="s">
         <v>50</v>
       </c>
@@ -1004,8 +1013,8 @@
       <c r="C10" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D10" s="31"/>
-      <c r="E10" s="33"/>
+      <c r="D10" s="27"/>
+      <c r="E10" s="29"/>
       <c r="F10" s="5"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -1018,8 +1027,8 @@
       <c r="C11" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="D11" s="31"/>
-      <c r="E11" s="33"/>
+      <c r="D11" s="27"/>
+      <c r="E11" s="29"/>
       <c r="F11" s="5" t="s">
         <v>64</v>
       </c>
@@ -1034,8 +1043,8 @@
       <c r="C12" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="D12" s="31"/>
-      <c r="E12" s="33"/>
+      <c r="D12" s="27"/>
+      <c r="E12" s="29"/>
       <c r="F12" s="5" t="s">
         <v>64</v>
       </c>
@@ -1050,8 +1059,8 @@
       <c r="C13" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="D13" s="31"/>
-      <c r="E13" s="33"/>
+      <c r="D13" s="27"/>
+      <c r="E13" s="29"/>
       <c r="F13" s="5" t="s">
         <v>64</v>
       </c>
@@ -1066,10 +1075,10 @@
       <c r="C14" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D14" s="31" t="s">
+      <c r="D14" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="E14" s="33"/>
+      <c r="E14" s="29"/>
       <c r="F14" s="5"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
@@ -1082,8 +1091,8 @@
       <c r="C15" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="D15" s="31"/>
-      <c r="E15" s="33"/>
+      <c r="D15" s="27"/>
+      <c r="E15" s="29"/>
       <c r="F15" s="5" t="s">
         <v>46</v>
       </c>
@@ -1098,8 +1107,8 @@
       <c r="C16" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="D16" s="31"/>
-      <c r="E16" s="33"/>
+      <c r="D16" s="27"/>
+      <c r="E16" s="29"/>
       <c r="F16" s="5"/>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
@@ -1112,8 +1121,8 @@
       <c r="C17" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D17" s="31"/>
-      <c r="E17" s="33"/>
+      <c r="D17" s="27"/>
+      <c r="E17" s="29"/>
       <c r="F17" s="5"/>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
@@ -1126,10 +1135,10 @@
       <c r="C18" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D18" s="32" t="s">
+      <c r="D18" s="28" t="s">
         <v>43</v>
       </c>
-      <c r="E18" s="33"/>
+      <c r="E18" s="29"/>
       <c r="F18" s="5"/>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
@@ -1142,8 +1151,8 @@
       <c r="C19" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D19" s="33"/>
-      <c r="E19" s="33"/>
+      <c r="D19" s="29"/>
+      <c r="E19" s="29"/>
       <c r="F19" s="5"/>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
@@ -1156,8 +1165,8 @@
       <c r="C20" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D20" s="33"/>
-      <c r="E20" s="33"/>
+      <c r="D20" s="29"/>
+      <c r="E20" s="29"/>
       <c r="F20" s="5"/>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
@@ -1170,8 +1179,8 @@
       <c r="C21" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D21" s="33"/>
-      <c r="E21" s="33"/>
+      <c r="D21" s="29"/>
+      <c r="E21" s="29"/>
       <c r="F21" s="5"/>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
@@ -1184,25 +1193,23 @@
       <c r="C22" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="D22" s="33"/>
-      <c r="E22" s="33"/>
+      <c r="D22" s="29"/>
+      <c r="E22" s="29"/>
       <c r="F22" s="5"/>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="2">
         <v>22</v>
       </c>
-      <c r="B23" s="4">
+      <c r="B23" s="36">
         <v>1173963053</v>
       </c>
-      <c r="C23" s="7" t="s">
+      <c r="C23" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="D23" s="33"/>
-      <c r="E23" s="33"/>
-      <c r="F23" s="5" t="s">
-        <v>49</v>
-      </c>
+      <c r="D23" s="29"/>
+      <c r="E23" s="29"/>
+      <c r="F23" s="5"/>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="2">
@@ -1214,8 +1221,8 @@
       <c r="C24" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="D24" s="33"/>
-      <c r="E24" s="33"/>
+      <c r="D24" s="29"/>
+      <c r="E24" s="29"/>
       <c r="F24" s="5"/>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
@@ -1228,8 +1235,8 @@
       <c r="C25" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="D25" s="33"/>
-      <c r="E25" s="33"/>
+      <c r="D25" s="29"/>
+      <c r="E25" s="29"/>
       <c r="F25" s="5"/>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
@@ -1242,8 +1249,8 @@
       <c r="C26" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="D26" s="33"/>
-      <c r="E26" s="33"/>
+      <c r="D26" s="29"/>
+      <c r="E26" s="29"/>
       <c r="F26" s="5" t="s">
         <v>46</v>
       </c>
@@ -1258,8 +1265,8 @@
       <c r="C27" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="D27" s="33"/>
-      <c r="E27" s="33"/>
+      <c r="D27" s="29"/>
+      <c r="E27" s="29"/>
       <c r="F27" s="5"/>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
@@ -1272,8 +1279,8 @@
       <c r="C28" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="D28" s="33"/>
-      <c r="E28" s="33"/>
+      <c r="D28" s="29"/>
+      <c r="E28" s="29"/>
       <c r="F28" s="5"/>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
@@ -1286,8 +1293,8 @@
       <c r="C29" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="D29" s="33"/>
-      <c r="E29" s="33"/>
+      <c r="D29" s="29"/>
+      <c r="E29" s="29"/>
       <c r="F29" s="5"/>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
@@ -1300,8 +1307,8 @@
       <c r="C30" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="D30" s="33"/>
-      <c r="E30" s="33"/>
+      <c r="D30" s="29"/>
+      <c r="E30" s="29"/>
       <c r="F30" s="5"/>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
@@ -1314,8 +1321,8 @@
       <c r="C31" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="D31" s="33"/>
-      <c r="E31" s="33"/>
+      <c r="D31" s="29"/>
+      <c r="E31" s="29"/>
       <c r="F31" s="5" t="s">
         <v>49</v>
       </c>
@@ -1330,8 +1337,8 @@
       <c r="C32" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="D32" s="33"/>
-      <c r="E32" s="33"/>
+      <c r="D32" s="29"/>
+      <c r="E32" s="29"/>
       <c r="F32" s="5"/>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
@@ -1344,8 +1351,8 @@
       <c r="C33" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="D33" s="33"/>
-      <c r="E33" s="33"/>
+      <c r="D33" s="29"/>
+      <c r="E33" s="29"/>
       <c r="F33" s="5"/>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
@@ -1358,8 +1365,8 @@
       <c r="C34" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="D34" s="33"/>
-      <c r="E34" s="33"/>
+      <c r="D34" s="29"/>
+      <c r="E34" s="29"/>
       <c r="F34" s="5"/>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
@@ -1372,8 +1379,8 @@
       <c r="C35" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="D35" s="33"/>
-      <c r="E35" s="33"/>
+      <c r="D35" s="29"/>
+      <c r="E35" s="29"/>
       <c r="F35" s="5" t="s">
         <v>48</v>
       </c>
@@ -1388,8 +1395,8 @@
       <c r="C36" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="D36" s="33"/>
-      <c r="E36" s="33"/>
+      <c r="D36" s="29"/>
+      <c r="E36" s="29"/>
       <c r="F36" s="5"/>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
@@ -1402,8 +1409,8 @@
       <c r="C37" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="D37" s="33"/>
-      <c r="E37" s="33"/>
+      <c r="D37" s="29"/>
+      <c r="E37" s="29"/>
       <c r="F37" s="5"/>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
@@ -1416,8 +1423,8 @@
       <c r="C38" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="D38" s="33"/>
-      <c r="E38" s="33"/>
+      <c r="D38" s="29"/>
+      <c r="E38" s="29"/>
       <c r="F38" s="5"/>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
@@ -1430,8 +1437,8 @@
       <c r="C39" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="D39" s="33"/>
-      <c r="E39" s="33"/>
+      <c r="D39" s="29"/>
+      <c r="E39" s="29"/>
       <c r="F39" s="5"/>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
@@ -1444,7 +1451,7 @@
       <c r="C40" s="13" t="s">
         <v>55</v>
       </c>
-      <c r="D40" s="33"/>
+      <c r="D40" s="29"/>
       <c r="E40" s="15" t="s">
         <v>54</v>
       </c>
@@ -1462,7 +1469,7 @@
       <c r="C41" s="13" t="s">
         <v>56</v>
       </c>
-      <c r="D41" s="33"/>
+      <c r="D41" s="29"/>
       <c r="E41" s="15" t="s">
         <v>54</v>
       </c>
@@ -1480,7 +1487,7 @@
       <c r="C42" s="13" t="s">
         <v>57</v>
       </c>
-      <c r="D42" s="35"/>
+      <c r="D42" s="31"/>
       <c r="E42" s="15" t="s">
         <v>54</v>
       </c>
@@ -1544,7 +1551,7 @@
       <c r="A2" s="19">
         <v>1</v>
       </c>
-      <c r="B2" s="26" t="s">
+      <c r="B2" s="32" t="s">
         <v>41</v>
       </c>
       <c r="C2" s="23">
@@ -1565,7 +1572,7 @@
       <c r="A3" s="19">
         <v>2</v>
       </c>
-      <c r="B3" s="26"/>
+      <c r="B3" s="32"/>
       <c r="C3" s="1">
         <v>1173963040</v>
       </c>
@@ -1584,7 +1591,7 @@
       <c r="A4" s="19">
         <v>3</v>
       </c>
-      <c r="B4" s="26"/>
+      <c r="B4" s="32"/>
       <c r="C4" s="7">
         <v>1173963041</v>
       </c>
@@ -1605,7 +1612,7 @@
       <c r="A5" s="19">
         <v>4</v>
       </c>
-      <c r="B5" s="26"/>
+      <c r="B5" s="32"/>
       <c r="C5" s="1">
         <v>1173963042</v>
       </c>
@@ -1624,7 +1631,7 @@
       <c r="A6" s="19">
         <v>5</v>
       </c>
-      <c r="B6" s="26"/>
+      <c r="B6" s="32"/>
       <c r="C6" s="1">
         <v>1173963043</v>
       </c>
@@ -1643,7 +1650,7 @@
       <c r="A7" s="19">
         <v>6</v>
       </c>
-      <c r="B7" s="26"/>
+      <c r="B7" s="32"/>
       <c r="C7" s="1" t="s">
         <v>63</v>
       </c>
@@ -1662,7 +1669,7 @@
       <c r="A8" s="19">
         <v>7</v>
       </c>
-      <c r="B8" s="26"/>
+      <c r="B8" s="32"/>
       <c r="C8" s="1" t="s">
         <v>62</v>
       </c>
@@ -1681,7 +1688,7 @@
       <c r="A9" s="19">
         <v>8</v>
       </c>
-      <c r="B9" s="26"/>
+      <c r="B9" s="32"/>
       <c r="C9" s="1" t="s">
         <v>61</v>
       </c>
@@ -1700,7 +1707,7 @@
       <c r="A10" s="19">
         <v>9</v>
       </c>
-      <c r="B10" s="26"/>
+      <c r="B10" s="32"/>
       <c r="C10" s="21" t="s">
         <v>51</v>
       </c>
@@ -1721,7 +1728,7 @@
       <c r="A11" s="19">
         <v>10</v>
       </c>
-      <c r="B11" s="26" t="s">
+      <c r="B11" s="32" t="s">
         <v>42</v>
       </c>
       <c r="C11" s="10">
@@ -1744,7 +1751,7 @@
       <c r="A12" s="19">
         <v>11</v>
       </c>
-      <c r="B12" s="26"/>
+      <c r="B12" s="32"/>
       <c r="C12" s="1">
         <v>1174221626</v>
       </c>
@@ -1763,7 +1770,7 @@
       <c r="A13" s="19">
         <v>12</v>
       </c>
-      <c r="B13" s="26"/>
+      <c r="B13" s="32"/>
       <c r="C13" s="1">
         <v>1173963044</v>
       </c>
@@ -1782,7 +1789,7 @@
       <c r="A14" s="19">
         <v>13</v>
       </c>
-      <c r="B14" s="26"/>
+      <c r="B14" s="32"/>
       <c r="C14" s="7">
         <v>1173963045</v>
       </c>
@@ -1803,7 +1810,7 @@
       <c r="A15" s="19">
         <v>14</v>
       </c>
-      <c r="B15" s="26"/>
+      <c r="B15" s="32"/>
       <c r="C15" s="1">
         <v>1173963046</v>
       </c>
@@ -1822,7 +1829,7 @@
       <c r="A16" s="19">
         <v>15</v>
       </c>
-      <c r="B16" s="26"/>
+      <c r="B16" s="32"/>
       <c r="C16" s="1">
         <v>1173963047</v>
       </c>
@@ -1841,7 +1848,7 @@
       <c r="A17" s="19">
         <v>16</v>
       </c>
-      <c r="B17" s="26"/>
+      <c r="B17" s="32"/>
       <c r="C17" s="1" t="s">
         <v>74</v>
       </c>
@@ -1860,7 +1867,7 @@
       <c r="A18" s="19">
         <v>17</v>
       </c>
-      <c r="B18" s="26"/>
+      <c r="B18" s="32"/>
       <c r="C18" s="1" t="s">
         <v>75</v>
       </c>
@@ -1879,7 +1886,7 @@
       <c r="A19" s="19">
         <v>18</v>
       </c>
-      <c r="B19" s="26"/>
+      <c r="B19" s="32"/>
       <c r="C19" s="12" t="s">
         <v>52</v>
       </c>
@@ -1898,7 +1905,7 @@
       <c r="A20" s="19">
         <v>19</v>
       </c>
-      <c r="B20" s="27" t="s">
+      <c r="B20" s="33" t="s">
         <v>43</v>
       </c>
       <c r="C20" s="8">
@@ -1919,7 +1926,7 @@
       <c r="A21" s="19">
         <v>20</v>
       </c>
-      <c r="B21" s="28"/>
+      <c r="B21" s="34"/>
       <c r="C21" s="7">
         <v>1174966078</v>
       </c>
@@ -1940,7 +1947,7 @@
       <c r="A22" s="19">
         <v>21</v>
       </c>
-      <c r="B22" s="28"/>
+      <c r="B22" s="34"/>
       <c r="C22" s="8">
         <v>1173963048</v>
       </c>
@@ -1959,7 +1966,7 @@
       <c r="A23" s="19">
         <v>22</v>
       </c>
-      <c r="B23" s="28"/>
+      <c r="B23" s="34"/>
       <c r="C23" s="8">
         <v>1173963049</v>
       </c>
@@ -1978,7 +1985,7 @@
       <c r="A24" s="19">
         <v>23</v>
       </c>
-      <c r="B24" s="28"/>
+      <c r="B24" s="34"/>
       <c r="C24" s="8">
         <v>1173963050</v>
       </c>
@@ -1997,7 +2004,7 @@
       <c r="A25" s="19">
         <v>24</v>
       </c>
-      <c r="B25" s="28"/>
+      <c r="B25" s="34"/>
       <c r="C25" s="8">
         <v>1173963051</v>
       </c>
@@ -2016,7 +2023,7 @@
       <c r="A26" s="19">
         <v>25</v>
       </c>
-      <c r="B26" s="28"/>
+      <c r="B26" s="34"/>
       <c r="C26" s="8">
         <v>1173963052</v>
       </c>
@@ -2035,28 +2042,26 @@
       <c r="A27" s="19">
         <v>26</v>
       </c>
-      <c r="B27" s="28"/>
-      <c r="C27" s="4">
+      <c r="B27" s="34"/>
+      <c r="C27" s="37">
         <v>1173963053</v>
       </c>
-      <c r="D27" s="7" t="s">
+      <c r="D27" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="E27" s="20" t="s">
-        <v>70</v>
-      </c>
-      <c r="F27" s="20" t="s">
-        <v>72</v>
-      </c>
-      <c r="G27" s="20" t="s">
-        <v>49</v>
-      </c>
+      <c r="E27" s="38" t="s">
+        <v>70</v>
+      </c>
+      <c r="F27" s="38" t="s">
+        <v>72</v>
+      </c>
+      <c r="G27" s="38"/>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" s="19">
         <v>27</v>
       </c>
-      <c r="B28" s="28"/>
+      <c r="B28" s="34"/>
       <c r="C28" s="8">
         <v>1173963054</v>
       </c>
@@ -2075,7 +2080,7 @@
       <c r="A29" s="19">
         <v>28</v>
       </c>
-      <c r="B29" s="28"/>
+      <c r="B29" s="34"/>
       <c r="C29" s="8">
         <v>1173963055</v>
       </c>
@@ -2094,7 +2099,7 @@
       <c r="A30" s="19">
         <v>29</v>
       </c>
-      <c r="B30" s="28"/>
+      <c r="B30" s="34"/>
       <c r="C30" s="4">
         <v>1173963056</v>
       </c>
@@ -2115,7 +2120,7 @@
       <c r="A31" s="19">
         <v>30</v>
       </c>
-      <c r="B31" s="28"/>
+      <c r="B31" s="34"/>
       <c r="C31" s="8">
         <v>1173963057</v>
       </c>
@@ -2134,7 +2139,7 @@
       <c r="A32" s="19">
         <v>31</v>
       </c>
-      <c r="B32" s="28"/>
+      <c r="B32" s="34"/>
       <c r="C32" s="8">
         <v>1173963058</v>
       </c>
@@ -2153,7 +2158,7 @@
       <c r="A33" s="19">
         <v>32</v>
       </c>
-      <c r="B33" s="28"/>
+      <c r="B33" s="34"/>
       <c r="C33" s="8">
         <v>1173963059</v>
       </c>
@@ -2172,7 +2177,7 @@
       <c r="A34" s="19">
         <v>33</v>
       </c>
-      <c r="B34" s="28"/>
+      <c r="B34" s="34"/>
       <c r="C34" s="8">
         <v>1173963060</v>
       </c>
@@ -2191,7 +2196,7 @@
       <c r="A35" s="19">
         <v>34</v>
       </c>
-      <c r="B35" s="28"/>
+      <c r="B35" s="34"/>
       <c r="C35" s="7">
         <v>1173963061</v>
       </c>
@@ -2212,7 +2217,7 @@
       <c r="A36" s="19">
         <v>35</v>
       </c>
-      <c r="B36" s="28"/>
+      <c r="B36" s="34"/>
       <c r="C36" s="8">
         <v>1173963062</v>
       </c>
@@ -2231,7 +2236,7 @@
       <c r="A37" s="19">
         <v>36</v>
       </c>
-      <c r="B37" s="28"/>
+      <c r="B37" s="34"/>
       <c r="C37" s="8">
         <v>1173963063</v>
       </c>
@@ -2250,7 +2255,7 @@
       <c r="A38" s="19">
         <v>37</v>
       </c>
-      <c r="B38" s="28"/>
+      <c r="B38" s="34"/>
       <c r="C38" s="8">
         <v>1173963064</v>
       </c>
@@ -2269,7 +2274,7 @@
       <c r="A39" s="19">
         <v>38</v>
       </c>
-      <c r="B39" s="28"/>
+      <c r="B39" s="34"/>
       <c r="C39" s="4">
         <v>1173963065</v>
       </c>
@@ -2290,7 +2295,7 @@
       <c r="A40" s="19">
         <v>39</v>
       </c>
-      <c r="B40" s="28"/>
+      <c r="B40" s="34"/>
       <c r="C40" s="8">
         <v>1173963066</v>
       </c>
@@ -2309,7 +2314,7 @@
       <c r="A41" s="19">
         <v>40</v>
       </c>
-      <c r="B41" s="28"/>
+      <c r="B41" s="34"/>
       <c r="C41" s="8">
         <v>1173963067</v>
       </c>
@@ -2328,7 +2333,7 @@
       <c r="A42" s="19">
         <v>41</v>
       </c>
-      <c r="B42" s="28"/>
+      <c r="B42" s="34"/>
       <c r="C42" s="8">
         <v>1170534788</v>
       </c>
@@ -2347,7 +2352,7 @@
       <c r="A43" s="19">
         <v>42</v>
       </c>
-      <c r="B43" s="28"/>
+      <c r="B43" s="34"/>
       <c r="C43" s="8">
         <v>1170534789</v>
       </c>
@@ -2366,7 +2371,7 @@
       <c r="A44" s="19">
         <v>43</v>
       </c>
-      <c r="B44" s="29"/>
+      <c r="B44" s="35"/>
       <c r="C44" s="23" t="s">
         <v>53</v>
       </c>

--- a/5. Other/Danh sách số SIM BH-SX/SIM_Test BH-SX.xlsx
+++ b/5. Other/Danh sách số SIM BH-SX/SIM_Test BH-SX.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNETGPS\VNET\5. Other\Danh sách số SIM BH-SX\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{466A70A8-4B07-444A-82F1-1846A9E5CA78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0834EAA6-605D-44F6-A259-ABB122F0451A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{68255EAF-D8EA-4C2C-BCF7-C24A5FBA6E37}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="246" uniqueCount="83">
   <si>
     <t>Seri</t>
   </si>
@@ -261,6 +261,21 @@
   </si>
   <si>
     <t>01212807436</t>
+  </si>
+  <si>
+    <t>8401260150905593</t>
+  </si>
+  <si>
+    <t>8401260150910846</t>
+  </si>
+  <si>
+    <t>8401260150905595</t>
+  </si>
+  <si>
+    <t>8401260150905597</t>
+  </si>
+  <si>
+    <t>đang thiếu</t>
   </si>
 </sst>
 </file>
@@ -487,6 +502,15 @@
     <xf numFmtId="49" fontId="2" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -509,22 +533,13 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -884,7 +899,7 @@
       <c r="D2" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="E2" s="26" t="s">
+      <c r="E2" s="29" t="s">
         <v>40</v>
       </c>
       <c r="F2" s="5"/>
@@ -899,10 +914,10 @@
       <c r="C3" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="D3" s="27" t="s">
+      <c r="D3" s="30" t="s">
         <v>42</v>
       </c>
-      <c r="E3" s="26"/>
+      <c r="E3" s="29"/>
       <c r="F3" s="5" t="s">
         <v>46</v>
       </c>
@@ -917,8 +932,8 @@
       <c r="C4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D4" s="27"/>
-      <c r="E4" s="26"/>
+      <c r="D4" s="30"/>
+      <c r="E4" s="29"/>
       <c r="F4" s="5"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -931,10 +946,10 @@
       <c r="C5" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D5" s="30" t="s">
+      <c r="D5" s="33" t="s">
         <v>43</v>
       </c>
-      <c r="E5" s="26"/>
+      <c r="E5" s="29"/>
       <c r="F5" s="5"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -947,8 +962,8 @@
       <c r="C6" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="D6" s="30"/>
-      <c r="E6" s="26"/>
+      <c r="D6" s="33"/>
+      <c r="E6" s="29"/>
       <c r="F6" s="5" t="s">
         <v>49</v>
       </c>
@@ -963,10 +978,10 @@
       <c r="C7" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D7" s="27" t="s">
+      <c r="D7" s="30" t="s">
         <v>41</v>
       </c>
-      <c r="E7" s="28" t="s">
+      <c r="E7" s="31" t="s">
         <v>44</v>
       </c>
       <c r="F7" s="5"/>
@@ -981,8 +996,8 @@
       <c r="C8" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="D8" s="27"/>
-      <c r="E8" s="29"/>
+      <c r="D8" s="30"/>
+      <c r="E8" s="32"/>
       <c r="F8" s="5" t="s">
         <v>47</v>
       </c>
@@ -997,8 +1012,8 @@
       <c r="C9" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D9" s="27"/>
-      <c r="E9" s="29"/>
+      <c r="D9" s="30"/>
+      <c r="E9" s="32"/>
       <c r="F9" s="5" t="s">
         <v>50</v>
       </c>
@@ -1013,8 +1028,8 @@
       <c r="C10" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D10" s="27"/>
-      <c r="E10" s="29"/>
+      <c r="D10" s="30"/>
+      <c r="E10" s="32"/>
       <c r="F10" s="5"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -1027,8 +1042,8 @@
       <c r="C11" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="D11" s="27"/>
-      <c r="E11" s="29"/>
+      <c r="D11" s="30"/>
+      <c r="E11" s="32"/>
       <c r="F11" s="5" t="s">
         <v>64</v>
       </c>
@@ -1043,8 +1058,8 @@
       <c r="C12" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="D12" s="27"/>
-      <c r="E12" s="29"/>
+      <c r="D12" s="30"/>
+      <c r="E12" s="32"/>
       <c r="F12" s="5" t="s">
         <v>64</v>
       </c>
@@ -1059,8 +1074,8 @@
       <c r="C13" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="D13" s="27"/>
-      <c r="E13" s="29"/>
+      <c r="D13" s="30"/>
+      <c r="E13" s="32"/>
       <c r="F13" s="5" t="s">
         <v>64</v>
       </c>
@@ -1075,10 +1090,10 @@
       <c r="C14" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D14" s="27" t="s">
+      <c r="D14" s="30" t="s">
         <v>42</v>
       </c>
-      <c r="E14" s="29"/>
+      <c r="E14" s="32"/>
       <c r="F14" s="5"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
@@ -1091,8 +1106,8 @@
       <c r="C15" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="D15" s="27"/>
-      <c r="E15" s="29"/>
+      <c r="D15" s="30"/>
+      <c r="E15" s="32"/>
       <c r="F15" s="5" t="s">
         <v>46</v>
       </c>
@@ -1107,8 +1122,8 @@
       <c r="C16" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="D16" s="27"/>
-      <c r="E16" s="29"/>
+      <c r="D16" s="30"/>
+      <c r="E16" s="32"/>
       <c r="F16" s="5"/>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
@@ -1121,8 +1136,8 @@
       <c r="C17" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D17" s="27"/>
-      <c r="E17" s="29"/>
+      <c r="D17" s="30"/>
+      <c r="E17" s="32"/>
       <c r="F17" s="5"/>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
@@ -1135,10 +1150,10 @@
       <c r="C18" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D18" s="28" t="s">
+      <c r="D18" s="31" t="s">
         <v>43</v>
       </c>
-      <c r="E18" s="29"/>
+      <c r="E18" s="32"/>
       <c r="F18" s="5"/>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
@@ -1151,8 +1166,8 @@
       <c r="C19" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D19" s="29"/>
-      <c r="E19" s="29"/>
+      <c r="D19" s="32"/>
+      <c r="E19" s="32"/>
       <c r="F19" s="5"/>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
@@ -1165,8 +1180,8 @@
       <c r="C20" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D20" s="29"/>
-      <c r="E20" s="29"/>
+      <c r="D20" s="32"/>
+      <c r="E20" s="32"/>
       <c r="F20" s="5"/>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
@@ -1179,8 +1194,8 @@
       <c r="C21" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D21" s="29"/>
-      <c r="E21" s="29"/>
+      <c r="D21" s="32"/>
+      <c r="E21" s="32"/>
       <c r="F21" s="5"/>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
@@ -1193,22 +1208,22 @@
       <c r="C22" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="D22" s="29"/>
-      <c r="E22" s="29"/>
+      <c r="D22" s="32"/>
+      <c r="E22" s="32"/>
       <c r="F22" s="5"/>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="2">
         <v>22</v>
       </c>
-      <c r="B23" s="36">
+      <c r="B23" s="26">
         <v>1173963053</v>
       </c>
       <c r="C23" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="D23" s="29"/>
-      <c r="E23" s="29"/>
+      <c r="D23" s="32"/>
+      <c r="E23" s="32"/>
       <c r="F23" s="5"/>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
@@ -1221,8 +1236,8 @@
       <c r="C24" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="D24" s="29"/>
-      <c r="E24" s="29"/>
+      <c r="D24" s="32"/>
+      <c r="E24" s="32"/>
       <c r="F24" s="5"/>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
@@ -1235,8 +1250,8 @@
       <c r="C25" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="D25" s="29"/>
-      <c r="E25" s="29"/>
+      <c r="D25" s="32"/>
+      <c r="E25" s="32"/>
       <c r="F25" s="5"/>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
@@ -1249,8 +1264,8 @@
       <c r="C26" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="D26" s="29"/>
-      <c r="E26" s="29"/>
+      <c r="D26" s="32"/>
+      <c r="E26" s="32"/>
       <c r="F26" s="5" t="s">
         <v>46</v>
       </c>
@@ -1265,8 +1280,8 @@
       <c r="C27" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="D27" s="29"/>
-      <c r="E27" s="29"/>
+      <c r="D27" s="32"/>
+      <c r="E27" s="32"/>
       <c r="F27" s="5"/>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
@@ -1279,8 +1294,8 @@
       <c r="C28" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="D28" s="29"/>
-      <c r="E28" s="29"/>
+      <c r="D28" s="32"/>
+      <c r="E28" s="32"/>
       <c r="F28" s="5"/>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
@@ -1293,8 +1308,8 @@
       <c r="C29" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="D29" s="29"/>
-      <c r="E29" s="29"/>
+      <c r="D29" s="32"/>
+      <c r="E29" s="32"/>
       <c r="F29" s="5"/>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
@@ -1307,8 +1322,8 @@
       <c r="C30" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="D30" s="29"/>
-      <c r="E30" s="29"/>
+      <c r="D30" s="32"/>
+      <c r="E30" s="32"/>
       <c r="F30" s="5"/>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
@@ -1321,8 +1336,8 @@
       <c r="C31" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="D31" s="29"/>
-      <c r="E31" s="29"/>
+      <c r="D31" s="32"/>
+      <c r="E31" s="32"/>
       <c r="F31" s="5" t="s">
         <v>49</v>
       </c>
@@ -1337,8 +1352,8 @@
       <c r="C32" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="D32" s="29"/>
-      <c r="E32" s="29"/>
+      <c r="D32" s="32"/>
+      <c r="E32" s="32"/>
       <c r="F32" s="5"/>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
@@ -1351,8 +1366,8 @@
       <c r="C33" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="D33" s="29"/>
-      <c r="E33" s="29"/>
+      <c r="D33" s="32"/>
+      <c r="E33" s="32"/>
       <c r="F33" s="5"/>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
@@ -1365,8 +1380,8 @@
       <c r="C34" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="D34" s="29"/>
-      <c r="E34" s="29"/>
+      <c r="D34" s="32"/>
+      <c r="E34" s="32"/>
       <c r="F34" s="5"/>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
@@ -1379,8 +1394,8 @@
       <c r="C35" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="D35" s="29"/>
-      <c r="E35" s="29"/>
+      <c r="D35" s="32"/>
+      <c r="E35" s="32"/>
       <c r="F35" s="5" t="s">
         <v>48</v>
       </c>
@@ -1395,8 +1410,8 @@
       <c r="C36" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="D36" s="29"/>
-      <c r="E36" s="29"/>
+      <c r="D36" s="32"/>
+      <c r="E36" s="32"/>
       <c r="F36" s="5"/>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
@@ -1409,8 +1424,8 @@
       <c r="C37" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="D37" s="29"/>
-      <c r="E37" s="29"/>
+      <c r="D37" s="32"/>
+      <c r="E37" s="32"/>
       <c r="F37" s="5"/>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
@@ -1423,8 +1438,8 @@
       <c r="C38" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="D38" s="29"/>
-      <c r="E38" s="29"/>
+      <c r="D38" s="32"/>
+      <c r="E38" s="32"/>
       <c r="F38" s="5"/>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
@@ -1437,8 +1452,8 @@
       <c r="C39" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="D39" s="29"/>
-      <c r="E39" s="29"/>
+      <c r="D39" s="32"/>
+      <c r="E39" s="32"/>
       <c r="F39" s="5"/>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
@@ -1451,7 +1466,7 @@
       <c r="C40" s="13" t="s">
         <v>55</v>
       </c>
-      <c r="D40" s="29"/>
+      <c r="D40" s="32"/>
       <c r="E40" s="15" t="s">
         <v>54</v>
       </c>
@@ -1469,7 +1484,7 @@
       <c r="C41" s="13" t="s">
         <v>56</v>
       </c>
-      <c r="D41" s="29"/>
+      <c r="D41" s="32"/>
       <c r="E41" s="15" t="s">
         <v>54</v>
       </c>
@@ -1487,7 +1502,7 @@
       <c r="C42" s="13" t="s">
         <v>57</v>
       </c>
-      <c r="D42" s="31"/>
+      <c r="D42" s="34"/>
       <c r="E42" s="15" t="s">
         <v>54</v>
       </c>
@@ -1512,7 +1527,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4F2BD792-CCE4-406F-96E2-4768C3AF568E}">
-  <dimension ref="A1:G44"/>
+  <dimension ref="A1:G48"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="6.28515625" style="18" customWidth="1"/>
@@ -1551,7 +1566,7 @@
       <c r="A2" s="19">
         <v>1</v>
       </c>
-      <c r="B2" s="32" t="s">
+      <c r="B2" s="35" t="s">
         <v>41</v>
       </c>
       <c r="C2" s="23">
@@ -1572,7 +1587,7 @@
       <c r="A3" s="19">
         <v>2</v>
       </c>
-      <c r="B3" s="32"/>
+      <c r="B3" s="35"/>
       <c r="C3" s="1">
         <v>1173963040</v>
       </c>
@@ -1591,7 +1606,7 @@
       <c r="A4" s="19">
         <v>3</v>
       </c>
-      <c r="B4" s="32"/>
+      <c r="B4" s="35"/>
       <c r="C4" s="7">
         <v>1173963041</v>
       </c>
@@ -1612,7 +1627,7 @@
       <c r="A5" s="19">
         <v>4</v>
       </c>
-      <c r="B5" s="32"/>
+      <c r="B5" s="35"/>
       <c r="C5" s="1">
         <v>1173963042</v>
       </c>
@@ -1631,7 +1646,7 @@
       <c r="A6" s="19">
         <v>5</v>
       </c>
-      <c r="B6" s="32"/>
+      <c r="B6" s="35"/>
       <c r="C6" s="1">
         <v>1173963043</v>
       </c>
@@ -1650,7 +1665,7 @@
       <c r="A7" s="19">
         <v>6</v>
       </c>
-      <c r="B7" s="32"/>
+      <c r="B7" s="35"/>
       <c r="C7" s="1" t="s">
         <v>63</v>
       </c>
@@ -1669,7 +1684,7 @@
       <c r="A8" s="19">
         <v>7</v>
       </c>
-      <c r="B8" s="32"/>
+      <c r="B8" s="35"/>
       <c r="C8" s="1" t="s">
         <v>62</v>
       </c>
@@ -1688,7 +1703,7 @@
       <c r="A9" s="19">
         <v>8</v>
       </c>
-      <c r="B9" s="32"/>
+      <c r="B9" s="35"/>
       <c r="C9" s="1" t="s">
         <v>61</v>
       </c>
@@ -1707,7 +1722,7 @@
       <c r="A10" s="19">
         <v>9</v>
       </c>
-      <c r="B10" s="32"/>
+      <c r="B10" s="35"/>
       <c r="C10" s="21" t="s">
         <v>51</v>
       </c>
@@ -1728,7 +1743,7 @@
       <c r="A11" s="19">
         <v>10</v>
       </c>
-      <c r="B11" s="32" t="s">
+      <c r="B11" s="35" t="s">
         <v>42</v>
       </c>
       <c r="C11" s="10">
@@ -1751,7 +1766,7 @@
       <c r="A12" s="19">
         <v>11</v>
       </c>
-      <c r="B12" s="32"/>
+      <c r="B12" s="35"/>
       <c r="C12" s="1">
         <v>1174221626</v>
       </c>
@@ -1770,7 +1785,7 @@
       <c r="A13" s="19">
         <v>12</v>
       </c>
-      <c r="B13" s="32"/>
+      <c r="B13" s="35"/>
       <c r="C13" s="1">
         <v>1173963044</v>
       </c>
@@ -1789,7 +1804,7 @@
       <c r="A14" s="19">
         <v>13</v>
       </c>
-      <c r="B14" s="32"/>
+      <c r="B14" s="35"/>
       <c r="C14" s="7">
         <v>1173963045</v>
       </c>
@@ -1810,7 +1825,7 @@
       <c r="A15" s="19">
         <v>14</v>
       </c>
-      <c r="B15" s="32"/>
+      <c r="B15" s="35"/>
       <c r="C15" s="1">
         <v>1173963046</v>
       </c>
@@ -1829,7 +1844,7 @@
       <c r="A16" s="19">
         <v>15</v>
       </c>
-      <c r="B16" s="32"/>
+      <c r="B16" s="35"/>
       <c r="C16" s="1">
         <v>1173963047</v>
       </c>
@@ -1848,7 +1863,7 @@
       <c r="A17" s="19">
         <v>16</v>
       </c>
-      <c r="B17" s="32"/>
+      <c r="B17" s="35"/>
       <c r="C17" s="1" t="s">
         <v>74</v>
       </c>
@@ -1867,7 +1882,7 @@
       <c r="A18" s="19">
         <v>17</v>
       </c>
-      <c r="B18" s="32"/>
+      <c r="B18" s="35"/>
       <c r="C18" s="1" t="s">
         <v>75</v>
       </c>
@@ -1886,7 +1901,7 @@
       <c r="A19" s="19">
         <v>18</v>
       </c>
-      <c r="B19" s="32"/>
+      <c r="B19" s="35"/>
       <c r="C19" s="12" t="s">
         <v>52</v>
       </c>
@@ -1905,7 +1920,7 @@
       <c r="A20" s="19">
         <v>19</v>
       </c>
-      <c r="B20" s="33" t="s">
+      <c r="B20" s="36" t="s">
         <v>43</v>
       </c>
       <c r="C20" s="8">
@@ -1926,7 +1941,7 @@
       <c r="A21" s="19">
         <v>20</v>
       </c>
-      <c r="B21" s="34"/>
+      <c r="B21" s="37"/>
       <c r="C21" s="7">
         <v>1174966078</v>
       </c>
@@ -1947,7 +1962,7 @@
       <c r="A22" s="19">
         <v>21</v>
       </c>
-      <c r="B22" s="34"/>
+      <c r="B22" s="37"/>
       <c r="C22" s="8">
         <v>1173963048</v>
       </c>
@@ -1966,7 +1981,7 @@
       <c r="A23" s="19">
         <v>22</v>
       </c>
-      <c r="B23" s="34"/>
+      <c r="B23" s="37"/>
       <c r="C23" s="8">
         <v>1173963049</v>
       </c>
@@ -1985,7 +2000,7 @@
       <c r="A24" s="19">
         <v>23</v>
       </c>
-      <c r="B24" s="34"/>
+      <c r="B24" s="37"/>
       <c r="C24" s="8">
         <v>1173963050</v>
       </c>
@@ -2004,7 +2019,7 @@
       <c r="A25" s="19">
         <v>24</v>
       </c>
-      <c r="B25" s="34"/>
+      <c r="B25" s="37"/>
       <c r="C25" s="8">
         <v>1173963051</v>
       </c>
@@ -2023,7 +2038,7 @@
       <c r="A26" s="19">
         <v>25</v>
       </c>
-      <c r="B26" s="34"/>
+      <c r="B26" s="37"/>
       <c r="C26" s="8">
         <v>1173963052</v>
       </c>
@@ -2042,26 +2057,26 @@
       <c r="A27" s="19">
         <v>26</v>
       </c>
-      <c r="B27" s="34"/>
-      <c r="C27" s="37">
+      <c r="B27" s="37"/>
+      <c r="C27" s="27">
         <v>1173963053</v>
       </c>
       <c r="D27" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="E27" s="38" t="s">
-        <v>70</v>
-      </c>
-      <c r="F27" s="38" t="s">
-        <v>72</v>
-      </c>
-      <c r="G27" s="38"/>
+      <c r="E27" s="28" t="s">
+        <v>70</v>
+      </c>
+      <c r="F27" s="28" t="s">
+        <v>72</v>
+      </c>
+      <c r="G27" s="28"/>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" s="19">
         <v>27</v>
       </c>
-      <c r="B28" s="34"/>
+      <c r="B28" s="37"/>
       <c r="C28" s="8">
         <v>1173963054</v>
       </c>
@@ -2080,7 +2095,7 @@
       <c r="A29" s="19">
         <v>28</v>
       </c>
-      <c r="B29" s="34"/>
+      <c r="B29" s="37"/>
       <c r="C29" s="8">
         <v>1173963055</v>
       </c>
@@ -2099,7 +2114,7 @@
       <c r="A30" s="19">
         <v>29</v>
       </c>
-      <c r="B30" s="34"/>
+      <c r="B30" s="37"/>
       <c r="C30" s="4">
         <v>1173963056</v>
       </c>
@@ -2120,7 +2135,7 @@
       <c r="A31" s="19">
         <v>30</v>
       </c>
-      <c r="B31" s="34"/>
+      <c r="B31" s="37"/>
       <c r="C31" s="8">
         <v>1173963057</v>
       </c>
@@ -2139,7 +2154,7 @@
       <c r="A32" s="19">
         <v>31</v>
       </c>
-      <c r="B32" s="34"/>
+      <c r="B32" s="37"/>
       <c r="C32" s="8">
         <v>1173963058</v>
       </c>
@@ -2158,7 +2173,7 @@
       <c r="A33" s="19">
         <v>32</v>
       </c>
-      <c r="B33" s="34"/>
+      <c r="B33" s="37"/>
       <c r="C33" s="8">
         <v>1173963059</v>
       </c>
@@ -2177,7 +2192,7 @@
       <c r="A34" s="19">
         <v>33</v>
       </c>
-      <c r="B34" s="34"/>
+      <c r="B34" s="37"/>
       <c r="C34" s="8">
         <v>1173963060</v>
       </c>
@@ -2196,7 +2211,7 @@
       <c r="A35" s="19">
         <v>34</v>
       </c>
-      <c r="B35" s="34"/>
+      <c r="B35" s="37"/>
       <c r="C35" s="7">
         <v>1173963061</v>
       </c>
@@ -2217,7 +2232,7 @@
       <c r="A36" s="19">
         <v>35</v>
       </c>
-      <c r="B36" s="34"/>
+      <c r="B36" s="37"/>
       <c r="C36" s="8">
         <v>1173963062</v>
       </c>
@@ -2236,7 +2251,7 @@
       <c r="A37" s="19">
         <v>36</v>
       </c>
-      <c r="B37" s="34"/>
+      <c r="B37" s="37"/>
       <c r="C37" s="8">
         <v>1173963063</v>
       </c>
@@ -2255,7 +2270,7 @@
       <c r="A38" s="19">
         <v>37</v>
       </c>
-      <c r="B38" s="34"/>
+      <c r="B38" s="37"/>
       <c r="C38" s="8">
         <v>1173963064</v>
       </c>
@@ -2274,7 +2289,7 @@
       <c r="A39" s="19">
         <v>38</v>
       </c>
-      <c r="B39" s="34"/>
+      <c r="B39" s="37"/>
       <c r="C39" s="4">
         <v>1173963065</v>
       </c>
@@ -2295,7 +2310,7 @@
       <c r="A40" s="19">
         <v>39</v>
       </c>
-      <c r="B40" s="34"/>
+      <c r="B40" s="37"/>
       <c r="C40" s="8">
         <v>1173963066</v>
       </c>
@@ -2314,7 +2329,7 @@
       <c r="A41" s="19">
         <v>40</v>
       </c>
-      <c r="B41" s="34"/>
+      <c r="B41" s="37"/>
       <c r="C41" s="8">
         <v>1173963067</v>
       </c>
@@ -2333,7 +2348,7 @@
       <c r="A42" s="19">
         <v>41</v>
       </c>
-      <c r="B42" s="34"/>
+      <c r="B42" s="37"/>
       <c r="C42" s="8">
         <v>1170534788</v>
       </c>
@@ -2352,7 +2367,7 @@
       <c r="A43" s="19">
         <v>42</v>
       </c>
-      <c r="B43" s="34"/>
+      <c r="B43" s="37"/>
       <c r="C43" s="8">
         <v>1170534789</v>
       </c>
@@ -2371,7 +2386,7 @@
       <c r="A44" s="19">
         <v>43</v>
       </c>
-      <c r="B44" s="35"/>
+      <c r="B44" s="37"/>
       <c r="C44" s="23" t="s">
         <v>53</v>
       </c>
@@ -2385,12 +2400,82 @@
         <v>71</v>
       </c>
       <c r="G44" s="19"/>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A45" s="19"/>
+      <c r="B45" s="37"/>
+      <c r="C45" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="D45" s="19">
+        <v>1211326214</v>
+      </c>
+      <c r="E45" s="19" t="s">
+        <v>64</v>
+      </c>
+      <c r="F45" s="19" t="s">
+        <v>72</v>
+      </c>
+      <c r="G45" s="19" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A46" s="19"/>
+      <c r="B46" s="37"/>
+      <c r="C46" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="D46" s="19">
+        <v>1212631236</v>
+      </c>
+      <c r="E46" s="19" t="s">
+        <v>64</v>
+      </c>
+      <c r="F46" s="19" t="s">
+        <v>72</v>
+      </c>
+      <c r="G46" s="19"/>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A47" s="19"/>
+      <c r="B47" s="37"/>
+      <c r="C47" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="D47" s="19">
+        <v>1210207642</v>
+      </c>
+      <c r="E47" s="19" t="s">
+        <v>64</v>
+      </c>
+      <c r="F47" s="19" t="s">
+        <v>72</v>
+      </c>
+      <c r="G47" s="19"/>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A48" s="19"/>
+      <c r="B48" s="38"/>
+      <c r="C48" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="D48" s="19">
+        <v>1211065926</v>
+      </c>
+      <c r="E48" s="19" t="s">
+        <v>64</v>
+      </c>
+      <c r="F48" s="19" t="s">
+        <v>72</v>
+      </c>
+      <c r="G48" s="19"/>
     </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="B2:B10"/>
     <mergeCell ref="B11:B19"/>
-    <mergeCell ref="B20:B44"/>
+    <mergeCell ref="B20:B48"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/5. Other/Danh sách số SIM BH-SX/SIM_Test BH-SX.xlsx
+++ b/5. Other/Danh sách số SIM BH-SX/SIM_Test BH-SX.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNETGPS\VNET\5. Other\Danh sách số SIM BH-SX\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\5. Other\Danh sách số SIM BH-SX\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0834EAA6-605D-44F6-A259-ABB122F0451A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCCEBD0A-BDA6-4AC9-8D30-3653788507CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{68255EAF-D8EA-4C2C-BCF7-C24A5FBA6E37}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{68255EAF-D8EA-4C2C-BCF7-C24A5FBA6E37}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="246" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="83">
   <si>
     <t>Seri</t>
   </si>
@@ -511,6 +511,18 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -527,18 +539,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -559,9 +559,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -599,7 +599,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -705,7 +705,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -847,7 +847,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -899,7 +899,7 @@
       <c r="D2" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="E2" s="29" t="s">
+      <c r="E2" s="33" t="s">
         <v>40</v>
       </c>
       <c r="F2" s="5"/>
@@ -914,10 +914,10 @@
       <c r="C3" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="D3" s="30" t="s">
+      <c r="D3" s="34" t="s">
         <v>42</v>
       </c>
-      <c r="E3" s="29"/>
+      <c r="E3" s="33"/>
       <c r="F3" s="5" t="s">
         <v>46</v>
       </c>
@@ -932,8 +932,8 @@
       <c r="C4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D4" s="30"/>
-      <c r="E4" s="29"/>
+      <c r="D4" s="34"/>
+      <c r="E4" s="33"/>
       <c r="F4" s="5"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -946,10 +946,10 @@
       <c r="C5" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D5" s="33" t="s">
+      <c r="D5" s="37" t="s">
         <v>43</v>
       </c>
-      <c r="E5" s="29"/>
+      <c r="E5" s="33"/>
       <c r="F5" s="5"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -962,8 +962,8 @@
       <c r="C6" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="D6" s="33"/>
-      <c r="E6" s="29"/>
+      <c r="D6" s="37"/>
+      <c r="E6" s="33"/>
       <c r="F6" s="5" t="s">
         <v>49</v>
       </c>
@@ -978,10 +978,10 @@
       <c r="C7" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D7" s="30" t="s">
+      <c r="D7" s="34" t="s">
         <v>41</v>
       </c>
-      <c r="E7" s="31" t="s">
+      <c r="E7" s="35" t="s">
         <v>44</v>
       </c>
       <c r="F7" s="5"/>
@@ -996,8 +996,8 @@
       <c r="C8" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="D8" s="30"/>
-      <c r="E8" s="32"/>
+      <c r="D8" s="34"/>
+      <c r="E8" s="36"/>
       <c r="F8" s="5" t="s">
         <v>47</v>
       </c>
@@ -1012,8 +1012,8 @@
       <c r="C9" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D9" s="30"/>
-      <c r="E9" s="32"/>
+      <c r="D9" s="34"/>
+      <c r="E9" s="36"/>
       <c r="F9" s="5" t="s">
         <v>50</v>
       </c>
@@ -1028,8 +1028,8 @@
       <c r="C10" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D10" s="30"/>
-      <c r="E10" s="32"/>
+      <c r="D10" s="34"/>
+      <c r="E10" s="36"/>
       <c r="F10" s="5"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -1042,8 +1042,8 @@
       <c r="C11" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="D11" s="30"/>
-      <c r="E11" s="32"/>
+      <c r="D11" s="34"/>
+      <c r="E11" s="36"/>
       <c r="F11" s="5" t="s">
         <v>64</v>
       </c>
@@ -1058,8 +1058,8 @@
       <c r="C12" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="D12" s="30"/>
-      <c r="E12" s="32"/>
+      <c r="D12" s="34"/>
+      <c r="E12" s="36"/>
       <c r="F12" s="5" t="s">
         <v>64</v>
       </c>
@@ -1074,8 +1074,8 @@
       <c r="C13" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="D13" s="30"/>
-      <c r="E13" s="32"/>
+      <c r="D13" s="34"/>
+      <c r="E13" s="36"/>
       <c r="F13" s="5" t="s">
         <v>64</v>
       </c>
@@ -1090,10 +1090,10 @@
       <c r="C14" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D14" s="30" t="s">
+      <c r="D14" s="34" t="s">
         <v>42</v>
       </c>
-      <c r="E14" s="32"/>
+      <c r="E14" s="36"/>
       <c r="F14" s="5"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
@@ -1106,8 +1106,8 @@
       <c r="C15" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="D15" s="30"/>
-      <c r="E15" s="32"/>
+      <c r="D15" s="34"/>
+      <c r="E15" s="36"/>
       <c r="F15" s="5" t="s">
         <v>46</v>
       </c>
@@ -1122,8 +1122,8 @@
       <c r="C16" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="D16" s="30"/>
-      <c r="E16" s="32"/>
+      <c r="D16" s="34"/>
+      <c r="E16" s="36"/>
       <c r="F16" s="5"/>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
@@ -1136,8 +1136,8 @@
       <c r="C17" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D17" s="30"/>
-      <c r="E17" s="32"/>
+      <c r="D17" s="34"/>
+      <c r="E17" s="36"/>
       <c r="F17" s="5"/>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
@@ -1150,10 +1150,10 @@
       <c r="C18" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D18" s="31" t="s">
+      <c r="D18" s="35" t="s">
         <v>43</v>
       </c>
-      <c r="E18" s="32"/>
+      <c r="E18" s="36"/>
       <c r="F18" s="5"/>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
@@ -1166,8 +1166,8 @@
       <c r="C19" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D19" s="32"/>
-      <c r="E19" s="32"/>
+      <c r="D19" s="36"/>
+      <c r="E19" s="36"/>
       <c r="F19" s="5"/>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
@@ -1180,8 +1180,8 @@
       <c r="C20" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D20" s="32"/>
-      <c r="E20" s="32"/>
+      <c r="D20" s="36"/>
+      <c r="E20" s="36"/>
       <c r="F20" s="5"/>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
@@ -1194,8 +1194,8 @@
       <c r="C21" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D21" s="32"/>
-      <c r="E21" s="32"/>
+      <c r="D21" s="36"/>
+      <c r="E21" s="36"/>
       <c r="F21" s="5"/>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
@@ -1208,8 +1208,8 @@
       <c r="C22" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="D22" s="32"/>
-      <c r="E22" s="32"/>
+      <c r="D22" s="36"/>
+      <c r="E22" s="36"/>
       <c r="F22" s="5"/>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
@@ -1222,8 +1222,8 @@
       <c r="C23" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="D23" s="32"/>
-      <c r="E23" s="32"/>
+      <c r="D23" s="36"/>
+      <c r="E23" s="36"/>
       <c r="F23" s="5"/>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
@@ -1236,8 +1236,8 @@
       <c r="C24" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="D24" s="32"/>
-      <c r="E24" s="32"/>
+      <c r="D24" s="36"/>
+      <c r="E24" s="36"/>
       <c r="F24" s="5"/>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
@@ -1250,8 +1250,8 @@
       <c r="C25" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="D25" s="32"/>
-      <c r="E25" s="32"/>
+      <c r="D25" s="36"/>
+      <c r="E25" s="36"/>
       <c r="F25" s="5"/>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
@@ -1264,8 +1264,8 @@
       <c r="C26" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="D26" s="32"/>
-      <c r="E26" s="32"/>
+      <c r="D26" s="36"/>
+      <c r="E26" s="36"/>
       <c r="F26" s="5" t="s">
         <v>46</v>
       </c>
@@ -1280,8 +1280,8 @@
       <c r="C27" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="D27" s="32"/>
-      <c r="E27" s="32"/>
+      <c r="D27" s="36"/>
+      <c r="E27" s="36"/>
       <c r="F27" s="5"/>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
@@ -1294,8 +1294,8 @@
       <c r="C28" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="D28" s="32"/>
-      <c r="E28" s="32"/>
+      <c r="D28" s="36"/>
+      <c r="E28" s="36"/>
       <c r="F28" s="5"/>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
@@ -1308,8 +1308,8 @@
       <c r="C29" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="D29" s="32"/>
-      <c r="E29" s="32"/>
+      <c r="D29" s="36"/>
+      <c r="E29" s="36"/>
       <c r="F29" s="5"/>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
@@ -1322,8 +1322,8 @@
       <c r="C30" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="D30" s="32"/>
-      <c r="E30" s="32"/>
+      <c r="D30" s="36"/>
+      <c r="E30" s="36"/>
       <c r="F30" s="5"/>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
@@ -1336,8 +1336,8 @@
       <c r="C31" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="D31" s="32"/>
-      <c r="E31" s="32"/>
+      <c r="D31" s="36"/>
+      <c r="E31" s="36"/>
       <c r="F31" s="5" t="s">
         <v>49</v>
       </c>
@@ -1352,8 +1352,8 @@
       <c r="C32" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="D32" s="32"/>
-      <c r="E32" s="32"/>
+      <c r="D32" s="36"/>
+      <c r="E32" s="36"/>
       <c r="F32" s="5"/>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
@@ -1366,8 +1366,8 @@
       <c r="C33" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="D33" s="32"/>
-      <c r="E33" s="32"/>
+      <c r="D33" s="36"/>
+      <c r="E33" s="36"/>
       <c r="F33" s="5"/>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
@@ -1380,8 +1380,8 @@
       <c r="C34" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="D34" s="32"/>
-      <c r="E34" s="32"/>
+      <c r="D34" s="36"/>
+      <c r="E34" s="36"/>
       <c r="F34" s="5"/>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
@@ -1394,8 +1394,8 @@
       <c r="C35" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="D35" s="32"/>
-      <c r="E35" s="32"/>
+      <c r="D35" s="36"/>
+      <c r="E35" s="36"/>
       <c r="F35" s="5" t="s">
         <v>48</v>
       </c>
@@ -1410,8 +1410,8 @@
       <c r="C36" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="D36" s="32"/>
-      <c r="E36" s="32"/>
+      <c r="D36" s="36"/>
+      <c r="E36" s="36"/>
       <c r="F36" s="5"/>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
@@ -1424,8 +1424,8 @@
       <c r="C37" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="D37" s="32"/>
-      <c r="E37" s="32"/>
+      <c r="D37" s="36"/>
+      <c r="E37" s="36"/>
       <c r="F37" s="5"/>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
@@ -1438,8 +1438,8 @@
       <c r="C38" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="D38" s="32"/>
-      <c r="E38" s="32"/>
+      <c r="D38" s="36"/>
+      <c r="E38" s="36"/>
       <c r="F38" s="5"/>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
@@ -1452,8 +1452,8 @@
       <c r="C39" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="D39" s="32"/>
-      <c r="E39" s="32"/>
+      <c r="D39" s="36"/>
+      <c r="E39" s="36"/>
       <c r="F39" s="5"/>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
@@ -1466,7 +1466,7 @@
       <c r="C40" s="13" t="s">
         <v>55</v>
       </c>
-      <c r="D40" s="32"/>
+      <c r="D40" s="36"/>
       <c r="E40" s="15" t="s">
         <v>54</v>
       </c>
@@ -1484,7 +1484,7 @@
       <c r="C41" s="13" t="s">
         <v>56</v>
       </c>
-      <c r="D41" s="32"/>
+      <c r="D41" s="36"/>
       <c r="E41" s="15" t="s">
         <v>54</v>
       </c>
@@ -1502,7 +1502,7 @@
       <c r="C42" s="13" t="s">
         <v>57</v>
       </c>
-      <c r="D42" s="34"/>
+      <c r="D42" s="38"/>
       <c r="E42" s="15" t="s">
         <v>54</v>
       </c>
@@ -1566,7 +1566,7 @@
       <c r="A2" s="19">
         <v>1</v>
       </c>
-      <c r="B2" s="35" t="s">
+      <c r="B2" s="29" t="s">
         <v>41</v>
       </c>
       <c r="C2" s="23">
@@ -1587,7 +1587,7 @@
       <c r="A3" s="19">
         <v>2</v>
       </c>
-      <c r="B3" s="35"/>
+      <c r="B3" s="29"/>
       <c r="C3" s="1">
         <v>1173963040</v>
       </c>
@@ -1606,7 +1606,7 @@
       <c r="A4" s="19">
         <v>3</v>
       </c>
-      <c r="B4" s="35"/>
+      <c r="B4" s="29"/>
       <c r="C4" s="7">
         <v>1173963041</v>
       </c>
@@ -1627,7 +1627,7 @@
       <c r="A5" s="19">
         <v>4</v>
       </c>
-      <c r="B5" s="35"/>
+      <c r="B5" s="29"/>
       <c r="C5" s="1">
         <v>1173963042</v>
       </c>
@@ -1646,7 +1646,7 @@
       <c r="A6" s="19">
         <v>5</v>
       </c>
-      <c r="B6" s="35"/>
+      <c r="B6" s="29"/>
       <c r="C6" s="1">
         <v>1173963043</v>
       </c>
@@ -1665,7 +1665,7 @@
       <c r="A7" s="19">
         <v>6</v>
       </c>
-      <c r="B7" s="35"/>
+      <c r="B7" s="29"/>
       <c r="C7" s="1" t="s">
         <v>63</v>
       </c>
@@ -1684,7 +1684,7 @@
       <c r="A8" s="19">
         <v>7</v>
       </c>
-      <c r="B8" s="35"/>
+      <c r="B8" s="29"/>
       <c r="C8" s="1" t="s">
         <v>62</v>
       </c>
@@ -1703,7 +1703,7 @@
       <c r="A9" s="19">
         <v>8</v>
       </c>
-      <c r="B9" s="35"/>
+      <c r="B9" s="29"/>
       <c r="C9" s="1" t="s">
         <v>61</v>
       </c>
@@ -1722,7 +1722,7 @@
       <c r="A10" s="19">
         <v>9</v>
       </c>
-      <c r="B10" s="35"/>
+      <c r="B10" s="29"/>
       <c r="C10" s="21" t="s">
         <v>51</v>
       </c>
@@ -1743,7 +1743,7 @@
       <c r="A11" s="19">
         <v>10</v>
       </c>
-      <c r="B11" s="35" t="s">
+      <c r="B11" s="29" t="s">
         <v>42</v>
       </c>
       <c r="C11" s="10">
@@ -1766,8 +1766,8 @@
       <c r="A12" s="19">
         <v>11</v>
       </c>
-      <c r="B12" s="35"/>
-      <c r="C12" s="1">
+      <c r="B12" s="29"/>
+      <c r="C12" s="8">
         <v>1174221626</v>
       </c>
       <c r="D12" s="1" t="s">
@@ -1785,26 +1785,28 @@
       <c r="A13" s="19">
         <v>12</v>
       </c>
-      <c r="B13" s="35"/>
-      <c r="C13" s="1">
+      <c r="B13" s="29"/>
+      <c r="C13" s="10">
         <v>1173963044</v>
       </c>
-      <c r="D13" s="1" t="s">
+      <c r="D13" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="E13" s="19" t="s">
-        <v>70</v>
-      </c>
-      <c r="F13" s="19" t="s">
-        <v>72</v>
-      </c>
-      <c r="G13" s="19"/>
+      <c r="E13" s="20" t="s">
+        <v>70</v>
+      </c>
+      <c r="F13" s="20" t="s">
+        <v>72</v>
+      </c>
+      <c r="G13" s="20" t="s">
+        <v>49</v>
+      </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="19">
         <v>13</v>
       </c>
-      <c r="B14" s="35"/>
+      <c r="B14" s="29"/>
       <c r="C14" s="7">
         <v>1173963045</v>
       </c>
@@ -1825,8 +1827,8 @@
       <c r="A15" s="19">
         <v>14</v>
       </c>
-      <c r="B15" s="35"/>
-      <c r="C15" s="1">
+      <c r="B15" s="29"/>
+      <c r="C15" s="8">
         <v>1173963046</v>
       </c>
       <c r="D15" s="1" t="s">
@@ -1844,8 +1846,8 @@
       <c r="A16" s="19">
         <v>15</v>
       </c>
-      <c r="B16" s="35"/>
-      <c r="C16" s="1">
+      <c r="B16" s="29"/>
+      <c r="C16" s="8">
         <v>1173963047</v>
       </c>
       <c r="D16" s="1" t="s">
@@ -1863,8 +1865,8 @@
       <c r="A17" s="19">
         <v>16</v>
       </c>
-      <c r="B17" s="35"/>
-      <c r="C17" s="1" t="s">
+      <c r="B17" s="29"/>
+      <c r="C17" s="8" t="s">
         <v>74</v>
       </c>
       <c r="D17" s="1" t="s">
@@ -1882,8 +1884,8 @@
       <c r="A18" s="19">
         <v>17</v>
       </c>
-      <c r="B18" s="35"/>
-      <c r="C18" s="1" t="s">
+      <c r="B18" s="29"/>
+      <c r="C18" s="8" t="s">
         <v>75</v>
       </c>
       <c r="D18" s="1" t="s">
@@ -1901,8 +1903,8 @@
       <c r="A19" s="19">
         <v>18</v>
       </c>
-      <c r="B19" s="35"/>
-      <c r="C19" s="12" t="s">
+      <c r="B19" s="29"/>
+      <c r="C19" s="23" t="s">
         <v>52</v>
       </c>
       <c r="D19" s="2" t="s">
@@ -1920,7 +1922,7 @@
       <c r="A20" s="19">
         <v>19</v>
       </c>
-      <c r="B20" s="36" t="s">
+      <c r="B20" s="30" t="s">
         <v>43</v>
       </c>
       <c r="C20" s="8">
@@ -1941,7 +1943,7 @@
       <c r="A21" s="19">
         <v>20</v>
       </c>
-      <c r="B21" s="37"/>
+      <c r="B21" s="31"/>
       <c r="C21" s="7">
         <v>1174966078</v>
       </c>
@@ -1962,7 +1964,7 @@
       <c r="A22" s="19">
         <v>21</v>
       </c>
-      <c r="B22" s="37"/>
+      <c r="B22" s="31"/>
       <c r="C22" s="8">
         <v>1173963048</v>
       </c>
@@ -1981,7 +1983,7 @@
       <c r="A23" s="19">
         <v>22</v>
       </c>
-      <c r="B23" s="37"/>
+      <c r="B23" s="31"/>
       <c r="C23" s="8">
         <v>1173963049</v>
       </c>
@@ -2000,7 +2002,7 @@
       <c r="A24" s="19">
         <v>23</v>
       </c>
-      <c r="B24" s="37"/>
+      <c r="B24" s="31"/>
       <c r="C24" s="8">
         <v>1173963050</v>
       </c>
@@ -2019,7 +2021,7 @@
       <c r="A25" s="19">
         <v>24</v>
       </c>
-      <c r="B25" s="37"/>
+      <c r="B25" s="31"/>
       <c r="C25" s="8">
         <v>1173963051</v>
       </c>
@@ -2038,7 +2040,7 @@
       <c r="A26" s="19">
         <v>25</v>
       </c>
-      <c r="B26" s="37"/>
+      <c r="B26" s="31"/>
       <c r="C26" s="8">
         <v>1173963052</v>
       </c>
@@ -2057,7 +2059,7 @@
       <c r="A27" s="19">
         <v>26</v>
       </c>
-      <c r="B27" s="37"/>
+      <c r="B27" s="31"/>
       <c r="C27" s="27">
         <v>1173963053</v>
       </c>
@@ -2076,7 +2078,7 @@
       <c r="A28" s="19">
         <v>27</v>
       </c>
-      <c r="B28" s="37"/>
+      <c r="B28" s="31"/>
       <c r="C28" s="8">
         <v>1173963054</v>
       </c>
@@ -2095,7 +2097,7 @@
       <c r="A29" s="19">
         <v>28</v>
       </c>
-      <c r="B29" s="37"/>
+      <c r="B29" s="31"/>
       <c r="C29" s="8">
         <v>1173963055</v>
       </c>
@@ -2114,7 +2116,7 @@
       <c r="A30" s="19">
         <v>29</v>
       </c>
-      <c r="B30" s="37"/>
+      <c r="B30" s="31"/>
       <c r="C30" s="4">
         <v>1173963056</v>
       </c>
@@ -2135,7 +2137,7 @@
       <c r="A31" s="19">
         <v>30</v>
       </c>
-      <c r="B31" s="37"/>
+      <c r="B31" s="31"/>
       <c r="C31" s="8">
         <v>1173963057</v>
       </c>
@@ -2154,7 +2156,7 @@
       <c r="A32" s="19">
         <v>31</v>
       </c>
-      <c r="B32" s="37"/>
+      <c r="B32" s="31"/>
       <c r="C32" s="8">
         <v>1173963058</v>
       </c>
@@ -2173,7 +2175,7 @@
       <c r="A33" s="19">
         <v>32</v>
       </c>
-      <c r="B33" s="37"/>
+      <c r="B33" s="31"/>
       <c r="C33" s="8">
         <v>1173963059</v>
       </c>
@@ -2192,7 +2194,7 @@
       <c r="A34" s="19">
         <v>33</v>
       </c>
-      <c r="B34" s="37"/>
+      <c r="B34" s="31"/>
       <c r="C34" s="8">
         <v>1173963060</v>
       </c>
@@ -2211,7 +2213,7 @@
       <c r="A35" s="19">
         <v>34</v>
       </c>
-      <c r="B35" s="37"/>
+      <c r="B35" s="31"/>
       <c r="C35" s="7">
         <v>1173963061</v>
       </c>
@@ -2232,7 +2234,7 @@
       <c r="A36" s="19">
         <v>35</v>
       </c>
-      <c r="B36" s="37"/>
+      <c r="B36" s="31"/>
       <c r="C36" s="8">
         <v>1173963062</v>
       </c>
@@ -2251,7 +2253,7 @@
       <c r="A37" s="19">
         <v>36</v>
       </c>
-      <c r="B37" s="37"/>
+      <c r="B37" s="31"/>
       <c r="C37" s="8">
         <v>1173963063</v>
       </c>
@@ -2270,7 +2272,7 @@
       <c r="A38" s="19">
         <v>37</v>
       </c>
-      <c r="B38" s="37"/>
+      <c r="B38" s="31"/>
       <c r="C38" s="8">
         <v>1173963064</v>
       </c>
@@ -2289,7 +2291,7 @@
       <c r="A39" s="19">
         <v>38</v>
       </c>
-      <c r="B39" s="37"/>
+      <c r="B39" s="31"/>
       <c r="C39" s="4">
         <v>1173963065</v>
       </c>
@@ -2310,7 +2312,7 @@
       <c r="A40" s="19">
         <v>39</v>
       </c>
-      <c r="B40" s="37"/>
+      <c r="B40" s="31"/>
       <c r="C40" s="8">
         <v>1173963066</v>
       </c>
@@ -2329,7 +2331,7 @@
       <c r="A41" s="19">
         <v>40</v>
       </c>
-      <c r="B41" s="37"/>
+      <c r="B41" s="31"/>
       <c r="C41" s="8">
         <v>1173963067</v>
       </c>
@@ -2348,7 +2350,7 @@
       <c r="A42" s="19">
         <v>41</v>
       </c>
-      <c r="B42" s="37"/>
+      <c r="B42" s="31"/>
       <c r="C42" s="8">
         <v>1170534788</v>
       </c>
@@ -2367,7 +2369,7 @@
       <c r="A43" s="19">
         <v>42</v>
       </c>
-      <c r="B43" s="37"/>
+      <c r="B43" s="31"/>
       <c r="C43" s="8">
         <v>1170534789</v>
       </c>
@@ -2386,7 +2388,7 @@
       <c r="A44" s="19">
         <v>43</v>
       </c>
-      <c r="B44" s="37"/>
+      <c r="B44" s="31"/>
       <c r="C44" s="23" t="s">
         <v>53</v>
       </c>
@@ -2403,7 +2405,7 @@
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" s="19"/>
-      <c r="B45" s="37"/>
+      <c r="B45" s="31"/>
       <c r="C45" s="2" t="s">
         <v>78</v>
       </c>
@@ -2422,7 +2424,7 @@
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" s="19"/>
-      <c r="B46" s="37"/>
+      <c r="B46" s="31"/>
       <c r="C46" s="2" t="s">
         <v>79</v>
       </c>
@@ -2439,7 +2441,7 @@
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A47" s="19"/>
-      <c r="B47" s="37"/>
+      <c r="B47" s="31"/>
       <c r="C47" s="2" t="s">
         <v>80</v>
       </c>
@@ -2456,7 +2458,7 @@
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A48" s="19"/>
-      <c r="B48" s="38"/>
+      <c r="B48" s="32"/>
       <c r="C48" s="2" t="s">
         <v>81</v>
       </c>
@@ -2478,5 +2480,6 @@
     <mergeCell ref="B20:B48"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
--- a/5. Other/Danh sách số SIM BH-SX/SIM_Test BH-SX.xlsx
+++ b/5. Other/Danh sách số SIM BH-SX/SIM_Test BH-SX.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\5. Other\Danh sách số SIM BH-SX\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCCEBD0A-BDA6-4AC9-8D30-3653788507CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0DA88AF6-14AC-47CF-B3CD-A83F8CBD9550}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{68255EAF-D8EA-4C2C-BCF7-C24A5FBA6E37}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="1" xr2:uid="{68255EAF-D8EA-4C2C-BCF7-C24A5FBA6E37}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="249" uniqueCount="82">
   <si>
     <t>Seri</t>
   </si>
@@ -273,9 +273,6 @@
   </si>
   <si>
     <t>8401260150905597</t>
-  </si>
-  <si>
-    <t>đang thiếu</t>
   </si>
 </sst>
 </file>
@@ -323,7 +320,7 @@
       <family val="1"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -363,6 +360,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B0F0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -431,7 +434,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -511,8 +514,23 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -523,23 +541,17 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="49" fontId="4" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -559,9 +571,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -599,7 +611,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -705,7 +717,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -847,7 +859,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -899,7 +911,7 @@
       <c r="D2" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="E2" s="33" t="s">
+      <c r="E2" s="29" t="s">
         <v>40</v>
       </c>
       <c r="F2" s="5"/>
@@ -914,10 +926,10 @@
       <c r="C3" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="D3" s="34" t="s">
+      <c r="D3" s="30" t="s">
         <v>42</v>
       </c>
-      <c r="E3" s="33"/>
+      <c r="E3" s="29"/>
       <c r="F3" s="5" t="s">
         <v>46</v>
       </c>
@@ -932,8 +944,8 @@
       <c r="C4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D4" s="34"/>
-      <c r="E4" s="33"/>
+      <c r="D4" s="30"/>
+      <c r="E4" s="29"/>
       <c r="F4" s="5"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -946,10 +958,10 @@
       <c r="C5" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D5" s="37" t="s">
+      <c r="D5" s="33" t="s">
         <v>43</v>
       </c>
-      <c r="E5" s="33"/>
+      <c r="E5" s="29"/>
       <c r="F5" s="5"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -962,8 +974,8 @@
       <c r="C6" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="D6" s="37"/>
-      <c r="E6" s="33"/>
+      <c r="D6" s="33"/>
+      <c r="E6" s="29"/>
       <c r="F6" s="5" t="s">
         <v>49</v>
       </c>
@@ -978,10 +990,10 @@
       <c r="C7" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D7" s="34" t="s">
+      <c r="D7" s="30" t="s">
         <v>41</v>
       </c>
-      <c r="E7" s="35" t="s">
+      <c r="E7" s="31" t="s">
         <v>44</v>
       </c>
       <c r="F7" s="5"/>
@@ -996,8 +1008,8 @@
       <c r="C8" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="D8" s="34"/>
-      <c r="E8" s="36"/>
+      <c r="D8" s="30"/>
+      <c r="E8" s="32"/>
       <c r="F8" s="5" t="s">
         <v>47</v>
       </c>
@@ -1012,8 +1024,8 @@
       <c r="C9" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D9" s="34"/>
-      <c r="E9" s="36"/>
+      <c r="D9" s="30"/>
+      <c r="E9" s="32"/>
       <c r="F9" s="5" t="s">
         <v>50</v>
       </c>
@@ -1028,8 +1040,8 @@
       <c r="C10" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D10" s="34"/>
-      <c r="E10" s="36"/>
+      <c r="D10" s="30"/>
+      <c r="E10" s="32"/>
       <c r="F10" s="5"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -1042,8 +1054,8 @@
       <c r="C11" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="D11" s="34"/>
-      <c r="E11" s="36"/>
+      <c r="D11" s="30"/>
+      <c r="E11" s="32"/>
       <c r="F11" s="5" t="s">
         <v>64</v>
       </c>
@@ -1058,8 +1070,8 @@
       <c r="C12" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="D12" s="34"/>
-      <c r="E12" s="36"/>
+      <c r="D12" s="30"/>
+      <c r="E12" s="32"/>
       <c r="F12" s="5" t="s">
         <v>64</v>
       </c>
@@ -1074,8 +1086,8 @@
       <c r="C13" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="D13" s="34"/>
-      <c r="E13" s="36"/>
+      <c r="D13" s="30"/>
+      <c r="E13" s="32"/>
       <c r="F13" s="5" t="s">
         <v>64</v>
       </c>
@@ -1090,10 +1102,10 @@
       <c r="C14" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D14" s="34" t="s">
+      <c r="D14" s="30" t="s">
         <v>42</v>
       </c>
-      <c r="E14" s="36"/>
+      <c r="E14" s="32"/>
       <c r="F14" s="5"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
@@ -1106,8 +1118,8 @@
       <c r="C15" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="D15" s="34"/>
-      <c r="E15" s="36"/>
+      <c r="D15" s="30"/>
+      <c r="E15" s="32"/>
       <c r="F15" s="5" t="s">
         <v>46</v>
       </c>
@@ -1122,8 +1134,8 @@
       <c r="C16" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="D16" s="34"/>
-      <c r="E16" s="36"/>
+      <c r="D16" s="30"/>
+      <c r="E16" s="32"/>
       <c r="F16" s="5"/>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
@@ -1136,8 +1148,8 @@
       <c r="C17" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D17" s="34"/>
-      <c r="E17" s="36"/>
+      <c r="D17" s="30"/>
+      <c r="E17" s="32"/>
       <c r="F17" s="5"/>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
@@ -1150,10 +1162,10 @@
       <c r="C18" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D18" s="35" t="s">
+      <c r="D18" s="31" t="s">
         <v>43</v>
       </c>
-      <c r="E18" s="36"/>
+      <c r="E18" s="32"/>
       <c r="F18" s="5"/>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
@@ -1166,8 +1178,8 @@
       <c r="C19" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D19" s="36"/>
-      <c r="E19" s="36"/>
+      <c r="D19" s="32"/>
+      <c r="E19" s="32"/>
       <c r="F19" s="5"/>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
@@ -1180,8 +1192,8 @@
       <c r="C20" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D20" s="36"/>
-      <c r="E20" s="36"/>
+      <c r="D20" s="32"/>
+      <c r="E20" s="32"/>
       <c r="F20" s="5"/>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
@@ -1194,8 +1206,8 @@
       <c r="C21" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D21" s="36"/>
-      <c r="E21" s="36"/>
+      <c r="D21" s="32"/>
+      <c r="E21" s="32"/>
       <c r="F21" s="5"/>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
@@ -1208,8 +1220,8 @@
       <c r="C22" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="D22" s="36"/>
-      <c r="E22" s="36"/>
+      <c r="D22" s="32"/>
+      <c r="E22" s="32"/>
       <c r="F22" s="5"/>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
@@ -1222,8 +1234,8 @@
       <c r="C23" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="D23" s="36"/>
-      <c r="E23" s="36"/>
+      <c r="D23" s="32"/>
+      <c r="E23" s="32"/>
       <c r="F23" s="5"/>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
@@ -1236,8 +1248,8 @@
       <c r="C24" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="D24" s="36"/>
-      <c r="E24" s="36"/>
+      <c r="D24" s="32"/>
+      <c r="E24" s="32"/>
       <c r="F24" s="5"/>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
@@ -1250,8 +1262,8 @@
       <c r="C25" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="D25" s="36"/>
-      <c r="E25" s="36"/>
+      <c r="D25" s="32"/>
+      <c r="E25" s="32"/>
       <c r="F25" s="5"/>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
@@ -1264,8 +1276,8 @@
       <c r="C26" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="D26" s="36"/>
-      <c r="E26" s="36"/>
+      <c r="D26" s="32"/>
+      <c r="E26" s="32"/>
       <c r="F26" s="5" t="s">
         <v>46</v>
       </c>
@@ -1280,8 +1292,8 @@
       <c r="C27" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="D27" s="36"/>
-      <c r="E27" s="36"/>
+      <c r="D27" s="32"/>
+      <c r="E27" s="32"/>
       <c r="F27" s="5"/>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
@@ -1294,8 +1306,8 @@
       <c r="C28" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="D28" s="36"/>
-      <c r="E28" s="36"/>
+      <c r="D28" s="32"/>
+      <c r="E28" s="32"/>
       <c r="F28" s="5"/>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
@@ -1308,8 +1320,8 @@
       <c r="C29" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="D29" s="36"/>
-      <c r="E29" s="36"/>
+      <c r="D29" s="32"/>
+      <c r="E29" s="32"/>
       <c r="F29" s="5"/>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
@@ -1322,8 +1334,8 @@
       <c r="C30" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="D30" s="36"/>
-      <c r="E30" s="36"/>
+      <c r="D30" s="32"/>
+      <c r="E30" s="32"/>
       <c r="F30" s="5"/>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
@@ -1336,8 +1348,8 @@
       <c r="C31" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="D31" s="36"/>
-      <c r="E31" s="36"/>
+      <c r="D31" s="32"/>
+      <c r="E31" s="32"/>
       <c r="F31" s="5" t="s">
         <v>49</v>
       </c>
@@ -1352,8 +1364,8 @@
       <c r="C32" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="D32" s="36"/>
-      <c r="E32" s="36"/>
+      <c r="D32" s="32"/>
+      <c r="E32" s="32"/>
       <c r="F32" s="5"/>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
@@ -1366,8 +1378,8 @@
       <c r="C33" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="D33" s="36"/>
-      <c r="E33" s="36"/>
+      <c r="D33" s="32"/>
+      <c r="E33" s="32"/>
       <c r="F33" s="5"/>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
@@ -1380,8 +1392,8 @@
       <c r="C34" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="D34" s="36"/>
-      <c r="E34" s="36"/>
+      <c r="D34" s="32"/>
+      <c r="E34" s="32"/>
       <c r="F34" s="5"/>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
@@ -1394,8 +1406,8 @@
       <c r="C35" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="D35" s="36"/>
-      <c r="E35" s="36"/>
+      <c r="D35" s="32"/>
+      <c r="E35" s="32"/>
       <c r="F35" s="5" t="s">
         <v>48</v>
       </c>
@@ -1410,8 +1422,8 @@
       <c r="C36" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="D36" s="36"/>
-      <c r="E36" s="36"/>
+      <c r="D36" s="32"/>
+      <c r="E36" s="32"/>
       <c r="F36" s="5"/>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
@@ -1424,8 +1436,8 @@
       <c r="C37" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="D37" s="36"/>
-      <c r="E37" s="36"/>
+      <c r="D37" s="32"/>
+      <c r="E37" s="32"/>
       <c r="F37" s="5"/>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
@@ -1438,8 +1450,8 @@
       <c r="C38" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="D38" s="36"/>
-      <c r="E38" s="36"/>
+      <c r="D38" s="32"/>
+      <c r="E38" s="32"/>
       <c r="F38" s="5"/>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
@@ -1452,8 +1464,8 @@
       <c r="C39" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="D39" s="36"/>
-      <c r="E39" s="36"/>
+      <c r="D39" s="32"/>
+      <c r="E39" s="32"/>
       <c r="F39" s="5"/>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
@@ -1466,7 +1478,7 @@
       <c r="C40" s="13" t="s">
         <v>55</v>
       </c>
-      <c r="D40" s="36"/>
+      <c r="D40" s="32"/>
       <c r="E40" s="15" t="s">
         <v>54</v>
       </c>
@@ -1484,7 +1496,7 @@
       <c r="C41" s="13" t="s">
         <v>56</v>
       </c>
-      <c r="D41" s="36"/>
+      <c r="D41" s="32"/>
       <c r="E41" s="15" t="s">
         <v>54</v>
       </c>
@@ -1502,7 +1514,7 @@
       <c r="C42" s="13" t="s">
         <v>57</v>
       </c>
-      <c r="D42" s="38"/>
+      <c r="D42" s="34"/>
       <c r="E42" s="15" t="s">
         <v>54</v>
       </c>
@@ -1566,47 +1578,49 @@
       <c r="A2" s="19">
         <v>1</v>
       </c>
-      <c r="B2" s="29" t="s">
+      <c r="B2" s="35" t="s">
         <v>41</v>
       </c>
-      <c r="C2" s="23">
+      <c r="C2" s="38">
         <v>1174221624</v>
       </c>
-      <c r="D2" s="23" t="s">
+      <c r="D2" s="38" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="19" t="s">
-        <v>70</v>
-      </c>
-      <c r="F2" s="19" t="s">
+      <c r="E2" s="39" t="s">
+        <v>70</v>
+      </c>
+      <c r="F2" s="39" t="s">
         <v>71</v>
       </c>
-      <c r="G2" s="19"/>
+      <c r="G2" s="39"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="19">
         <v>2</v>
       </c>
-      <c r="B3" s="29"/>
-      <c r="C3" s="1">
+      <c r="B3" s="36"/>
+      <c r="C3" s="7">
         <v>1173963040</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="D3" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="E3" s="19" t="s">
-        <v>70</v>
-      </c>
-      <c r="F3" s="19" t="s">
-        <v>72</v>
-      </c>
-      <c r="G3" s="19"/>
+      <c r="E3" s="20" t="s">
+        <v>70</v>
+      </c>
+      <c r="F3" s="20" t="s">
+        <v>72</v>
+      </c>
+      <c r="G3" s="20" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="19">
         <v>3</v>
       </c>
-      <c r="B4" s="29"/>
+      <c r="B4" s="36"/>
       <c r="C4" s="7">
         <v>1173963041</v>
       </c>
@@ -1627,102 +1641,106 @@
       <c r="A5" s="19">
         <v>4</v>
       </c>
-      <c r="B5" s="29"/>
-      <c r="C5" s="1">
+      <c r="B5" s="36"/>
+      <c r="C5" s="7">
         <v>1173963042</v>
       </c>
-      <c r="D5" s="1" t="s">
+      <c r="D5" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="E5" s="19" t="s">
-        <v>70</v>
-      </c>
-      <c r="F5" s="19" t="s">
-        <v>72</v>
-      </c>
-      <c r="G5" s="19"/>
+      <c r="E5" s="20" t="s">
+        <v>70</v>
+      </c>
+      <c r="F5" s="20" t="s">
+        <v>72</v>
+      </c>
+      <c r="G5" s="20" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="19">
         <v>5</v>
       </c>
-      <c r="B6" s="29"/>
-      <c r="C6" s="1">
+      <c r="B6" s="36"/>
+      <c r="C6" s="7">
         <v>1173963043</v>
       </c>
-      <c r="D6" s="1" t="s">
+      <c r="D6" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="E6" s="19" t="s">
-        <v>70</v>
-      </c>
-      <c r="F6" s="19" t="s">
-        <v>72</v>
-      </c>
-      <c r="G6" s="19"/>
+      <c r="E6" s="20" t="s">
+        <v>70</v>
+      </c>
+      <c r="F6" s="20" t="s">
+        <v>72</v>
+      </c>
+      <c r="G6" s="20" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="19">
         <v>6</v>
       </c>
-      <c r="B7" s="29"/>
-      <c r="C7" s="1" t="s">
+      <c r="B7" s="36"/>
+      <c r="C7" s="40" t="s">
         <v>63</v>
       </c>
-      <c r="D7" s="1" t="s">
+      <c r="D7" s="40" t="s">
         <v>58</v>
       </c>
-      <c r="E7" s="19" t="s">
+      <c r="E7" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="F7" s="19" t="s">
-        <v>72</v>
-      </c>
-      <c r="G7" s="19"/>
+      <c r="F7" s="39" t="s">
+        <v>72</v>
+      </c>
+      <c r="G7" s="39"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="19">
         <v>7</v>
       </c>
-      <c r="B8" s="29"/>
-      <c r="C8" s="1" t="s">
+      <c r="B8" s="36"/>
+      <c r="C8" s="40" t="s">
         <v>62</v>
       </c>
-      <c r="D8" s="1" t="s">
+      <c r="D8" s="40" t="s">
         <v>59</v>
       </c>
-      <c r="E8" s="19" t="s">
+      <c r="E8" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="F8" s="19" t="s">
-        <v>72</v>
-      </c>
-      <c r="G8" s="19"/>
+      <c r="F8" s="39" t="s">
+        <v>72</v>
+      </c>
+      <c r="G8" s="39"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="19">
         <v>8</v>
       </c>
-      <c r="B9" s="29"/>
-      <c r="C9" s="1" t="s">
+      <c r="B9" s="36"/>
+      <c r="C9" s="40" t="s">
         <v>61</v>
       </c>
-      <c r="D9" s="1" t="s">
+      <c r="D9" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="E9" s="19" t="s">
+      <c r="E9" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="F9" s="19" t="s">
-        <v>72</v>
-      </c>
-      <c r="G9" s="19"/>
+      <c r="F9" s="39" t="s">
+        <v>72</v>
+      </c>
+      <c r="G9" s="39"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="19">
         <v>9</v>
       </c>
-      <c r="B10" s="29"/>
+      <c r="B10" s="36"/>
       <c r="C10" s="21" t="s">
         <v>51</v>
       </c>
@@ -1743,9 +1761,7 @@
       <c r="A11" s="19">
         <v>10</v>
       </c>
-      <c r="B11" s="29" t="s">
-        <v>42</v>
-      </c>
+      <c r="B11" s="36"/>
       <c r="C11" s="10">
         <v>1174221625</v>
       </c>
@@ -1766,26 +1782,26 @@
       <c r="A12" s="19">
         <v>11</v>
       </c>
-      <c r="B12" s="29"/>
-      <c r="C12" s="8">
+      <c r="B12" s="36"/>
+      <c r="C12" s="40">
         <v>1174221626</v>
       </c>
-      <c r="D12" s="1" t="s">
+      <c r="D12" s="40" t="s">
         <v>5</v>
       </c>
-      <c r="E12" s="19" t="s">
-        <v>70</v>
-      </c>
-      <c r="F12" s="19" t="s">
+      <c r="E12" s="39" t="s">
+        <v>70</v>
+      </c>
+      <c r="F12" s="39" t="s">
         <v>71</v>
       </c>
-      <c r="G12" s="19"/>
+      <c r="G12" s="39"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="19">
         <v>12</v>
       </c>
-      <c r="B13" s="29"/>
+      <c r="B13" s="36"/>
       <c r="C13" s="10">
         <v>1173963044</v>
       </c>
@@ -1806,7 +1822,7 @@
       <c r="A14" s="19">
         <v>13</v>
       </c>
-      <c r="B14" s="29"/>
+      <c r="B14" s="36"/>
       <c r="C14" s="7">
         <v>1173963045</v>
       </c>
@@ -1827,102 +1843,102 @@
       <c r="A15" s="19">
         <v>14</v>
       </c>
-      <c r="B15" s="29"/>
-      <c r="C15" s="8">
+      <c r="B15" s="36"/>
+      <c r="C15" s="40">
         <v>1173963046</v>
       </c>
-      <c r="D15" s="1" t="s">
+      <c r="D15" s="40" t="s">
         <v>14</v>
       </c>
-      <c r="E15" s="19" t="s">
-        <v>70</v>
-      </c>
-      <c r="F15" s="19" t="s">
-        <v>72</v>
-      </c>
-      <c r="G15" s="19"/>
+      <c r="E15" s="39" t="s">
+        <v>70</v>
+      </c>
+      <c r="F15" s="39" t="s">
+        <v>72</v>
+      </c>
+      <c r="G15" s="39"/>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="19">
         <v>15</v>
       </c>
-      <c r="B16" s="29"/>
-      <c r="C16" s="8">
+      <c r="B16" s="36"/>
+      <c r="C16" s="40">
         <v>1173963047</v>
       </c>
-      <c r="D16" s="1" t="s">
+      <c r="D16" s="40" t="s">
         <v>15</v>
       </c>
-      <c r="E16" s="19" t="s">
-        <v>70</v>
-      </c>
-      <c r="F16" s="19" t="s">
-        <v>72</v>
-      </c>
-      <c r="G16" s="19"/>
+      <c r="E16" s="39" t="s">
+        <v>70</v>
+      </c>
+      <c r="F16" s="39" t="s">
+        <v>72</v>
+      </c>
+      <c r="G16" s="39"/>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="19">
         <v>16</v>
       </c>
-      <c r="B17" s="29"/>
-      <c r="C17" s="8" t="s">
+      <c r="B17" s="36"/>
+      <c r="C17" s="40" t="s">
         <v>74</v>
       </c>
-      <c r="D17" s="1" t="s">
+      <c r="D17" s="40" t="s">
         <v>76</v>
       </c>
-      <c r="E17" s="19" t="s">
+      <c r="E17" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="F17" s="19" t="s">
-        <v>72</v>
-      </c>
-      <c r="G17" s="19"/>
+      <c r="F17" s="39" t="s">
+        <v>72</v>
+      </c>
+      <c r="G17" s="39"/>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="19">
         <v>17</v>
       </c>
-      <c r="B18" s="29"/>
-      <c r="C18" s="8" t="s">
+      <c r="B18" s="36"/>
+      <c r="C18" s="40" t="s">
         <v>75</v>
       </c>
-      <c r="D18" s="1" t="s">
+      <c r="D18" s="40" t="s">
         <v>77</v>
       </c>
-      <c r="E18" s="19" t="s">
+      <c r="E18" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="F18" s="19" t="s">
-        <v>72</v>
-      </c>
-      <c r="G18" s="19"/>
+      <c r="F18" s="39" t="s">
+        <v>72</v>
+      </c>
+      <c r="G18" s="39"/>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="19">
         <v>18</v>
       </c>
-      <c r="B19" s="29"/>
-      <c r="C19" s="23" t="s">
+      <c r="B19" s="37"/>
+      <c r="C19" s="38" t="s">
         <v>52</v>
       </c>
-      <c r="D19" s="2" t="s">
+      <c r="D19" s="41" t="s">
         <v>56</v>
       </c>
-      <c r="E19" s="19" t="s">
+      <c r="E19" s="39" t="s">
         <v>66</v>
       </c>
-      <c r="F19" s="19" t="s">
+      <c r="F19" s="39" t="s">
         <v>71</v>
       </c>
-      <c r="G19" s="19"/>
+      <c r="G19" s="39"/>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="19">
         <v>19</v>
       </c>
-      <c r="B20" s="30" t="s">
+      <c r="B20" s="35" t="s">
         <v>43</v>
       </c>
       <c r="C20" s="8">
@@ -1943,7 +1959,7 @@
       <c r="A21" s="19">
         <v>20</v>
       </c>
-      <c r="B21" s="31"/>
+      <c r="B21" s="36"/>
       <c r="C21" s="7">
         <v>1174966078</v>
       </c>
@@ -1964,7 +1980,7 @@
       <c r="A22" s="19">
         <v>21</v>
       </c>
-      <c r="B22" s="31"/>
+      <c r="B22" s="36"/>
       <c r="C22" s="8">
         <v>1173963048</v>
       </c>
@@ -1983,7 +1999,7 @@
       <c r="A23" s="19">
         <v>22</v>
       </c>
-      <c r="B23" s="31"/>
+      <c r="B23" s="36"/>
       <c r="C23" s="8">
         <v>1173963049</v>
       </c>
@@ -2002,7 +2018,7 @@
       <c r="A24" s="19">
         <v>23</v>
       </c>
-      <c r="B24" s="31"/>
+      <c r="B24" s="36"/>
       <c r="C24" s="8">
         <v>1173963050</v>
       </c>
@@ -2021,7 +2037,7 @@
       <c r="A25" s="19">
         <v>24</v>
       </c>
-      <c r="B25" s="31"/>
+      <c r="B25" s="36"/>
       <c r="C25" s="8">
         <v>1173963051</v>
       </c>
@@ -2040,7 +2056,7 @@
       <c r="A26" s="19">
         <v>25</v>
       </c>
-      <c r="B26" s="31"/>
+      <c r="B26" s="36"/>
       <c r="C26" s="8">
         <v>1173963052</v>
       </c>
@@ -2059,7 +2075,7 @@
       <c r="A27" s="19">
         <v>26</v>
       </c>
-      <c r="B27" s="31"/>
+      <c r="B27" s="36"/>
       <c r="C27" s="27">
         <v>1173963053</v>
       </c>
@@ -2078,7 +2094,7 @@
       <c r="A28" s="19">
         <v>27</v>
       </c>
-      <c r="B28" s="31"/>
+      <c r="B28" s="36"/>
       <c r="C28" s="8">
         <v>1173963054</v>
       </c>
@@ -2097,7 +2113,7 @@
       <c r="A29" s="19">
         <v>28</v>
       </c>
-      <c r="B29" s="31"/>
+      <c r="B29" s="36"/>
       <c r="C29" s="8">
         <v>1173963055</v>
       </c>
@@ -2116,7 +2132,7 @@
       <c r="A30" s="19">
         <v>29</v>
       </c>
-      <c r="B30" s="31"/>
+      <c r="B30" s="36"/>
       <c r="C30" s="4">
         <v>1173963056</v>
       </c>
@@ -2137,7 +2153,7 @@
       <c r="A31" s="19">
         <v>30</v>
       </c>
-      <c r="B31" s="31"/>
+      <c r="B31" s="36"/>
       <c r="C31" s="8">
         <v>1173963057</v>
       </c>
@@ -2156,7 +2172,7 @@
       <c r="A32" s="19">
         <v>31</v>
       </c>
-      <c r="B32" s="31"/>
+      <c r="B32" s="36"/>
       <c r="C32" s="8">
         <v>1173963058</v>
       </c>
@@ -2175,7 +2191,7 @@
       <c r="A33" s="19">
         <v>32</v>
       </c>
-      <c r="B33" s="31"/>
+      <c r="B33" s="36"/>
       <c r="C33" s="8">
         <v>1173963059</v>
       </c>
@@ -2194,7 +2210,7 @@
       <c r="A34" s="19">
         <v>33</v>
       </c>
-      <c r="B34" s="31"/>
+      <c r="B34" s="36"/>
       <c r="C34" s="8">
         <v>1173963060</v>
       </c>
@@ -2213,7 +2229,7 @@
       <c r="A35" s="19">
         <v>34</v>
       </c>
-      <c r="B35" s="31"/>
+      <c r="B35" s="36"/>
       <c r="C35" s="7">
         <v>1173963061</v>
       </c>
@@ -2234,7 +2250,7 @@
       <c r="A36" s="19">
         <v>35</v>
       </c>
-      <c r="B36" s="31"/>
+      <c r="B36" s="36"/>
       <c r="C36" s="8">
         <v>1173963062</v>
       </c>
@@ -2253,7 +2269,7 @@
       <c r="A37" s="19">
         <v>36</v>
       </c>
-      <c r="B37" s="31"/>
+      <c r="B37" s="36"/>
       <c r="C37" s="8">
         <v>1173963063</v>
       </c>
@@ -2272,7 +2288,7 @@
       <c r="A38" s="19">
         <v>37</v>
       </c>
-      <c r="B38" s="31"/>
+      <c r="B38" s="36"/>
       <c r="C38" s="8">
         <v>1173963064</v>
       </c>
@@ -2291,7 +2307,7 @@
       <c r="A39" s="19">
         <v>38</v>
       </c>
-      <c r="B39" s="31"/>
+      <c r="B39" s="36"/>
       <c r="C39" s="4">
         <v>1173963065</v>
       </c>
@@ -2312,7 +2328,7 @@
       <c r="A40" s="19">
         <v>39</v>
       </c>
-      <c r="B40" s="31"/>
+      <c r="B40" s="36"/>
       <c r="C40" s="8">
         <v>1173963066</v>
       </c>
@@ -2331,7 +2347,7 @@
       <c r="A41" s="19">
         <v>40</v>
       </c>
-      <c r="B41" s="31"/>
+      <c r="B41" s="36"/>
       <c r="C41" s="8">
         <v>1173963067</v>
       </c>
@@ -2350,7 +2366,7 @@
       <c r="A42" s="19">
         <v>41</v>
       </c>
-      <c r="B42" s="31"/>
+      <c r="B42" s="36"/>
       <c r="C42" s="8">
         <v>1170534788</v>
       </c>
@@ -2369,7 +2385,7 @@
       <c r="A43" s="19">
         <v>42</v>
       </c>
-      <c r="B43" s="31"/>
+      <c r="B43" s="36"/>
       <c r="C43" s="8">
         <v>1170534789</v>
       </c>
@@ -2388,7 +2404,7 @@
       <c r="A44" s="19">
         <v>43</v>
       </c>
-      <c r="B44" s="31"/>
+      <c r="B44" s="36"/>
       <c r="C44" s="23" t="s">
         <v>53</v>
       </c>
@@ -2405,26 +2421,26 @@
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" s="19"/>
-      <c r="B45" s="31"/>
-      <c r="C45" s="2" t="s">
+      <c r="B45" s="36"/>
+      <c r="C45" s="6" t="s">
         <v>78</v>
       </c>
-      <c r="D45" s="19">
+      <c r="D45" s="20">
         <v>1211326214</v>
       </c>
-      <c r="E45" s="19" t="s">
+      <c r="E45" s="20" t="s">
         <v>64</v>
       </c>
-      <c r="F45" s="19" t="s">
-        <v>72</v>
-      </c>
-      <c r="G45" s="19" t="s">
-        <v>82</v>
+      <c r="F45" s="20" t="s">
+        <v>72</v>
+      </c>
+      <c r="G45" s="20" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" s="19"/>
-      <c r="B46" s="31"/>
+      <c r="B46" s="36"/>
       <c r="C46" s="2" t="s">
         <v>79</v>
       </c>
@@ -2441,7 +2457,7 @@
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A47" s="19"/>
-      <c r="B47" s="31"/>
+      <c r="B47" s="36"/>
       <c r="C47" s="2" t="s">
         <v>80</v>
       </c>
@@ -2458,7 +2474,7 @@
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A48" s="19"/>
-      <c r="B48" s="32"/>
+      <c r="B48" s="37"/>
       <c r="C48" s="2" t="s">
         <v>81</v>
       </c>
@@ -2474,10 +2490,9 @@
       <c r="G48" s="19"/>
     </row>
   </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="B2:B10"/>
-    <mergeCell ref="B11:B19"/>
+  <mergeCells count="2">
     <mergeCell ref="B20:B48"/>
+    <mergeCell ref="B2:B19"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>

--- a/5. Other/Danh sách số SIM BH-SX/SIM_Test BH-SX.xlsx
+++ b/5. Other/Danh sách số SIM BH-SX/SIM_Test BH-SX.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\5. Other\Danh sách số SIM BH-SX\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0DA88AF6-14AC-47CF-B3CD-A83F8CBD9550}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBD43352-EEFA-4761-9B47-E7F5B0F78BFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="1" xr2:uid="{68255EAF-D8EA-4C2C-BCF7-C24A5FBA6E37}"/>
   </bookViews>
@@ -16,6 +16,9 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="SIM_TEST" sheetId="2" r:id="rId2"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">SIM_TEST!$A$1:$G$48</definedName>
+  </definedNames>
   <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -26,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="249" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="86">
   <si>
     <t>Seri</t>
   </si>
@@ -273,6 +276,18 @@
   </si>
   <si>
     <t>8401260150905597</t>
+  </si>
+  <si>
+    <t>01211326214</t>
+  </si>
+  <si>
+    <t>01212631236</t>
+  </si>
+  <si>
+    <t>01210207642</t>
+  </si>
+  <si>
+    <t>01211065926</t>
   </si>
 </sst>
 </file>
@@ -434,7 +449,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -514,6 +529,18 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="2" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -541,16 +568,10 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -911,7 +932,7 @@
       <c r="D2" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="E2" s="29" t="s">
+      <c r="E2" s="33" t="s">
         <v>40</v>
       </c>
       <c r="F2" s="5"/>
@@ -926,10 +947,10 @@
       <c r="C3" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="D3" s="30" t="s">
+      <c r="D3" s="34" t="s">
         <v>42</v>
       </c>
-      <c r="E3" s="29"/>
+      <c r="E3" s="33"/>
       <c r="F3" s="5" t="s">
         <v>46</v>
       </c>
@@ -944,8 +965,8 @@
       <c r="C4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D4" s="30"/>
-      <c r="E4" s="29"/>
+      <c r="D4" s="34"/>
+      <c r="E4" s="33"/>
       <c r="F4" s="5"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -958,10 +979,10 @@
       <c r="C5" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D5" s="33" t="s">
+      <c r="D5" s="37" t="s">
         <v>43</v>
       </c>
-      <c r="E5" s="29"/>
+      <c r="E5" s="33"/>
       <c r="F5" s="5"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -974,8 +995,8 @@
       <c r="C6" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="D6" s="33"/>
-      <c r="E6" s="29"/>
+      <c r="D6" s="37"/>
+      <c r="E6" s="33"/>
       <c r="F6" s="5" t="s">
         <v>49</v>
       </c>
@@ -990,10 +1011,10 @@
       <c r="C7" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D7" s="30" t="s">
+      <c r="D7" s="34" t="s">
         <v>41</v>
       </c>
-      <c r="E7" s="31" t="s">
+      <c r="E7" s="35" t="s">
         <v>44</v>
       </c>
       <c r="F7" s="5"/>
@@ -1008,8 +1029,8 @@
       <c r="C8" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="D8" s="30"/>
-      <c r="E8" s="32"/>
+      <c r="D8" s="34"/>
+      <c r="E8" s="36"/>
       <c r="F8" s="5" t="s">
         <v>47</v>
       </c>
@@ -1024,8 +1045,8 @@
       <c r="C9" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D9" s="30"/>
-      <c r="E9" s="32"/>
+      <c r="D9" s="34"/>
+      <c r="E9" s="36"/>
       <c r="F9" s="5" t="s">
         <v>50</v>
       </c>
@@ -1040,8 +1061,8 @@
       <c r="C10" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D10" s="30"/>
-      <c r="E10" s="32"/>
+      <c r="D10" s="34"/>
+      <c r="E10" s="36"/>
       <c r="F10" s="5"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -1054,8 +1075,8 @@
       <c r="C11" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="D11" s="30"/>
-      <c r="E11" s="32"/>
+      <c r="D11" s="34"/>
+      <c r="E11" s="36"/>
       <c r="F11" s="5" t="s">
         <v>64</v>
       </c>
@@ -1070,8 +1091,8 @@
       <c r="C12" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="D12" s="30"/>
-      <c r="E12" s="32"/>
+      <c r="D12" s="34"/>
+      <c r="E12" s="36"/>
       <c r="F12" s="5" t="s">
         <v>64</v>
       </c>
@@ -1086,8 +1107,8 @@
       <c r="C13" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="D13" s="30"/>
-      <c r="E13" s="32"/>
+      <c r="D13" s="34"/>
+      <c r="E13" s="36"/>
       <c r="F13" s="5" t="s">
         <v>64</v>
       </c>
@@ -1102,10 +1123,10 @@
       <c r="C14" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D14" s="30" t="s">
+      <c r="D14" s="34" t="s">
         <v>42</v>
       </c>
-      <c r="E14" s="32"/>
+      <c r="E14" s="36"/>
       <c r="F14" s="5"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
@@ -1118,8 +1139,8 @@
       <c r="C15" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="D15" s="30"/>
-      <c r="E15" s="32"/>
+      <c r="D15" s="34"/>
+      <c r="E15" s="36"/>
       <c r="F15" s="5" t="s">
         <v>46</v>
       </c>
@@ -1134,8 +1155,8 @@
       <c r="C16" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="D16" s="30"/>
-      <c r="E16" s="32"/>
+      <c r="D16" s="34"/>
+      <c r="E16" s="36"/>
       <c r="F16" s="5"/>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
@@ -1148,8 +1169,8 @@
       <c r="C17" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D17" s="30"/>
-      <c r="E17" s="32"/>
+      <c r="D17" s="34"/>
+      <c r="E17" s="36"/>
       <c r="F17" s="5"/>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
@@ -1162,10 +1183,10 @@
       <c r="C18" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D18" s="31" t="s">
+      <c r="D18" s="35" t="s">
         <v>43</v>
       </c>
-      <c r="E18" s="32"/>
+      <c r="E18" s="36"/>
       <c r="F18" s="5"/>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
@@ -1178,8 +1199,8 @@
       <c r="C19" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D19" s="32"/>
-      <c r="E19" s="32"/>
+      <c r="D19" s="36"/>
+      <c r="E19" s="36"/>
       <c r="F19" s="5"/>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
@@ -1192,8 +1213,8 @@
       <c r="C20" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D20" s="32"/>
-      <c r="E20" s="32"/>
+      <c r="D20" s="36"/>
+      <c r="E20" s="36"/>
       <c r="F20" s="5"/>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
@@ -1206,8 +1227,8 @@
       <c r="C21" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D21" s="32"/>
-      <c r="E21" s="32"/>
+      <c r="D21" s="36"/>
+      <c r="E21" s="36"/>
       <c r="F21" s="5"/>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
@@ -1220,8 +1241,8 @@
       <c r="C22" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="D22" s="32"/>
-      <c r="E22" s="32"/>
+      <c r="D22" s="36"/>
+      <c r="E22" s="36"/>
       <c r="F22" s="5"/>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
@@ -1234,8 +1255,8 @@
       <c r="C23" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="D23" s="32"/>
-      <c r="E23" s="32"/>
+      <c r="D23" s="36"/>
+      <c r="E23" s="36"/>
       <c r="F23" s="5"/>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
@@ -1248,8 +1269,8 @@
       <c r="C24" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="D24" s="32"/>
-      <c r="E24" s="32"/>
+      <c r="D24" s="36"/>
+      <c r="E24" s="36"/>
       <c r="F24" s="5"/>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
@@ -1262,8 +1283,8 @@
       <c r="C25" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="D25" s="32"/>
-      <c r="E25" s="32"/>
+      <c r="D25" s="36"/>
+      <c r="E25" s="36"/>
       <c r="F25" s="5"/>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
@@ -1276,8 +1297,8 @@
       <c r="C26" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="D26" s="32"/>
-      <c r="E26" s="32"/>
+      <c r="D26" s="36"/>
+      <c r="E26" s="36"/>
       <c r="F26" s="5" t="s">
         <v>46</v>
       </c>
@@ -1292,8 +1313,8 @@
       <c r="C27" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="D27" s="32"/>
-      <c r="E27" s="32"/>
+      <c r="D27" s="36"/>
+      <c r="E27" s="36"/>
       <c r="F27" s="5"/>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
@@ -1306,8 +1327,8 @@
       <c r="C28" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="D28" s="32"/>
-      <c r="E28" s="32"/>
+      <c r="D28" s="36"/>
+      <c r="E28" s="36"/>
       <c r="F28" s="5"/>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
@@ -1320,8 +1341,8 @@
       <c r="C29" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="D29" s="32"/>
-      <c r="E29" s="32"/>
+      <c r="D29" s="36"/>
+      <c r="E29" s="36"/>
       <c r="F29" s="5"/>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
@@ -1334,8 +1355,8 @@
       <c r="C30" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="D30" s="32"/>
-      <c r="E30" s="32"/>
+      <c r="D30" s="36"/>
+      <c r="E30" s="36"/>
       <c r="F30" s="5"/>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
@@ -1348,8 +1369,8 @@
       <c r="C31" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="D31" s="32"/>
-      <c r="E31" s="32"/>
+      <c r="D31" s="36"/>
+      <c r="E31" s="36"/>
       <c r="F31" s="5" t="s">
         <v>49</v>
       </c>
@@ -1364,8 +1385,8 @@
       <c r="C32" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="D32" s="32"/>
-      <c r="E32" s="32"/>
+      <c r="D32" s="36"/>
+      <c r="E32" s="36"/>
       <c r="F32" s="5"/>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
@@ -1378,8 +1399,8 @@
       <c r="C33" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="D33" s="32"/>
-      <c r="E33" s="32"/>
+      <c r="D33" s="36"/>
+      <c r="E33" s="36"/>
       <c r="F33" s="5"/>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
@@ -1392,8 +1413,8 @@
       <c r="C34" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="D34" s="32"/>
-      <c r="E34" s="32"/>
+      <c r="D34" s="36"/>
+      <c r="E34" s="36"/>
       <c r="F34" s="5"/>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
@@ -1406,8 +1427,8 @@
       <c r="C35" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="D35" s="32"/>
-      <c r="E35" s="32"/>
+      <c r="D35" s="36"/>
+      <c r="E35" s="36"/>
       <c r="F35" s="5" t="s">
         <v>48</v>
       </c>
@@ -1422,8 +1443,8 @@
       <c r="C36" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="D36" s="32"/>
-      <c r="E36" s="32"/>
+      <c r="D36" s="36"/>
+      <c r="E36" s="36"/>
       <c r="F36" s="5"/>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
@@ -1436,8 +1457,8 @@
       <c r="C37" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="D37" s="32"/>
-      <c r="E37" s="32"/>
+      <c r="D37" s="36"/>
+      <c r="E37" s="36"/>
       <c r="F37" s="5"/>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
@@ -1450,8 +1471,8 @@
       <c r="C38" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="D38" s="32"/>
-      <c r="E38" s="32"/>
+      <c r="D38" s="36"/>
+      <c r="E38" s="36"/>
       <c r="F38" s="5"/>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
@@ -1464,8 +1485,8 @@
       <c r="C39" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="D39" s="32"/>
-      <c r="E39" s="32"/>
+      <c r="D39" s="36"/>
+      <c r="E39" s="36"/>
       <c r="F39" s="5"/>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
@@ -1478,7 +1499,7 @@
       <c r="C40" s="13" t="s">
         <v>55</v>
       </c>
-      <c r="D40" s="32"/>
+      <c r="D40" s="36"/>
       <c r="E40" s="15" t="s">
         <v>54</v>
       </c>
@@ -1496,7 +1517,7 @@
       <c r="C41" s="13" t="s">
         <v>56</v>
       </c>
-      <c r="D41" s="32"/>
+      <c r="D41" s="36"/>
       <c r="E41" s="15" t="s">
         <v>54</v>
       </c>
@@ -1514,7 +1535,7 @@
       <c r="C42" s="13" t="s">
         <v>57</v>
       </c>
-      <c r="D42" s="34"/>
+      <c r="D42" s="38"/>
       <c r="E42" s="15" t="s">
         <v>54</v>
       </c>
@@ -1539,6 +1560,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4F2BD792-CCE4-406F-96E2-4768C3AF568E}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:G48"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1574,32 +1596,32 @@
         <v>45</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2" s="19">
         <v>1</v>
       </c>
-      <c r="B2" s="35" t="s">
+      <c r="B2" s="39" t="s">
         <v>41</v>
       </c>
-      <c r="C2" s="38">
+      <c r="C2" s="29">
         <v>1174221624</v>
       </c>
-      <c r="D2" s="38" t="s">
+      <c r="D2" s="29" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="39" t="s">
-        <v>70</v>
-      </c>
-      <c r="F2" s="39" t="s">
+      <c r="E2" s="30" t="s">
+        <v>70</v>
+      </c>
+      <c r="F2" s="30" t="s">
         <v>71</v>
       </c>
-      <c r="G2" s="39"/>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G2" s="30"/>
+    </row>
+    <row r="3" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3" s="19">
         <v>2</v>
       </c>
-      <c r="B3" s="36"/>
+      <c r="B3" s="40"/>
       <c r="C3" s="7">
         <v>1173963040</v>
       </c>
@@ -1616,11 +1638,11 @@
         <v>47</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A4" s="19">
         <v>3</v>
       </c>
-      <c r="B4" s="36"/>
+      <c r="B4" s="40"/>
       <c r="C4" s="7">
         <v>1173963041</v>
       </c>
@@ -1637,11 +1659,11 @@
         <v>46</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A5" s="19">
         <v>4</v>
       </c>
-      <c r="B5" s="36"/>
+      <c r="B5" s="40"/>
       <c r="C5" s="7">
         <v>1173963042</v>
       </c>
@@ -1658,11 +1680,11 @@
         <v>47</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A6" s="19">
         <v>5</v>
       </c>
-      <c r="B6" s="36"/>
+      <c r="B6" s="40"/>
       <c r="C6" s="7">
         <v>1173963043</v>
       </c>
@@ -1679,68 +1701,68 @@
         <v>47</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A7" s="19">
         <v>6</v>
       </c>
-      <c r="B7" s="36"/>
-      <c r="C7" s="40" t="s">
+      <c r="B7" s="40"/>
+      <c r="C7" s="31" t="s">
         <v>63</v>
       </c>
-      <c r="D7" s="40" t="s">
+      <c r="D7" s="31" t="s">
         <v>58</v>
       </c>
-      <c r="E7" s="39" t="s">
+      <c r="E7" s="30" t="s">
         <v>64</v>
       </c>
-      <c r="F7" s="39" t="s">
-        <v>72</v>
-      </c>
-      <c r="G7" s="39"/>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="F7" s="30" t="s">
+        <v>72</v>
+      </c>
+      <c r="G7" s="30"/>
+    </row>
+    <row r="8" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A8" s="19">
         <v>7</v>
       </c>
-      <c r="B8" s="36"/>
-      <c r="C8" s="40" t="s">
+      <c r="B8" s="40"/>
+      <c r="C8" s="31" t="s">
         <v>62</v>
       </c>
-      <c r="D8" s="40" t="s">
+      <c r="D8" s="31" t="s">
         <v>59</v>
       </c>
-      <c r="E8" s="39" t="s">
+      <c r="E8" s="30" t="s">
         <v>64</v>
       </c>
-      <c r="F8" s="39" t="s">
-        <v>72</v>
-      </c>
-      <c r="G8" s="39"/>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="F8" s="30" t="s">
+        <v>72</v>
+      </c>
+      <c r="G8" s="30"/>
+    </row>
+    <row r="9" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A9" s="19">
         <v>8</v>
       </c>
-      <c r="B9" s="36"/>
-      <c r="C9" s="40" t="s">
+      <c r="B9" s="40"/>
+      <c r="C9" s="31" t="s">
         <v>61</v>
       </c>
-      <c r="D9" s="40" t="s">
+      <c r="D9" s="31" t="s">
         <v>60</v>
       </c>
-      <c r="E9" s="39" t="s">
+      <c r="E9" s="30" t="s">
         <v>64</v>
       </c>
-      <c r="F9" s="39" t="s">
-        <v>72</v>
-      </c>
-      <c r="G9" s="39"/>
+      <c r="F9" s="30" t="s">
+        <v>72</v>
+      </c>
+      <c r="G9" s="30"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="19">
         <v>9</v>
       </c>
-      <c r="B10" s="36"/>
+      <c r="B10" s="40"/>
       <c r="C10" s="21" t="s">
         <v>51</v>
       </c>
@@ -1757,11 +1779,11 @@
         <v>73</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A11" s="19">
         <v>10</v>
       </c>
-      <c r="B11" s="36"/>
+      <c r="B11" s="40"/>
       <c r="C11" s="10">
         <v>1174221625</v>
       </c>
@@ -1778,30 +1800,30 @@
         <v>46</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A12" s="19">
         <v>11</v>
       </c>
-      <c r="B12" s="36"/>
-      <c r="C12" s="40">
+      <c r="B12" s="40"/>
+      <c r="C12" s="31">
         <v>1174221626</v>
       </c>
-      <c r="D12" s="40" t="s">
+      <c r="D12" s="31" t="s">
         <v>5</v>
       </c>
-      <c r="E12" s="39" t="s">
-        <v>70</v>
-      </c>
-      <c r="F12" s="39" t="s">
+      <c r="E12" s="30" t="s">
+        <v>70</v>
+      </c>
+      <c r="F12" s="30" t="s">
         <v>71</v>
       </c>
-      <c r="G12" s="39"/>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G12" s="30"/>
+    </row>
+    <row r="13" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A13" s="19">
         <v>12</v>
       </c>
-      <c r="B13" s="36"/>
+      <c r="B13" s="40"/>
       <c r="C13" s="10">
         <v>1173963044</v>
       </c>
@@ -1818,11 +1840,11 @@
         <v>49</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A14" s="19">
         <v>13</v>
       </c>
-      <c r="B14" s="36"/>
+      <c r="B14" s="40"/>
       <c r="C14" s="7">
         <v>1173963045</v>
       </c>
@@ -1839,106 +1861,106 @@
         <v>46</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A15" s="19">
         <v>14</v>
       </c>
-      <c r="B15" s="36"/>
-      <c r="C15" s="40">
+      <c r="B15" s="40"/>
+      <c r="C15" s="31">
         <v>1173963046</v>
       </c>
-      <c r="D15" s="40" t="s">
+      <c r="D15" s="31" t="s">
         <v>14</v>
       </c>
-      <c r="E15" s="39" t="s">
-        <v>70</v>
-      </c>
-      <c r="F15" s="39" t="s">
-        <v>72</v>
-      </c>
-      <c r="G15" s="39"/>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="E15" s="30" t="s">
+        <v>70</v>
+      </c>
+      <c r="F15" s="30" t="s">
+        <v>72</v>
+      </c>
+      <c r="G15" s="30"/>
+    </row>
+    <row r="16" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A16" s="19">
         <v>15</v>
       </c>
-      <c r="B16" s="36"/>
-      <c r="C16" s="40">
+      <c r="B16" s="40"/>
+      <c r="C16" s="31">
         <v>1173963047</v>
       </c>
-      <c r="D16" s="40" t="s">
+      <c r="D16" s="31" t="s">
         <v>15</v>
       </c>
-      <c r="E16" s="39" t="s">
-        <v>70</v>
-      </c>
-      <c r="F16" s="39" t="s">
-        <v>72</v>
-      </c>
-      <c r="G16" s="39"/>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="E16" s="30" t="s">
+        <v>70</v>
+      </c>
+      <c r="F16" s="30" t="s">
+        <v>72</v>
+      </c>
+      <c r="G16" s="30"/>
+    </row>
+    <row r="17" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A17" s="19">
         <v>16</v>
       </c>
-      <c r="B17" s="36"/>
-      <c r="C17" s="40" t="s">
+      <c r="B17" s="40"/>
+      <c r="C17" s="31" t="s">
         <v>74</v>
       </c>
-      <c r="D17" s="40" t="s">
+      <c r="D17" s="31" t="s">
         <v>76</v>
       </c>
-      <c r="E17" s="39" t="s">
+      <c r="E17" s="30" t="s">
         <v>64</v>
       </c>
-      <c r="F17" s="39" t="s">
-        <v>72</v>
-      </c>
-      <c r="G17" s="39"/>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="F17" s="30" t="s">
+        <v>72</v>
+      </c>
+      <c r="G17" s="30"/>
+    </row>
+    <row r="18" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18" s="19">
         <v>17</v>
       </c>
-      <c r="B18" s="36"/>
-      <c r="C18" s="40" t="s">
+      <c r="B18" s="40"/>
+      <c r="C18" s="31" t="s">
         <v>75</v>
       </c>
-      <c r="D18" s="40" t="s">
+      <c r="D18" s="31" t="s">
         <v>77</v>
       </c>
-      <c r="E18" s="39" t="s">
+      <c r="E18" s="30" t="s">
         <v>64</v>
       </c>
-      <c r="F18" s="39" t="s">
-        <v>72</v>
-      </c>
-      <c r="G18" s="39"/>
+      <c r="F18" s="30" t="s">
+        <v>72</v>
+      </c>
+      <c r="G18" s="30"/>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="19">
         <v>18</v>
       </c>
-      <c r="B19" s="37"/>
-      <c r="C19" s="38" t="s">
+      <c r="B19" s="41"/>
+      <c r="C19" s="29" t="s">
         <v>52</v>
       </c>
-      <c r="D19" s="41" t="s">
+      <c r="D19" s="32" t="s">
         <v>56</v>
       </c>
-      <c r="E19" s="39" t="s">
+      <c r="E19" s="30" t="s">
         <v>66</v>
       </c>
-      <c r="F19" s="39" t="s">
+      <c r="F19" s="30" t="s">
         <v>71</v>
       </c>
-      <c r="G19" s="39"/>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G19" s="30"/>
+    </row>
+    <row r="20" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A20" s="19">
         <v>19</v>
       </c>
-      <c r="B20" s="35" t="s">
+      <c r="B20" s="39" t="s">
         <v>43</v>
       </c>
       <c r="C20" s="8">
@@ -1955,11 +1977,11 @@
       </c>
       <c r="G20" s="19"/>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A21" s="19">
         <v>20</v>
       </c>
-      <c r="B21" s="36"/>
+      <c r="B21" s="40"/>
       <c r="C21" s="7">
         <v>1174966078</v>
       </c>
@@ -1976,11 +1998,11 @@
         <v>49</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A22" s="19">
         <v>21</v>
       </c>
-      <c r="B22" s="36"/>
+      <c r="B22" s="40"/>
       <c r="C22" s="8">
         <v>1173963048</v>
       </c>
@@ -1995,11 +2017,11 @@
       </c>
       <c r="G22" s="19"/>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A23" s="19">
         <v>22</v>
       </c>
-      <c r="B23" s="36"/>
+      <c r="B23" s="40"/>
       <c r="C23" s="8">
         <v>1173963049</v>
       </c>
@@ -2014,11 +2036,11 @@
       </c>
       <c r="G23" s="19"/>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A24" s="19">
         <v>23</v>
       </c>
-      <c r="B24" s="36"/>
+      <c r="B24" s="40"/>
       <c r="C24" s="8">
         <v>1173963050</v>
       </c>
@@ -2033,11 +2055,11 @@
       </c>
       <c r="G24" s="19"/>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A25" s="19">
         <v>24</v>
       </c>
-      <c r="B25" s="36"/>
+      <c r="B25" s="40"/>
       <c r="C25" s="8">
         <v>1173963051</v>
       </c>
@@ -2052,11 +2074,11 @@
       </c>
       <c r="G25" s="19"/>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A26" s="19">
         <v>25</v>
       </c>
-      <c r="B26" s="36"/>
+      <c r="B26" s="40"/>
       <c r="C26" s="8">
         <v>1173963052</v>
       </c>
@@ -2071,11 +2093,11 @@
       </c>
       <c r="G26" s="19"/>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27" s="19">
         <v>26</v>
       </c>
-      <c r="B27" s="36"/>
+      <c r="B27" s="40"/>
       <c r="C27" s="27">
         <v>1173963053</v>
       </c>
@@ -2090,11 +2112,11 @@
       </c>
       <c r="G27" s="28"/>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28" s="19">
         <v>27</v>
       </c>
-      <c r="B28" s="36"/>
+      <c r="B28" s="40"/>
       <c r="C28" s="8">
         <v>1173963054</v>
       </c>
@@ -2109,11 +2131,11 @@
       </c>
       <c r="G28" s="19"/>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A29" s="19">
         <v>28</v>
       </c>
-      <c r="B29" s="36"/>
+      <c r="B29" s="40"/>
       <c r="C29" s="8">
         <v>1173963055</v>
       </c>
@@ -2128,11 +2150,11 @@
       </c>
       <c r="G29" s="19"/>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A30" s="19">
         <v>29</v>
       </c>
-      <c r="B30" s="36"/>
+      <c r="B30" s="40"/>
       <c r="C30" s="4">
         <v>1173963056</v>
       </c>
@@ -2149,11 +2171,11 @@
         <v>46</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A31" s="19">
         <v>30</v>
       </c>
-      <c r="B31" s="36"/>
+      <c r="B31" s="40"/>
       <c r="C31" s="8">
         <v>1173963057</v>
       </c>
@@ -2168,11 +2190,11 @@
       </c>
       <c r="G31" s="19"/>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A32" s="19">
         <v>31</v>
       </c>
-      <c r="B32" s="36"/>
+      <c r="B32" s="40"/>
       <c r="C32" s="8">
         <v>1173963058</v>
       </c>
@@ -2187,11 +2209,11 @@
       </c>
       <c r="G32" s="19"/>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A33" s="19">
         <v>32</v>
       </c>
-      <c r="B33" s="36"/>
+      <c r="B33" s="40"/>
       <c r="C33" s="8">
         <v>1173963059</v>
       </c>
@@ -2206,11 +2228,11 @@
       </c>
       <c r="G33" s="19"/>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A34" s="19">
         <v>33</v>
       </c>
-      <c r="B34" s="36"/>
+      <c r="B34" s="40"/>
       <c r="C34" s="8">
         <v>1173963060</v>
       </c>
@@ -2225,11 +2247,11 @@
       </c>
       <c r="G34" s="19"/>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A35" s="19">
         <v>34</v>
       </c>
-      <c r="B35" s="36"/>
+      <c r="B35" s="40"/>
       <c r="C35" s="7">
         <v>1173963061</v>
       </c>
@@ -2246,11 +2268,11 @@
         <v>49</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A36" s="19">
         <v>35</v>
       </c>
-      <c r="B36" s="36"/>
+      <c r="B36" s="40"/>
       <c r="C36" s="8">
         <v>1173963062</v>
       </c>
@@ -2265,11 +2287,11 @@
       </c>
       <c r="G36" s="19"/>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A37" s="19">
         <v>36</v>
       </c>
-      <c r="B37" s="36"/>
+      <c r="B37" s="40"/>
       <c r="C37" s="8">
         <v>1173963063</v>
       </c>
@@ -2284,11 +2306,11 @@
       </c>
       <c r="G37" s="19"/>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A38" s="19">
         <v>37</v>
       </c>
-      <c r="B38" s="36"/>
+      <c r="B38" s="40"/>
       <c r="C38" s="8">
         <v>1173963064</v>
       </c>
@@ -2303,11 +2325,11 @@
       </c>
       <c r="G38" s="19"/>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A39" s="19">
         <v>38</v>
       </c>
-      <c r="B39" s="36"/>
+      <c r="B39" s="40"/>
       <c r="C39" s="4">
         <v>1173963065</v>
       </c>
@@ -2324,11 +2346,11 @@
         <v>49</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A40" s="19">
         <v>39</v>
       </c>
-      <c r="B40" s="36"/>
+      <c r="B40" s="40"/>
       <c r="C40" s="8">
         <v>1173963066</v>
       </c>
@@ -2343,11 +2365,11 @@
       </c>
       <c r="G40" s="19"/>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A41" s="19">
         <v>40</v>
       </c>
-      <c r="B41" s="36"/>
+      <c r="B41" s="40"/>
       <c r="C41" s="8">
         <v>1173963067</v>
       </c>
@@ -2362,11 +2384,11 @@
       </c>
       <c r="G41" s="19"/>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A42" s="19">
         <v>41</v>
       </c>
-      <c r="B42" s="36"/>
+      <c r="B42" s="40"/>
       <c r="C42" s="8">
         <v>1170534788</v>
       </c>
@@ -2381,11 +2403,11 @@
       </c>
       <c r="G42" s="19"/>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A43" s="19">
         <v>42</v>
       </c>
-      <c r="B43" s="36"/>
+      <c r="B43" s="40"/>
       <c r="C43" s="8">
         <v>1170534789</v>
       </c>
@@ -2404,7 +2426,7 @@
       <c r="A44" s="19">
         <v>43</v>
       </c>
-      <c r="B44" s="36"/>
+      <c r="B44" s="40"/>
       <c r="C44" s="23" t="s">
         <v>53</v>
       </c>
@@ -2419,14 +2441,14 @@
       </c>
       <c r="G44" s="19"/>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A45" s="19"/>
-      <c r="B45" s="36"/>
+      <c r="B45" s="40"/>
       <c r="C45" s="6" t="s">
         <v>78</v>
       </c>
-      <c r="D45" s="20">
-        <v>1211326214</v>
+      <c r="D45" s="42" t="s">
+        <v>82</v>
       </c>
       <c r="E45" s="20" t="s">
         <v>64</v>
@@ -2438,14 +2460,14 @@
         <v>49</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A46" s="19"/>
-      <c r="B46" s="36"/>
+      <c r="B46" s="40"/>
       <c r="C46" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="D46" s="19">
-        <v>1212631236</v>
+      <c r="D46" s="43" t="s">
+        <v>83</v>
       </c>
       <c r="E46" s="19" t="s">
         <v>64</v>
@@ -2455,14 +2477,14 @@
       </c>
       <c r="G46" s="19"/>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A47" s="19"/>
-      <c r="B47" s="36"/>
+      <c r="B47" s="40"/>
       <c r="C47" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="D47" s="19">
-        <v>1210207642</v>
+      <c r="D47" s="43" t="s">
+        <v>84</v>
       </c>
       <c r="E47" s="19" t="s">
         <v>64</v>
@@ -2472,14 +2494,14 @@
       </c>
       <c r="G47" s="19"/>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A48" s="19"/>
-      <c r="B48" s="37"/>
+      <c r="B48" s="41"/>
       <c r="C48" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="D48" s="19">
-        <v>1211065926</v>
+      <c r="D48" s="43" t="s">
+        <v>85</v>
       </c>
       <c r="E48" s="19" t="s">
         <v>64</v>
@@ -2490,6 +2512,13 @@
       <c r="G48" s="19"/>
     </row>
   </sheetData>
+  <autoFilter ref="A1:G48" xr:uid="{4F2BD792-CCE4-406F-96E2-4768C3AF568E}">
+    <filterColumn colId="4">
+      <filters>
+        <filter val="Viettel"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <mergeCells count="2">
     <mergeCell ref="B20:B48"/>
     <mergeCell ref="B2:B19"/>
